--- a/docs/00_构建与版本/版本改动与测试/Ⅱ代储罐在线计量仪版本升级记录.xlsx
+++ b/docs/00_构建与版本/版本改动与测试/Ⅱ代储罐在线计量仪版本升级记录.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本改动" sheetId="1" r:id="Rd74b4fc7154a4099"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本改动" sheetId="1" r:id="R8c8c62ce251b4ce2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1328,107 +1328,129 @@
         <x:v>46289</x:v>
       </x:c>
       <x:c r="B4" s="13" t="str">
+        <x:v>V1.45.0.0</x:v>
+      </x:c>
+      <x:c r="C4" s="13" t="str">
+        <x:v>V1.44.0.0</x:v>
+      </x:c>
+      <x:c r="D4" s="14" t="str">
+        <x:v>维护模式成为继电器报警唯一屏蔽入口</x:v>
+      </x:c>
+      <x:c r="E4" s="14" t="str">
+        <x:v>1. 未进入维护时，普通或强制上下行不再自动关闭继电器报警，可继续按位置和报警条件实时动作。
+2. 进入维护后仍屏蔽四路继电器最终动作，退出维护后按当前报警条件或锁存状态恢复。
+3. 手动报警抑制字段固定为 0 兼容保留；共享协议升级到 38，双板需配套使用。</x:v>
+      </x:c>
+      <x:c r="F4" s="15" t="str">
+        <x:v>CPU2/CPU3 必须配套升级；参数地址和现场设置不变、无需重设。升级后需实测上下行跨阈值、维护进入/退出、物理继电器和 AO 故障电流。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" s="28" customFormat="1" ht="82.5" customHeight="1">
+      <x:c r="A5" s="33" t="n">
+        <x:v>46289</x:v>
+      </x:c>
+      <x:c r="B5" s="13" t="str">
         <x:v>V1.44.2.0</x:v>
       </x:c>
-      <x:c r="C4" s="13" t="str">
+      <x:c r="C5" s="13" t="str">
         <x:v>V1.43.1.0</x:v>
       </x:c>
-      <x:c r="D4" s="14" t="str">
+      <x:c r="D5" s="14" t="str">
         <x:v>修复继电器参数非对齐访问风险</x:v>
       </x:c>
-      <x:c r="E4" s="14" t="str">
+      <x:c r="E5" s="14" t="str">
         <x:v>1. 继电器报警参数明确按 1 字节对齐，避免固件读取非对齐浮点配置时触发 HardFault 重启。
 2. 参数总大小、继电器配置位置、CRC 范围和现场保存值保持不变，升级不清参数。
 3. 增加编译期布局检查，后续布局变化会在构建阶段直接失败。</x:v>
       </x:c>
-      <x:c r="F4" s="15" t="str">
+      <x:c r="F5" s="15" t="str">
         <x:v>CPU2 PATCH 版本；CPU3 保持 V1.43.1.0。升级前记录现场继电器设置，升级后核对并实测报警输出；目标板长期运行待验证。</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" s="28" customFormat="1" ht="82.5" customHeight="1">
-      <x:c r="A5" s="33" t="n">
+    <x:row r="6" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A6" s="33" t="n">
         <x:v>46286</x:v>
       </x:c>
-      <x:c r="B5" s="13" t="inlineStr">
+      <x:c r="B6" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.44.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C5" s="13" t="inlineStr">
+      <x:c r="C6" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.43.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D5" s="14" t="inlineStr">
+      <x:c r="D6" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复液位跟随自动恢复重跑计数</x:t>
         </x:is>
       </x:c>
-      <x:c r="E5" s="14" t="inlineStr">
+      <x:c r="E6" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1. 液位成功进入 STATE_FLOWOIL 后，活动自动恢复上下文清零业务重跑计数。
 2. 后续再次无法进入跟随状态时，从零开始按既有上限连续计数并报警。
 3. 恢复检查失败计数、命令切换取消恢复及参数/协议保持不变。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F5" s="15" t="inlineStr">
+      <x:c r="F6" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">CPU2 PATCH 版本；目标板、传感器与现场故障恢复时序待验证。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="6" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A6" s="33" t="n">
+    <x:row r="7" s="28" customFormat="1" ht="16.5" customHeight="1">
+      <x:c r="A7" s="34" t="n">
         <x:v>46279</x:v>
       </x:c>
-      <x:c r="B6" s="13" t="inlineStr">
+      <x:c r="B7" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.44.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C6" s="13" t="inlineStr">
+      <x:c r="C7" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.43.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D6" s="14" t="inlineStr">
+      <x:c r="D7" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复外部COM长期运行后通信无响应</x:t>
         </x:is>
       </x:c>
-      <x:c r="E6" s="14" t="inlineStr">
+      <x:c r="E7" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1. 外部COM启动保护结束后锁存就绪状态，避免设备长时间运行跨计时回绕后停止处理通信。
 2. 保留原有三路串口收发和1秒启动保护，不阻塞屏幕和CPU2通信。
 3. 补充长期运行、计时回绕和发送完成恢复检查。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F6" s="15" t="inlineStr">
+      <x:c r="F7" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">CPU3修复版本；升级前确认CPU2配套版本，参数无需重设；RS485长期运行需现场验证。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="7" s="28" customFormat="1" ht="16.5" customHeight="1">
-      <x:c r="A7" s="34" t="n">
+    <x:row r="8" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A8" s="33" t="n">
         <x:v>46272</x:v>
       </x:c>
-      <x:c r="B7" s="17" t="inlineStr">
+      <x:c r="B8" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.44.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C7" s="17" t="inlineStr">
+      <x:c r="C8" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.43.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D7" s="18" t="inlineStr">
+      <x:c r="D8" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">称重探底与下行保护</x:t>
         </x:is>
       </x:c>
-      <x:c r="E7" s="18" t="inlineStr">
+      <x:c r="E8" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠探底扭力阈值改为开始检测后需要减少的重量，名称不变。
 2.⁠接近预计罐底才检测并分段减速，减少低速运行距离。
@@ -1439,32 +1461,32 @@
 7.⁠SI 分布首点必须高于探底释放位置，不再自动改写首点。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F7" s="19" t="inlineStr">
+      <x:c r="F8" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">两块板需配套升级；称重探底阈值不能为 0。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="8" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A8" s="33" t="n">
+    <x:row r="9" s="28" customFormat="1" ht="82.5" customHeight="1">
+      <x:c r="A9" s="34" t="n">
         <x:v>46272</x:v>
       </x:c>
-      <x:c r="B8" s="13" t="inlineStr">
+      <x:c r="B9" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.43.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C8" s="13" t="inlineStr">
+      <x:c r="C9" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.42.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D8" s="14" t="inlineStr">
+      <x:c r="D9" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">液位定时矫正</x:t>
         </x:is>
       </x:c>
-      <x:c r="E8" s="14" t="inlineStr">
+      <x:c r="E9" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增“定时矫正”和“矫正周期”设置。
 2.⁠设备稳定跟随液位后，可按周期重新检查找液位所用的参考频率。
@@ -1473,68 +1495,38 @@
 5.⁠矫正失败会尝试恢复，多次失败后报故障。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F8" s="20" t="inlineStr">
+      <x:c r="F9" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">两块板需配套升级；液位定时矫正升级后默认关闭。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="9" s="28" customFormat="1" ht="82.5" customHeight="1">
-      <x:c r="A9" s="34" t="n">
+    <x:row r="10" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A10" s="33" t="n">
         <x:v>46270</x:v>
       </x:c>
-      <x:c r="B9" s="17" t="inlineStr">
+      <x:c r="B10" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.42.11.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C9" s="17" t="inlineStr">
+      <x:c r="C10" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.41.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D9" s="18" t="inlineStr">
+      <x:c r="D10" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复液位跟随时的丢步误报</x:t>
         </x:is>
       </x:c>
-      <x:c r="E9" s="18" t="inlineStr">
+      <x:c r="E10" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复固定频率找液位方式（方式5）换向、变速时，误报电机没有走够距离（丢步）的问题。
 2.⁠停止等待时不再按仍在运动计算，减少误报。
 3.⁠探头抖动或回退时，不重复计算前进距离。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F9" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="10" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A10" s="33" t="n">
-        <x:v>46270</x:v>
-      </x:c>
-      <x:c r="B10" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.42.10.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C10" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.41.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D10" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">新增两路常亮面板指示灯</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E10" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠新增两路面板指示灯控制，按现有接线保持常亮。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F10" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -1543,56 +1535,86 @@
     </x:row>
     <x:row r="11" s="28" customFormat="1" ht="66" customHeight="1">
       <x:c r="A11" s="34" t="n">
+        <x:v>46270</x:v>
+      </x:c>
+      <x:c r="B11" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.42.10.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C11" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.41.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D11" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">新增两路常亮面板指示灯</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E11" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠新增两路面板指示灯控制，按现有接线保持常亮。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F11" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="12" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A12" s="33" t="n">
         <x:v>46269</x:v>
       </x:c>
-      <x:c r="B11" s="17" t="inlineStr">
+      <x:c r="B12" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.42.10.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C11" s="17" t="inlineStr">
+      <x:c r="C12" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D11" s="18" t="inlineStr">
+      <x:c r="D12" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">调整SI分布测量首个测点和读数等待</x:t>
         </x:is>
       </x:c>
-      <x:c r="E11" s="18" t="inlineStr">
+      <x:c r="E12" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠探底后，上提 100 mm 的停机位置直接作为第 0 测点，不再多向下走一次。
 2.⁠到达每个测点后，先切密度模式，再按设置时间等待。
 3.⁠读数为零或还不能使用时先继续等待，不立即认定探头已在空气中。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F11" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="12" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A12" s="33" t="n">
+      <x:c r="F12" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="13" s="28" customFormat="1" ht="16.5" customHeight="1">
+      <x:c r="A13" s="34" t="n">
         <x:v>46268</x:v>
       </x:c>
-      <x:c r="B12" s="13" t="inlineStr">
+      <x:c r="B13" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.42.9.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C12" s="13" t="inlineStr">
+      <x:c r="C13" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D12" s="14" t="inlineStr">
+      <x:c r="D13" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加DM4传感器通信重试和液位读数等待</x:t>
         </x:is>
       </x:c>
-      <x:c r="E12" s="14" t="inlineStr">
+      <x:c r="E13" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠DM4 传感器（V4 协议）通信失败后，允许重复发送的读取命令最多尝试 3 次。
 2.⁠液位频率为 0 时，先停机等待读数稳定。
@@ -1600,66 +1622,35 @@
 4.⁠记录失败时收到的数据，方便售后提供给研发排查。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F12" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="13" s="28" customFormat="1" ht="16.5" customHeight="1">
-      <x:c r="A13" s="34" t="n">
+      <x:c r="F13" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="14" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A14" s="33" t="n">
         <x:v>46261</x:v>
       </x:c>
-      <x:c r="B13" s="17" t="inlineStr">
+      <x:c r="B14" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.42.8.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C13" s="17" t="inlineStr">
+      <x:c r="C14" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D13" s="18" t="inlineStr">
+      <x:c r="D14" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加DM4传感器通信间隔和读数不稳定提示</x:t>
         </x:is>
       </x:c>
-      <x:c r="E13" s="18" t="inlineStr">
+      <x:c r="E14" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠每次与 DM4 传感器（V4 协议）通信后，留出至少 30 毫秒间隔，避免请求过密。
 2.⁠读到负频率时，提示当前频率不稳定。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F13" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="14" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A14" s="33" t="n">
-        <x:v>46260</x:v>
-      </x:c>
-      <x:c r="B14" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.42.7.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C14" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.40.1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D14" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">修复DM4传感器读数未稳时的通信误报</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E14" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠修复 DM4 传感器（V4 协议）读数暂未稳定时，被误报为通信故障的问题。
-2.⁠传感器自动发送数据、主控请求后传感器再回复，这两种方式都按相同规则处理暂时没有有效读数的情况。</x:t>
         </x:is>
       </x:c>
       <x:c r="F14" s="20" t="inlineStr">
@@ -1674,59 +1665,60 @@
       </x:c>
       <x:c r="B15" s="17" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.42.7.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C15" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.40.1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D15" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">修复DM4传感器读数未稳时的通信误报</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E15" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠修复 DM4 传感器（V4 协议）读数暂未稳定时，被误报为通信故障的问题。
+2.⁠传感器自动发送数据、主控请求后传感器再回复，这两种方式都按相同规则处理暂时没有有效读数的情况。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F15" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="16" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A16" s="33" t="n">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="B16" s="13" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.42.6.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C15" s="17" t="inlineStr">
+      <x:c r="C16" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D15" s="18" t="inlineStr">
+      <x:c r="D16" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">区分调试版和发布版程序包</x:t>
         </x:is>
       </x:c>
-      <x:c r="E15" s="18" t="inlineStr">
+      <x:c r="E16" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠程序文件区分 DEBUG 调试版和 RELEASE 发布版。
 2.⁠调试版可接收串口调试命令，发布版不接收这些命令。
 3.⁠发布版仍保留日志发送、正常测量和业务通信。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F15" s="19" t="inlineStr">
+      <x:c r="F16" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">串口调试使用 DEBUG 包；RELEASE 包不响应调试命令。</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="16" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A16" s="33" t="n">
-        <x:v>46260</x:v>
-      </x:c>
-      <x:c r="B16" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.42.5.1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C16" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.40.1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D16" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">调整调试串口未接线时的设置</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E16" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠调整调试串口未连接设备时的输入设置。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F16" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1736,119 +1728,118 @@
       </x:c>
       <x:c r="B17" s="17" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.42.5.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C17" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.40.1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D17" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">调整调试串口未接线时的设置</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E17" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠调整调试串口未连接设备时的输入设置。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F17" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="18" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A18" s="33" t="n">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="B18" s="13" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.42.5.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C17" s="17" t="inlineStr">
+      <x:c r="C18" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D17" s="18" t="inlineStr">
+      <x:c r="D18" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复DM4传感器通信测试的冲突与误判</x:t>
         </x:is>
       </x:c>
-      <x:c r="E17" s="18" t="inlineStr">
+      <x:c r="E18" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复传感器通信测试（SC）与 DM4 传感器（V4 协议）自动发送数据互相影响的问题。
 2.⁠探头在空气中暂时测不出密度时，可仍判断通信正常。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F17" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="18" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A18" s="33" t="n">
+      <x:c r="F18" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="19" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A19" s="34" t="n">
         <x:v>46259</x:v>
       </x:c>
-      <x:c r="B18" s="13" t="inlineStr">
+      <x:c r="B19" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.42.4.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C18" s="13" t="inlineStr">
+      <x:c r="C19" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D18" s="14" t="inlineStr">
+      <x:c r="D19" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">读取部件参数前先切密度模式</x:t>
         </x:is>
       </x:c>
-      <x:c r="E18" s="14" t="inlineStr">
+      <x:c r="E19" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠读取部件参数前先切换到密度模式。
 2.⁠通信自检前也会确认密度模式，减少从液位模式切入时的误报。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F18" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="19" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A19" s="34" t="n">
+      <x:c r="F19" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="20" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A20" s="33" t="n">
         <x:v>46258</x:v>
       </x:c>
-      <x:c r="B19" s="17" t="inlineStr">
+      <x:c r="B20" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.42.3.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C19" s="17" t="inlineStr">
+      <x:c r="C20" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D19" s="18" t="inlineStr">
+      <x:c r="D20" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复运动完成误判，密度未出时等待</x:t>
         </x:is>
       </x:c>
-      <x:c r="E19" s="18" t="inlineStr">
+      <x:c r="E20" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复探头仍在连续移动，却被程序误判已完成的问题。
 2.⁠电机收到启动要求后仍不转，会停止并报错。
 3.⁠DM4 传感器在密度模式下暂时读到频率 0 时，继续等待测量结果。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F19" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="20" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A20" s="33" t="n">
-        <x:v>46255</x:v>
-      </x:c>
-      <x:c r="B20" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.42.2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C20" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.40.1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D20" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">防止把旧温度、黏度当作新读数</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E20" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠温度还未更新时，不把旧温度当作新结果。
-2.⁠黏度还未更新时，不把旧黏度当作新结果。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F20" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -1861,116 +1852,147 @@
       </x:c>
       <x:c r="B21" s="17" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.42.2.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C21" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.40.1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D21" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">防止把旧温度、黏度当作新读数</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E21" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠温度还未更新时，不把旧温度当作新结果。
+2.⁠黏度还未更新时，不把旧黏度当作新结果。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F21" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="22" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A22" s="33" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="B22" s="13" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.42.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C21" s="17" t="inlineStr">
+      <x:c r="C22" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D21" s="18" t="inlineStr">
+      <x:c r="D22" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">切换操作先停机，探底失败沿用罐高</x:t>
         </x:is>
       </x:c>
-      <x:c r="E21" s="18" t="inlineStr">
+      <x:c r="E22" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠切换操作时先停机退出，不再误记为测量故障。
 2.⁠恢复原有做法：探底失败或偏差过大时，使用已设置的罐高作为后续参考。
 3.⁠统一液位、水位变化后电流数据的更新。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F21" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="22" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A22" s="33" t="n">
+      <x:c r="F22" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="23" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A23" s="34" t="n">
         <x:v>46253</x:v>
       </x:c>
-      <x:c r="B22" s="13" t="inlineStr">
+      <x:c r="B23" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.42.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C22" s="13" t="inlineStr">
+      <x:c r="C23" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D22" s="14" t="inlineStr">
+      <x:c r="D23" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增多参数传感器参数修改与读回确认</x:t>
         </x:is>
       </x:c>
-      <x:c r="E22" s="14" t="inlineStr">
+      <x:c r="E23" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增通过调试串口修改多参数传感器（V3/V4 协议）参数的命令。
 2.⁠修改后重新读取，确认实际值。
 3.⁠DM4 传感器（V4 协议）只允许在识别成功、通信方式正确时修改指定范围的参数。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F22" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="23" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A23" s="34" t="n">
+      <x:c r="F23" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="24" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A24" s="33" t="n">
         <x:v>46253</x:v>
       </x:c>
-      <x:c r="B23" s="17" t="inlineStr">
+      <x:c r="B24" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.41.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C23" s="17" t="inlineStr">
+      <x:c r="C24" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D23" s="18" t="inlineStr">
+      <x:c r="D24" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">滑环匹配完成前先确认传感器</x:t>
         </x:is>
       </x:c>
-      <x:c r="E23" s="18" t="inlineStr">
+      <x:c r="E24" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠无线滑环连上后，继续检查传感器类型和编号，全部识别成功才显示匹配完成。
 2.⁠修复识别不采用 V4 协议的传感器时，短暂误报 13-3 的问题。
 3.⁠无法确认传感器时，测量前会重新识别。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F23" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="24" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A24" s="33" t="n">
+      <x:c r="F24" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="25" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A25" s="34" t="n">
         <x:v>46252</x:v>
       </x:c>
-      <x:c r="B24" s="13" t="inlineStr">
+      <x:c r="B25" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.41.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C24" s="13" t="inlineStr">
+      <x:c r="C25" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D24" s="14" t="inlineStr">
+      <x:c r="D25" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">改善DM4传感器无线连接并增加测试命令</x:t>
         </x:is>
       </x:c>
-      <x:c r="E24" s="14" t="inlineStr">
+      <x:c r="E25" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增 DM4 传感器（V4 协议）的通信、模式和参数测试命令。
 2.⁠改善 DM4 传感器通过无线滑环连接时的识别和数据接收。
@@ -1978,133 +2000,102 @@
 4.⁠增加丢失数据和错误数据的记录，方便排查。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F24" s="20" t="inlineStr">
+      <x:c r="F25" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">测水操作与磁零点检测不能同时开启。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="25" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A25" s="34" t="n">
+    <x:row r="26" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A26" s="33" t="n">
         <x:v>46251</x:v>
       </x:c>
-      <x:c r="B25" s="17" t="inlineStr">
+      <x:c r="B26" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C25" s="17" t="inlineStr">
+      <x:c r="C26" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D25" s="18" t="inlineStr">
+      <x:c r="D26" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复屏幕残影和确认键多按一次</x:t>
         </x:is>
       </x:c>
-      <x:c r="E25" s="18" t="inlineStr">
+      <x:c r="E26" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复屏幕异常恢复后可能留下旧画面或残影的问题。
 2.⁠限制连续恢复次数，避免一直反复重启屏幕。
 3.⁠修复操作确认页还需额外多按一次确认的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F25" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="26" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A26" s="33" t="n">
+      <x:c r="F26" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="27" s="28" customFormat="1" ht="16.5" customHeight="1">
+      <x:c r="A27" s="34" t="n">
         <x:v>46251</x:v>
       </x:c>
-      <x:c r="B26" s="13" t="inlineStr">
+      <x:c r="B27" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C26" s="13" t="inlineStr">
+      <x:c r="C27" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D26" s="14" t="inlineStr">
+      <x:c r="D27" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">液位跟随支持更细的低速调整</x:t>
         </x:is>
       </x:c>
-      <x:c r="E26" s="14" t="inlineStr">
+      <x:c r="E27" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠固定频率找液位方式（方式5）跟随液位时，可更慢、更细地调整速度。
 2.⁠改变方向前先慢停，减少低速阶段误报丢步。
 3.⁠关闭电流输出后，不再继续操作电流输出硬件。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F26" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="27" s="28" customFormat="1" ht="16.5" customHeight="1">
-      <x:c r="A27" s="34" t="n">
+      <x:c r="F27" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="28" s="28" customFormat="1" ht="16.5" customHeight="1">
+      <x:c r="A28" s="33" t="n">
         <x:v>46248</x:v>
       </x:c>
-      <x:c r="B27" s="17" t="inlineStr">
+      <x:c r="B28" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C27" s="17" t="inlineStr">
+      <x:c r="C28" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D27" s="18" t="inlineStr">
+      <x:c r="D28" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加位置异常检查与故障提示</x:t>
         </x:is>
       </x:c>
-      <x:c r="E27" s="18" t="inlineStr">
+      <x:c r="E28" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加上电位置变化检查，发现保存位置与当前情况不符时提示故障。
 2.⁠运行中位置突然跳变时，增加检查和保护。
 3.⁠完善位置保存和掉电保存，屏幕增加相关故障原因。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F27" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="28" s="28" customFormat="1" ht="16.5" customHeight="1">
-      <x:c r="A28" s="33" t="n">
-        <x:v>46247</x:v>
-      </x:c>
-      <x:c r="B28" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.39.2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C28" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.39.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D28" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">新增协议查询，减少连接选错</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E28" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠新增查询当前通信协议的功能。
-2.⁠与设备连接的电脑或控制系统可据此识别设备，减少自动连接时选错协议。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F28" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -2122,60 +2113,61 @@
       </x:c>
       <x:c r="C29" s="17" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.39.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D29" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">新增协议查询，减少连接选错</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E29" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠新增查询当前通信协议的功能。
+2.⁠与设备连接的电脑或控制系统可据此识别设备，减少自动连接时选错协议。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F29" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="30" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A30" s="33" t="n">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="B30" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.39.2.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C30" s="13" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.38.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D29" s="18" t="inlineStr">
+      <x:c r="D30" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修正固定频率找液位的方向和停点</x:t>
         </x:is>
       </x:c>
-      <x:c r="E29" s="18" t="inlineStr">
+      <x:c r="E30" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修正固定频率找液位方式（方式5）根据设定频率选择移动方向和速度的处理。
 2.⁠找到液体后，不再固定多向下走 100 mm。
 3.⁠到达低液位盲区时停止下行，避免继续向下找。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F29" s="19" t="inlineStr">
+      <x:c r="F30" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">升级后核对固定频率找液位的频率和阈值设置。</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="30" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A30" s="33" t="n">
-        <x:v>46247</x:v>
-      </x:c>
-      <x:c r="B30" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.39.1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C30" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.38.2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D30" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">减少两块板命令过密造成的通信异常</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E30" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠连续查询或操作之间增加必要间隔，减少命令发得过密造成的通信异常。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F30" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="31" s="28" customFormat="1" ht="49.5" customHeight="1">
       <x:c r="A31" s="34" t="n">
-        <x:v>46246</x:v>
+        <x:v>46247</x:v>
       </x:c>
       <x:c r="B31" s="17" t="inlineStr">
         <x:is>
@@ -2184,17 +2176,17 @@
       </x:c>
       <x:c r="C31" s="17" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">V1.38.1.1</x:t>
+          <x:t xml:space="preserve">V1.38.2.0</x:t>
         </x:is>
       </x:c>
       <x:c r="D31" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">显示文字整理</x:t>
+          <x:t xml:space="preserve">减少两块板命令过密造成的通信异常</x:t>
         </x:is>
       </x:c>
       <x:c r="E31" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.⁠整理重复的显示文字数据，节省程序空间，文字外观不变。</x:t>
+          <x:t xml:space="preserve">1.⁠连续查询或操作之间增加必要间隔，减少命令发得过密造成的通信异常。</x:t>
         </x:is>
       </x:c>
       <x:c r="F31" s="19" t="inlineStr">
@@ -2205,120 +2197,150 @@
     </x:row>
     <x:row r="32" s="28" customFormat="1" ht="66" customHeight="1">
       <x:c r="A32" s="33" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="B32" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.39.1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C32" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.38.1.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D32" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">显示文字整理</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E32" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠整理重复的显示文字数据，节省程序空间，文字外观不变。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F32" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="33" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A33" s="34" t="n">
         <x:v>46245</x:v>
       </x:c>
-      <x:c r="B32" s="13" t="inlineStr">
+      <x:c r="B33" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.39.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C32" s="13" t="inlineStr">
+      <x:c r="C33" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.38.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D32" s="14" t="inlineStr">
+      <x:c r="D33" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修正传感器识别并统一故障名称</x:t>
         </x:is>
       </x:c>
-      <x:c r="E32" s="14" t="inlineStr">
+      <x:c r="E33" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修正多参数传感器（V3/V4 协议）和 DSM 传感器的识别顺序及编号判断。
 2.⁠识别完 DM4 传感器（V4 协议）后，恢复原来的通信方式。
 3.⁠统一 49 项屏幕、日志和故障表的名称。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F32" s="20" t="inlineStr">
+      <x:c r="F33" s="21" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">编号为 0 的 DM4 传感器需使用后续版本。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="33" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A33" s="34" t="n">
+    <x:row r="34" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A34" s="33" t="n">
         <x:v>46244</x:v>
       </x:c>
-      <x:c r="B33" s="17" t="inlineStr">
+      <x:c r="B34" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.39.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C33" s="17" t="inlineStr">
+      <x:c r="C34" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.38.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D33" s="18" t="inlineStr">
+      <x:c r="D34" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">提高电流微调精度，补齐DM4传感器读数</x:t>
         </x:is>
       </x:c>
-      <x:c r="E33" s="18" t="inlineStr">
+      <x:c r="E34" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠电流修正可以精细到 0.001 mA，屏幕显示三位小数。
 2.⁠读取 DM4 传感器（V4 协议）数据前先检查测量模式，减少模式不对时的错误读数。
 3.⁠补齐水电容、姿态、黏度等读取。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F33" s="21" t="inlineStr">
+      <x:c r="F34" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">两块板及连接的电脑或控制系统需配套；旧电流修正值会自动换算。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="34" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A34" s="33" t="n">
+    <x:row r="35" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A35" s="34" t="n">
         <x:v>46242</x:v>
       </x:c>
-      <x:c r="B34" s="13" t="inlineStr">
+      <x:c r="B35" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.38.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C34" s="13" t="inlineStr">
+      <x:c r="C35" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.37.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D34" s="14" t="inlineStr">
+      <x:c r="D35" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增DSM传感器版本及更多部件信息查询</x:t>
         </x:is>
       </x:c>
-      <x:c r="E34" s="14" t="inlineStr">
+      <x:c r="E35" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加 DSM 传感器版本识别。
 2.⁠读取部件参数时，增加供电电压、黏度等信息。
 3.⁠附加信息读不到时，不阻断原有主要参数读取。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F34" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="35" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A35" s="34" t="n">
+      <x:c r="F35" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="36" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A36" s="33" t="n">
         <x:v>46242</x:v>
       </x:c>
-      <x:c r="B35" s="17" t="inlineStr">
+      <x:c r="B36" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.37.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C35" s="17" t="inlineStr">
+      <x:c r="C36" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.37.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D35" s="18" t="inlineStr">
+      <x:c r="D36" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增DM4传感器（V4协议）支持</x:t>
         </x:is>
       </x:c>
-      <x:c r="E35" s="18" t="inlineStr">
+      <x:c r="E36" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增 DM4 传感器（V4 协议）支持，屏幕类型名称为“多参数V4”。
 2.⁠支持传感器自动发送数据，也支持主控请求后传感器再回复。
@@ -2326,129 +2348,98 @@
 4.⁠部分纯运动操作在传感器离线时也可执行。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F35" s="19" t="inlineStr">
+      <x:c r="F36" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">退回旧程序前，先将传感器参数 65（发送方式）改为“交互方式”，并改回旧程序支持的传感器类型。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="36" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A36" s="33" t="n">
+    <x:row r="37" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A37" s="34" t="n">
         <x:v>46241</x:v>
       </x:c>
-      <x:c r="B36" s="13" t="inlineStr">
+      <x:c r="B37" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.36.4.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C36" s="13" t="inlineStr">
+      <x:c r="C37" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.36.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D36" s="14" t="inlineStr">
+      <x:c r="D37" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复DSM传感器通信误报和异常倾角显示</x:t>
         </x:is>
       </x:c>
-      <x:c r="E36" s="14" t="inlineStr">
+      <x:c r="E37" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复收到完整传感器回复，却误报数据不完整或通信错误的问题。
 2.⁠查完蓝牙状态后，确认传感器通信已恢复再继续测量。
 3.⁠传感器返回的错误提示值，不再显示成真实倾角。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F36" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="37" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A37" s="34" t="n">
+      <x:c r="F37" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="38" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A38" s="33" t="n">
         <x:v>46241</x:v>
       </x:c>
-      <x:c r="B37" s="17" t="inlineStr">
+      <x:c r="B38" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.36.3.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C37" s="17" t="inlineStr">
+      <x:c r="C38" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.36.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D37" s="18" t="inlineStr">
+      <x:c r="D38" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复长距离低速移动过早报超时</x:t>
         </x:is>
       </x:c>
-      <x:c r="E37" s="18" t="inlineStr">
+      <x:c r="E38" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复低速、长距离移动还没到目标，就在 1 小时被判超时的问题。
 2.⁠按实际距离和速度安排允许时间，日志可查看已用时间和允许时间。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F37" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="38" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A38" s="33" t="n">
+      <x:c r="F38" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="39" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A39" s="34" t="n">
         <x:v>46238</x:v>
       </x:c>
-      <x:c r="B38" s="13" t="inlineStr">
+      <x:c r="B39" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.36.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C38" s="13" t="inlineStr">
+      <x:c r="C39" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.36.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D38" s="14" t="inlineStr">
+      <x:c r="D39" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">液位标定后同步调整电流量程</x:t>
         </x:is>
       </x:c>
-      <x:c r="E38" s="14" t="inlineStr">
+      <x:c r="E39" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠液位标定改变罐高后，电流量程会相应调整，不超过新罐高。
 2.⁠修复旧量程影响电流输出或阻止后续修改参数的问题。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F38" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="39" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A39" s="34" t="n">
-        <x:v>46232</x:v>
-      </x:c>
-      <x:c r="B39" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.36.1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C39" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.36.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D39" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">修复蓝牙查询干扰传感器通信</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E39" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠修复查完蓝牙信号后，残留回复干扰传感器通信的问题。
-2.⁠查询中途被新操作打断时，也会恢复传感器通信。</x:t>
         </x:is>
       </x:c>
       <x:c r="F39" s="19" t="inlineStr">
@@ -2463,20 +2454,51 @@
       </x:c>
       <x:c r="B40" s="13" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.36.1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C40" s="13" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.36.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C40" s="13" t="inlineStr">
+      <x:c r="D40" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">修复蓝牙查询干扰传感器通信</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E40" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠修复查完蓝牙信号后，残留回复干扰传感器通信的问题。
+2.⁠查询中途被新操作打断时，也会恢复传感器通信。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F40" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="41" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A41" s="34" t="n">
+        <x:v>46232</x:v>
+      </x:c>
+      <x:c r="B41" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.36.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D40" s="14" t="inlineStr">
+      <x:c r="C41" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.36.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D41" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增扭力温度显示，修正标定保存</x:t>
         </x:is>
       </x:c>
-      <x:c r="E40" s="14" t="inlineStr">
+      <x:c r="E41" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠读取部件参数、获取空载或满载扭力时，可查看扭力模块温度。
 2.⁠收到错误的扭力数据时，不再当作通信恢复正常。
@@ -2484,32 +2506,32 @@
 4.⁠罐高标定完成规定动作后，才保存新罐高。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F40" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="41" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A41" s="34" t="n">
+      <x:c r="F41" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="42" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A42" s="33" t="n">
         <x:v>46231</x:v>
       </x:c>
-      <x:c r="B41" s="17" t="inlineStr">
+      <x:c r="B42" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.35.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C41" s="17" t="inlineStr">
+      <x:c r="C42" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.35.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D41" s="18" t="inlineStr">
+      <x:c r="D42" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加低电压停机和位置保护</x:t>
         </x:is>
       </x:c>
-      <x:c r="E41" s="18" t="inlineStr">
+      <x:c r="E42" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加 24 V 供电检查，电压过低时禁止运动并尝试保存位置。
 2.⁠供电检测异常后，设备会有限次数地尝试恢复。
@@ -2517,32 +2539,32 @@
 4.⁠增加供电故障的屏幕提示。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F41" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="42" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A42" s="33" t="n">
+      <x:c r="F42" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="43" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A43" s="34" t="n">
         <x:v>46228</x:v>
       </x:c>
-      <x:c r="B42" s="13" t="inlineStr">
+      <x:c r="B43" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.34.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C42" s="13" t="inlineStr">
+      <x:c r="C43" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.34.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D42" s="14" t="inlineStr">
+      <x:c r="D43" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">调整故障编号并提高密度允许上限</x:t>
         </x:is>
       </x:c>
-      <x:c r="E42" s="14" t="inlineStr">
+      <x:c r="E43" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠调整扭力、电流输出等故障的编号和分类。
 2.⁠密度允许上限从 2000.0 调整为 3000.0 kg/m3。
@@ -2550,32 +2572,32 @@
 4.⁠减少上电显示等待，改善外部通信启动。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F42" s="20" t="inlineStr">
+      <x:c r="F43" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">两块板需配套，并使用对应版本的故障代码表。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="43" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A43" s="34" t="n">
+    <x:row r="44" s="28" customFormat="1" ht="132" customHeight="1">
+      <x:c r="A44" s="33" t="n">
         <x:v>46228</x:v>
       </x:c>
-      <x:c r="B43" s="17" t="inlineStr">
+      <x:c r="B44" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.33.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C43" s="17" t="inlineStr">
+      <x:c r="C44" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.33.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D43" s="18" t="inlineStr">
+      <x:c r="D44" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">防止测量目标被改，检查报警设置</x:t>
         </x:is>
       </x:c>
-      <x:c r="E43" s="18" t="inlineStr">
+      <x:c r="E44" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠测量开始后固定使用本次输入的目标，后续修改不会改变正在测量的目标。
 2.⁠自动恢复重测也使用本次目标。
@@ -2583,32 +2605,32 @@
 4.⁠参数更新期间，其他可用的状态数据可以继续读取。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F43" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="44" s="28" customFormat="1" ht="132" customHeight="1">
-      <x:c r="A44" s="33" t="n">
+      <x:c r="F44" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="45" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A45" s="34" t="n">
         <x:v>46226</x:v>
       </x:c>
-      <x:c r="B44" s="13" t="inlineStr">
+      <x:c r="B45" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.32.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C44" s="13" t="inlineStr">
+      <x:c r="C45" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.32.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D44" s="14" t="inlineStr">
+      <x:c r="D45" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增液位测试，修复区间测量结果</x:t>
         </x:is>
       </x:c>
-      <x:c r="E44" s="14" t="inlineStr">
+      <x:c r="E45" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增固定频率找液位测试命令（LF）。
 2.⁠修复区间测点数量计算错误的问题。
@@ -2616,64 +2638,64 @@
 4.⁠传感器内部出错时，明确返回故障。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F44" s="20" t="inlineStr">
+      <x:c r="F45" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">LH 通信接口的“读线圈”固定返回全 0，不能用于判断实际开关状态。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="45" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A45" s="34" t="n">
+    <x:row r="46" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A46" s="33" t="n">
         <x:v>46226</x:v>
       </x:c>
-      <x:c r="B45" s="17" t="inlineStr">
+      <x:c r="B46" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.31.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C45" s="17" t="inlineStr">
+      <x:c r="C46" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.31.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D45" s="18" t="inlineStr">
+      <x:c r="D46" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">测量期间限制修改设备设置</x:t>
         </x:is>
       </x:c>
-      <x:c r="E45" s="18" t="inlineStr">
+      <x:c r="E46" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠测量或自动恢复期间，不允许修改普通设备设置。
 2.⁠设备停在故障状态且没有继续执行任务时，可以修正参数。
 3.⁠调整程序运行监测，缩短检查间隔。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F45" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="46" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A46" s="33" t="n">
+      <x:c r="F46" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="47" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A47" s="34" t="n">
         <x:v>46226</x:v>
       </x:c>
-      <x:c r="B46" s="13" t="inlineStr">
+      <x:c r="B47" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.31.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C46" s="13" t="inlineStr">
+      <x:c r="C47" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.31.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D46" s="14" t="inlineStr">
+      <x:c r="D47" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增屏幕维护操作和报警清除</x:t>
         </x:is>
       </x:c>
-      <x:c r="E46" s="14" t="inlineStr">
+      <x:c r="E47" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠屏幕可进入、退出维护模式。
 2.⁠屏幕可清除全部继电器锁存报警，即报警条件消失后仍保持的报警。
@@ -2681,32 +2703,32 @@
 4.⁠继电器页可查看是否禁止动作，以及程序要求的最终动作。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F46" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="47" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A47" s="34" t="n">
+      <x:c r="F47" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="48" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A48" s="33" t="n">
         <x:v>46225</x:v>
       </x:c>
-      <x:c r="B47" s="17" t="inlineStr">
+      <x:c r="B48" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.31.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C47" s="17" t="inlineStr">
+      <x:c r="C48" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.30.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D47" s="18" t="inlineStr">
+      <x:c r="D48" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增LH通信接口及电流、报警维护操作</x:t>
         </x:is>
       </x:c>
-      <x:c r="E47" s="18" t="inlineStr">
+      <x:c r="E48" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增 LH 通信接口。
 2.⁠新增电流修正操作。
@@ -2716,64 +2738,64 @@
 6.⁠调整通信地址。LTD 通信接口默认改为波特率 4800、8 位数据、无校验、1 位停止（4800 8N1）。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F47" s="19" t="inlineStr">
+      <x:c r="F48" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">两块板需配套升级；升级后核对 LTD 通信接口地址和波特率。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="48" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A48" s="33" t="n">
+    <x:row r="49" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A49" s="34" t="n">
         <x:v>46224</x:v>
       </x:c>
-      <x:c r="B48" s="13" t="inlineStr">
+      <x:c r="B49" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.30.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C48" s="13" t="inlineStr">
+      <x:c r="C49" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.29.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D48" s="14" t="inlineStr">
+      <x:c r="D49" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复通信数据异常导致设备卡住</x:t>
         </x:is>
       </x:c>
-      <x:c r="E48" s="14" t="inlineStr">
+      <x:c r="E49" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复连续收到大量数据或错误数据后，设备可能卡住不响应的问题。
 2.⁠通信异常的端口会单独尝试恢复。
 3.⁠收到过长或不完整的数据时，丢弃后重新接收。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F48" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="49" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A49" s="34" t="n">
+      <x:c r="F49" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="50" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A50" s="33" t="n">
         <x:v>46223</x:v>
       </x:c>
-      <x:c r="B49" s="17" t="inlineStr">
+      <x:c r="B50" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.30.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C49" s="17" t="inlineStr">
+      <x:c r="C50" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.29.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D49" s="18" t="inlineStr">
+      <x:c r="D50" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增水位设置项并调整菜单操作</x:t>
         </x:is>
       </x:c>
-      <x:c r="E49" s="18" t="inlineStr">
+      <x:c r="E50" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增“水位滞后时间”设置项。
 2.⁠进入菜单的长按确认时间改为约 3 秒。
@@ -2781,95 +2803,95 @@
 4.⁠更新液位频率、水位电容和 SI 分布测量第一个测点的部分出厂默认值。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F49" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="50" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A50" s="33" t="n">
+      <x:c r="F50" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="51" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A51" s="34" t="n">
         <x:v>46221</x:v>
       </x:c>
-      <x:c r="B50" s="13" t="inlineStr">
+      <x:c r="B51" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.29.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C50" s="13" t="inlineStr">
+      <x:c r="C51" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.28.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D50" s="14" t="inlineStr">
+      <x:c r="D51" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复测量完成后结果仍旧或不全</x:t>
         </x:is>
       </x:c>
-      <x:c r="E50" s="14" t="inlineStr">
+      <x:c r="E51" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复已显示测量完成，但测点还是旧数据或没有收齐的问题。
 2.⁠结果传输失败后可以重试，成功后清除对应传输故障。
 3.⁠输出调试日志时，减少对正常通信的影响。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F50" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="51" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A51" s="34" t="n">
+      <x:c r="F51" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="52" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A52" s="33" t="n">
         <x:v>46220</x:v>
       </x:c>
-      <x:c r="B51" s="17" t="inlineStr">
+      <x:c r="B52" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.29.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C51" s="17" t="inlineStr">
+      <x:c r="C52" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.27.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D51" s="18" t="inlineStr">
+      <x:c r="D52" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">等待读数时保持电流，增加通信统计</x:t>
         </x:is>
       </x:c>
-      <x:c r="E51" s="18" t="inlineStr">
+      <x:c r="E52" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠重新找液位、切换操作或读数暂未稳定时，保持上次正常过程电流。
 2.⁠屏幕增加主控通信次数、失败比例和失败原因，方便检查连接。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F51" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="52" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A52" s="33" t="n">
+      <x:c r="F52" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="53" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A53" s="34" t="n">
         <x:v>46219</x:v>
       </x:c>
-      <x:c r="B52" s="13" t="inlineStr">
+      <x:c r="B53" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.28.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C52" s="13" t="inlineStr">
+      <x:c r="C53" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.26.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D52" s="14" t="inlineStr">
+      <x:c r="D53" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加故障电流选择，修复通信提示</x:t>
         </x:is>
       </x:c>
-      <x:c r="E52" s="14" t="inlineStr">
+      <x:c r="E53" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠电流故障时可选择输出设定的故障电流，或保持上次正常电流。
 2.⁠修复两块板程序不匹配时一直显示“通信尝试”的问题。
@@ -2877,32 +2899,32 @@
 4.⁠设备重启后，不继续使用重启前的旧测点。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F52" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="53" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A53" s="34" t="n">
+      <x:c r="F53" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="54" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A54" s="33" t="n">
         <x:v>46219</x:v>
       </x:c>
-      <x:c r="B53" s="17" t="inlineStr">
+      <x:c r="B54" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.27.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C53" s="17" t="inlineStr">
+      <x:c r="C54" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.25.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D53" s="18" t="inlineStr">
+      <x:c r="D54" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">扩展电流输出设置，防止混入旧结果</x:t>
         </x:is>
       </x:c>
-      <x:c r="E53" s="18" t="inlineStr">
+      <x:c r="E54" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠电流输出可设置测量来源、固定电流、变化快慢、故障动作和模拟测试。
 2.⁠修复固定点结果中混入不同次测量数据的问题。
@@ -2910,32 +2932,32 @@
 4.⁠自动恢复后，只有真正测量成功才记录“重试成功”。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F53" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="54" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A54" s="33" t="n">
+      <x:c r="F54" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="55" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A55" s="34" t="n">
         <x:v>46218</x:v>
       </x:c>
-      <x:c r="B54" s="13" t="inlineStr">
+      <x:c r="B55" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.26.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C54" s="13" t="inlineStr">
+      <x:c r="C55" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.24.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D54" s="14" t="inlineStr">
+      <x:c r="D55" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修正SI分布测量完成时机及新旧结果混用</x:t>
         </x:is>
       </x:c>
-      <x:c r="E54" s="14" t="inlineStr">
+      <x:c r="E55" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠SI 分布测量测完各点后，先回到液面并停稳，再显示测量完成。
 2.⁠取消或失败时，不把本轮结果当作完整结果。
@@ -2943,128 +2965,128 @@
 4.⁠完善跨日自动测量及站 2 通信兼容。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F54" s="20" t="inlineStr">
+      <x:c r="F55" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">升级前记录 SI 分布测量和串口通信设置；该版本存在旧设置保存失败风险。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="55" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A55" s="34" t="n">
+    <x:row r="56" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A56" s="33" t="n">
         <x:v>46217</x:v>
       </x:c>
-      <x:c r="B55" s="17" t="inlineStr">
+      <x:c r="B56" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.25.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C55" s="17" t="inlineStr">
+      <x:c r="C56" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.23.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D55" s="18" t="inlineStr">
+      <x:c r="D56" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">重新编排故障编号和中文原因</x:t>
         </x:is>
       </x:c>
-      <x:c r="E55" s="18" t="inlineStr">
+      <x:c r="E56" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠按二代设备的部件重新整理故障编号。
 2.⁠补充中文故障原因，日志与屏幕使用相同名称。
 3.⁠删除重复或已被更具体原因替代的故障项。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F55" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="56" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A56" s="33" t="n">
+      <x:c r="F56" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="57" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A57" s="34" t="n">
         <x:v>46216</x:v>
       </x:c>
-      <x:c r="B56" s="13" t="inlineStr">
+      <x:c r="B57" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.24.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C56" s="13" t="inlineStr">
+      <x:c r="C57" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.22.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D56" s="14" t="inlineStr">
+      <x:c r="D57" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增安全传感器支持并兼容旧类型</x:t>
         </x:is>
       </x:c>
-      <x:c r="E56" s="14" t="inlineStr">
+      <x:c r="E57" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增安全传感器的识别、测量和参数读取。
 2.⁠仍可识别原有 DSM 传感器、LTD 传感器（V2 协议）。
 3.⁠传感器不支持某些附加功能时，不再因此阻断原有测量。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F56" s="20" t="inlineStr">
+      <x:c r="F57" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">退回旧程序前，先改回旧程序支持的传感器类型。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="57" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A57" s="34" t="n">
+    <x:row r="58" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A58" s="33" t="n">
         <x:v>46215</x:v>
       </x:c>
-      <x:c r="B57" s="17" t="inlineStr">
+      <x:c r="B58" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.23.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C57" s="17" t="inlineStr">
+      <x:c r="C58" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.22.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D57" s="18" t="inlineStr">
+      <x:c r="D58" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">细分故障原因，支持远程切换协议</x:t>
         </x:is>
       </x:c>
-      <x:c r="E57" s="18" t="inlineStr">
+      <x:c r="E58" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠故障原因分类更细，方便区分电机、传感器、存储和电流输出问题。
 2.⁠减少同一故障反复刷日志。
 3.⁠可由外部设备切换通信协议，保存失败会提示并恢复原设置。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F57" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="58" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A58" s="33" t="n">
+      <x:c r="F58" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="59" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A59" s="34" t="n">
         <x:v>46214</x:v>
       </x:c>
-      <x:c r="B58" s="13" t="inlineStr">
+      <x:c r="B59" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.22.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C58" s="13" t="inlineStr">
+      <x:c r="C59" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.21.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D58" s="14" t="inlineStr">
+      <x:c r="D59" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">支持通过LTD通信接口查询数据和设置参数</x:t>
         </x:is>
       </x:c>
-      <x:c r="E58" s="14" t="inlineStr">
+      <x:c r="E59" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠LTD 通信接口可以查询测量数据、读取和修改参数。
 2.⁠主控确认接收参数后，才回复修改成功。
@@ -3072,32 +3094,32 @@
 4.⁠新增停止、版本、状态和故障查询命令。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F58" s="20" t="inlineStr">
+      <x:c r="F59" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">原设置为 LTD 通信协议的端口，升级后会开始回复数据；需核对连接设备设置。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="59" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A59" s="34" t="n">
+    <x:row r="60" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A60" s="33" t="n">
         <x:v>46213</x:v>
       </x:c>
-      <x:c r="B59" s="17" t="inlineStr">
+      <x:c r="B60" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.21.6.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C59" s="17" t="inlineStr">
+      <x:c r="C60" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.20.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D59" s="18" t="inlineStr">
+      <x:c r="D60" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复上电通信等待和操作误报成功</x:t>
         </x:is>
       </x:c>
-      <x:c r="E59" s="18" t="inlineStr">
+      <x:c r="E60" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复蓝牙持续收数据时，设备上电一直等待的问题。
 2.⁠修复传感器低电压回复被误认成编号错误的问题。
@@ -3105,69 +3127,38 @@
 4.⁠通信恢复后重新读取设备数据，避免显示断线前的旧数据。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F59" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="60" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A60" s="33" t="n">
+      <x:c r="F60" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="61" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A61" s="34" t="n">
         <x:v>46211</x:v>
       </x:c>
-      <x:c r="B60" s="13" t="inlineStr">
+      <x:c r="B61" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.21.5.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C60" s="13" t="inlineStr">
+      <x:c r="C61" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.19.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D60" s="14" t="inlineStr">
+      <x:c r="D61" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">电流环重接后自动恢复输出</x:t>
         </x:is>
       </x:c>
-      <x:c r="E60" s="14" t="inlineStr">
+      <x:c r="E61" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠电流环断开后重新接上，设备会定期尝试恢复输出。
 2.⁠恢复成功后回到有效目标电流，不再继续输出故障电流。
 3.⁠电流输出故障单独记录，不再由后台检查直接中断整机测量。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F60" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="61" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A61" s="34" t="n">
-        <x:v>46211</x:v>
-      </x:c>
-      <x:c r="B61" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.21.4.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C61" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.19.1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D61" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">修复长距离运行时探头越来越慢</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E61" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠修复编码轮方式下，探头长距离分段运行后越来越慢的问题。
-2.⁠修改速度、恢复速度和切换慢速时，也使用正确的尺带长度。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F61" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -3180,115 +3171,146 @@
       </x:c>
       <x:c r="B62" s="13" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.21.4.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C62" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.19.1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D62" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">修复长距离运行时探头越来越慢</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E62" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠修复编码轮方式下，探头长距离分段运行后越来越慢的问题。
+2.⁠修改速度、恢复速度和切换慢速时，也使用正确的尺带长度。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F62" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="63" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A63" s="34" t="n">
+        <x:v>46211</x:v>
+      </x:c>
+      <x:c r="B63" s="17" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.21.3.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C62" s="13" t="inlineStr">
+      <x:c r="C63" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.19.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D62" s="14" t="inlineStr">
+      <x:c r="D63" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">减少液位短时波动引起的反复动作</x:t>
         </x:is>
       </x:c>
-      <x:c r="E62" s="14" t="inlineStr">
+      <x:c r="E63" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠方式 0/1 等液位变化持续一段时间后再动作，减少短时波动影响。
 2.⁠重新找液位期间，屏幕仍显示跟随状态。
 3.⁠调整固定频率找液位方式（方式5）的运行方法。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F62" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="63" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A63" s="34" t="n">
+      <x:c r="F63" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="64" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A64" s="33" t="n">
         <x:v>46209</x:v>
       </x:c>
-      <x:c r="B63" s="17" t="inlineStr">
+      <x:c r="B64" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.21.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C63" s="17" t="inlineStr">
+      <x:c r="C64" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.19.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D63" s="18" t="inlineStr">
+      <x:c r="D64" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SI分布测量完成后自动返回液位跟随</x:t>
         </x:is>
       </x:c>
-      <x:c r="E63" s="18" t="inlineStr">
+      <x:c r="E64" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠SI 分布测量成功后，自动找液位并继续跟随。
 2.⁠测量中途收到新操作时，优先执行新操作。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F63" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="64" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A64" s="33" t="n">
+      <x:c r="F64" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="65" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A65" s="34" t="n">
         <x:v>46205</x:v>
       </x:c>
-      <x:c r="B64" s="13" t="inlineStr">
+      <x:c r="B65" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.21.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C64" s="13" t="inlineStr">
+      <x:c r="C65" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.19.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D64" s="14" t="inlineStr">
+      <x:c r="D65" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修正SI分布测量的测点位置和空气点判断</x:t>
         </x:is>
       </x:c>
-      <x:c r="E64" s="14" t="inlineStr">
+      <x:c r="E65" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复 SI 分布测量第一个测点的位置多加了一次罐底位置的问题。
 2.⁠后续测点按实际位置上报。
 3.⁠调整空气点的判断顺序，减少误报。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F64" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="65" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A65" s="34" t="n">
+      <x:c r="F65" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="66" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A66" s="33" t="n">
         <x:v>46204</x:v>
       </x:c>
-      <x:c r="B65" s="17" t="inlineStr">
+      <x:c r="B66" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.21.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C65" s="17" t="inlineStr">
+      <x:c r="C66" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.19.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D65" s="18" t="inlineStr">
+      <x:c r="D66" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增独立SI分布测量及自动测量</x:t>
         </x:is>
       </x:c>
-      <x:c r="E65" s="18" t="inlineStr">
+      <x:c r="E66" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增独立的 SI 分布测量，可设置第一个测点的位置、测点间距、停留时间和探底频次。
 2.⁠增加自动分布测量设置，最多测 200 点。
@@ -3296,96 +3318,96 @@
 4.⁠取消测量后，不把只测了一部分的结果显示为完成。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F65" s="19" t="inlineStr">
+      <x:c r="F66" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SI 接口读到 -200.00 ℃ 或密度 0，表示暂无有效读数，不能当作实测值。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="66" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A66" s="33" t="n">
+    <x:row r="67" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A67" s="34" t="n">
         <x:v>46204</x:v>
       </x:c>
-      <x:c r="B66" s="13" t="inlineStr">
+      <x:c r="B67" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.20.3.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C66" s="13" t="inlineStr">
+      <x:c r="C67" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.18.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D66" s="14" t="inlineStr">
+      <x:c r="D67" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">编码器通信失败后自动重试</x:t>
         </x:is>
       </x:c>
-      <x:c r="E66" s="14" t="inlineStr">
+      <x:c r="E67" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠编码器通信前几次失败时立即重试。
 2.⁠持续异常不再重复刷日志，但仍继续尝试读取，便于恢复。
 3.⁠取得正常位置后及时使用，减少上电等待。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F66" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="67" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A67" s="34" t="n">
+      <x:c r="F67" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="68" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A68" s="33" t="n">
         <x:v>46202</x:v>
       </x:c>
-      <x:c r="B67" s="17" t="inlineStr">
+      <x:c r="B68" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.20.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C67" s="17" t="inlineStr">
+      <x:c r="C68" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.18.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D67" s="18" t="inlineStr">
+      <x:c r="D68" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">减少上电编码器误报和蓝牙识别失败</x:t>
         </x:is>
       </x:c>
-      <x:c r="E67" s="18" t="inlineStr">
+      <x:c r="E68" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠减少编码器刚上电未稳定时的误报。
 2.⁠过滤传感器上电时的干扰内容，减少蓝牙识别失败。
 3.⁠增加故障记录，方便区分不同的通信问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F67" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="68" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A68" s="33" t="n">
+      <x:c r="F68" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="69" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A69" s="34" t="n">
         <x:v>46200</x:v>
       </x:c>
-      <x:c r="B68" s="13" t="inlineStr">
+      <x:c r="B69" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.20.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C68" s="13" t="inlineStr">
+      <x:c r="C69" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.18.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D68" s="14" t="inlineStr">
+      <x:c r="D69" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修正测点等待时间和菜单返回</x:t>
         </x:is>
       </x:c>
-      <x:c r="E68" s="14" t="inlineStr">
+      <x:c r="E69" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复分布测量每点停留时间的单位错误，按设置的秒数等待。
 2.⁠普通菜单 120 秒无操作，自动回到状态页。
@@ -3393,64 +3415,64 @@
 4.⁠参数日志可以查看修改前后的差别。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F68" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="69" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A69" s="34" t="n">
+      <x:c r="F69" s="21" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="70" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A70" s="33" t="n">
         <x:v>46199</x:v>
       </x:c>
-      <x:c r="B69" s="17" t="inlineStr">
+      <x:c r="B70" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.20.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C69" s="17" t="inlineStr">
+      <x:c r="C70" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.18.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D69" s="18" t="inlineStr">
+      <x:c r="D70" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">密度显示两位小数，保留频率判断的小数</x:t>
         </x:is>
       </x:c>
-      <x:c r="E69" s="18" t="inlineStr">
+      <x:c r="E70" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠密度读数和相关参数统一显示两位小数。
 2.⁠修复判断液位频率变化时丢失小数的问题。
 3.⁠继电器名称统一为 K1～K4，并调整菜单顺序。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F69" s="21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="70" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A70" s="33" t="n">
+      <x:c r="F70" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="71" s="28" customFormat="1" ht="16.5" customHeight="1">
+      <x:c r="A71" s="34" t="n">
         <x:v>46199</x:v>
       </x:c>
-      <x:c r="B70" s="13" t="inlineStr">
+      <x:c r="B71" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.19.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C70" s="13" t="inlineStr">
+      <x:c r="C71" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.17.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D70" s="14" t="inlineStr">
+      <x:c r="D71" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复液位、水位标定多出 0.1 mm</x:t>
         </x:is>
       </x:c>
-      <x:c r="E70" s="14" t="inlineStr">
+      <x:c r="E71" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复液位、水位标定结果固定多出 0.1 mm 的问题。
 2.⁠取消“强制提零点”操作。
@@ -3458,132 +3480,102 @@
 4.⁠统一使用“液位”“扭力”等名称。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F70" s="20" t="inlineStr">
+      <x:c r="F71" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">瓦锡兰通信默认改为波特率 2400、8 位数据、偶校验、1 位停止位；命令 115 不再执行。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="71" s="28" customFormat="1" ht="16.5" customHeight="1">
-      <x:c r="A71" s="34" t="n">
+    <x:row r="72" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A72" s="33" t="n">
         <x:v>46199</x:v>
       </x:c>
-      <x:c r="B71" s="17" t="inlineStr">
+      <x:c r="B72" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.18.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C71" s="17" t="inlineStr">
+      <x:c r="C72" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.16.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D71" s="18" t="inlineStr">
+      <x:c r="D72" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增电流量程与正反向输出设置</x:t>
         </x:is>
       </x:c>
-      <x:c r="E71" s="18" t="inlineStr">
+      <x:c r="E72" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠可以分别设置液位范围和对应电流值。
 2.⁠支持液位升高时电流增加，或电流降低。
 3.⁠电流报警和继电器报警可分别设置。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F71" s="19" t="inlineStr">
+      <x:c r="F72" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">两块板需配套升级；升级后核对电流量程和报警值。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="72" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A72" s="33" t="n">
+    <x:row r="73" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A73" s="34" t="n">
         <x:v>46198</x:v>
       </x:c>
-      <x:c r="B72" s="13" t="inlineStr">
+      <x:c r="B73" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.18.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C72" s="13" t="inlineStr">
+      <x:c r="C73" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.16.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D72" s="14" t="inlineStr">
+      <x:c r="D73" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复继电器读数误判，息屏设置立即生效</x:t>
         </x:is>
       </x:c>
-      <x:c r="E72" s="14" t="inlineStr">
+      <x:c r="E73" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复液位已恢复正常，继电器却仍认为液位无效的问题。
 2.⁠还未测得温度时，不把初始 0 值当作真实温度报警。
 3.⁠息屏开关保存后立即生效，无需重启。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F72" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="73" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A73" s="34" t="n">
+      <x:c r="F73" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="74" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A74" s="33" t="n">
         <x:v>46198</x:v>
       </x:c>
-      <x:c r="B73" s="17" t="inlineStr">
+      <x:c r="B74" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.18.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C73" s="17" t="inlineStr">
+      <x:c r="C74" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.16.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D73" s="18" t="inlineStr">
+      <x:c r="D74" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复标零误报及手动电流测试干扰</x:t>
         </x:is>
       </x:c>
-      <x:c r="E73" s="18" t="inlineStr">
+      <x:c r="E74" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复重新标零时，探头离开零点误报扭力故障的问题。
 2.⁠完善电流测试和故障记录。
 3.⁠修复自动电流更新干扰手动电流测试的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F73" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="74" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A74" s="33" t="n">
-        <x:v>46198</x:v>
-      </x:c>
-      <x:c r="B74" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.17.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C74" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.16.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D74" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">程序说明</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E74" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠补充程序内的中文说明，设备操作和程序版本不变。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F74" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -3592,24 +3584,54 @@
     </x:row>
     <x:row r="75" s="28" customFormat="1" ht="33" customHeight="1">
       <x:c r="A75" s="34" t="n">
+        <x:v>46198</x:v>
+      </x:c>
+      <x:c r="B75" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.17.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C75" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.16.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D75" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">程序说明</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E75" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠补充程序内的中文说明，设备操作和程序版本不变。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F75" s="21" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="76" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A76" s="33" t="n">
         <x:v>46197</x:v>
       </x:c>
-      <x:c r="B75" s="17" t="inlineStr">
+      <x:c r="B76" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.17.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C75" s="17" t="inlineStr">
+      <x:c r="C76" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.16.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D75" s="18" t="inlineStr">
+      <x:c r="D76" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复蓝牙查询后的通信恢复和菜单返回</x:t>
         </x:is>
       </x:c>
-      <x:c r="E75" s="18" t="inlineStr">
+      <x:c r="E76" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠统一检查蓝牙主机、从机的连接状态。
 2.⁠改善查完蓝牙状态后，传感器通信未恢复的问题。
@@ -3617,326 +3639,295 @@
 4.⁠尺带厚度增加常用材料选项和手工输入。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F75" s="21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="76" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A76" s="33" t="n">
+      <x:c r="F76" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="77" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A77" s="34" t="n">
         <x:v>46197</x:v>
       </x:c>
-      <x:c r="B76" s="13" t="inlineStr">
+      <x:c r="B77" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.16.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C76" s="13" t="inlineStr">
+      <x:c r="C77" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.15.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D76" s="14" t="inlineStr">
+      <x:c r="D77" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复探头接近测点时过早停车</x:t>
         </x:is>
       </x:c>
-      <x:c r="E76" s="14" t="inlineStr">
+      <x:c r="E77" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠单点、固定点和分布测点改为先快后慢地接近目标。
 2.⁠修复低速阶段过早停车、未到目标的问题。
 3.⁠瓦锡兰测后回固定点采用同样的定位方法。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F76" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="77" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A77" s="34" t="n">
+      <x:c r="F77" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="78" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A78" s="33" t="n">
         <x:v>46196</x:v>
       </x:c>
-      <x:c r="B77" s="17" t="inlineStr">
+      <x:c r="B78" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.16.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C77" s="17" t="inlineStr">
+      <x:c r="C78" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.15.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D77" s="18" t="inlineStr">
+      <x:c r="D78" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复继电器报警设置保存后数值不对</x:t>
         </x:is>
       </x:c>
-      <x:c r="E77" s="18" t="inlineStr">
+      <x:c r="E78" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复屏幕输入的报警上下限，保存到主控板后数值不正确的问题。
 2.⁠修复报警解除范围等设置保存不正确的问题。
 3.⁠打印参数时补全报警设置，方便核对。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F77" s="19" t="inlineStr">
+      <x:c r="F78" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">曾用旧版设置过继电器报警值的设备，升级后需重新读取并核对。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="78" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A78" s="33" t="n">
+    <x:row r="79" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A79" s="34" t="n">
         <x:v>46191</x:v>
       </x:c>
-      <x:c r="B78" s="13" t="inlineStr">
+      <x:c r="B79" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.16.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C78" s="13" t="inlineStr">
+      <x:c r="C79" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.15.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D78" s="14" t="inlineStr">
+      <x:c r="D79" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复手动通信设置被默认值覆盖</x:t>
         </x:is>
       </x:c>
-      <x:c r="E78" s="14" t="inlineStr">
+      <x:c r="E79" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复手动设置的波特率、校验位等被默认值反复覆盖的问题。
 2.⁠选好通信协议后，可以单独修改串口设置并保存。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F78" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="79" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A79" s="34" t="n">
+      <x:c r="F79" s="21" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="80" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A80" s="33" t="n">
         <x:v>46190</x:v>
       </x:c>
-      <x:c r="B79" s="17" t="inlineStr">
+      <x:c r="B80" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.16.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C79" s="17" t="inlineStr">
+      <x:c r="C80" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.15.0.2</x:t>
         </x:is>
       </x:c>
-      <x:c r="D79" s="18" t="inlineStr">
+      <x:c r="D80" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">可设置日期时间，有电池可断电保留</x:t>
         </x:is>
       </x:c>
-      <x:c r="E79" s="18" t="inlineStr">
+      <x:c r="E80" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增屏幕日期和时间设置。
 2.⁠带时钟电池的显示板可在断电后保留时间。
 3.⁠旧板没有外部时钟时，仍可正常启动。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F79" s="21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="80" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A80" s="33" t="n">
+      <x:c r="F80" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="81" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A81" s="34" t="n">
         <x:v>46190</x:v>
       </x:c>
-      <x:c r="B80" s="13" t="inlineStr">
+      <x:c r="B81" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.16.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C80" s="13" t="inlineStr">
+      <x:c r="C81" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.15.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D80" s="14" t="inlineStr">
+      <x:c r="D81" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">减少屏幕闪烁，修复参数显示异常</x:t>
         </x:is>
       </x:c>
-      <x:c r="E80" s="14" t="inlineStr">
+      <x:c r="E81" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠减少状态页频繁闪烁和读数跳动。
 2.⁠修复参数范围显示异常、输入文字超出屏幕的问题。
 3.⁠罐底检测方式只允许选择有效的两种方式。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F80" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="81" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A81" s="34" t="n">
+      <x:c r="F81" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="82" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A82" s="33" t="n">
         <x:v>46188</x:v>
       </x:c>
-      <x:c r="B81" s="17" t="inlineStr">
+      <x:c r="B82" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.16.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C81" s="17" t="inlineStr">
+      <x:c r="C82" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.15.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D81" s="18" t="inlineStr">
+      <x:c r="D82" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增电流输出开关和状态显示</x:t>
         </x:is>
       </x:c>
-      <x:c r="E81" s="18" t="inlineStr">
+      <x:c r="E82" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增电流输出开关。
 2.⁠屏幕可查看电流输出状态和相关故障。
 3.⁠整理液位对应电流的计算和测试功能。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F81" s="19" t="inlineStr">
+      <x:c r="F82" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">两块板需配套升级；升级后电流输出默认关闭。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="82" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A82" s="33" t="n">
+    <x:row r="83" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A83" s="34" t="n">
         <x:v>46186</x:v>
       </x:c>
-      <x:c r="B82" s="13" t="inlineStr">
+      <x:c r="B83" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.15.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C82" s="13" t="inlineStr">
+      <x:c r="C83" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.14.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D82" s="14" t="inlineStr">
+      <x:c r="D83" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增蓝牙信号显示，调整测量菜单</x:t>
         </x:is>
       </x:c>
-      <x:c r="E82" s="14" t="inlineStr">
+      <x:c r="E83" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠读取部件参数时可以查看蓝牙信号强度。
 2.⁠重新整理测量和探头运动菜单，方便查找。
 3.⁠修复瓦锡兰测量时，把异常频率误当空气点的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F82" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="83" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A83" s="34" t="n">
+      <x:c r="F83" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="84" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A84" s="33" t="n">
         <x:v>46186</x:v>
       </x:c>
-      <x:c r="B83" s="17" t="inlineStr">
+      <x:c r="B84" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.14.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C83" s="17" t="inlineStr">
+      <x:c r="C84" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.13.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D83" s="18" t="inlineStr">
+      <x:c r="D84" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">统一移动目标检查和停车后位置更新</x:t>
         </x:is>
       </x:c>
-      <x:c r="E83" s="18" t="inlineStr">
+      <x:c r="E84" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠统一普通移动和点动的目标位置检查。
 2.⁠统一停车后的位置更新，以及变速后恢复原速度的处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F83" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="84" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A84" s="33" t="n">
+      <x:c r="F84" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="85" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A85" s="34" t="n">
         <x:v>46185</x:v>
       </x:c>
-      <x:c r="B84" s="13" t="inlineStr">
+      <x:c r="B85" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.14.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C84" s="13" t="inlineStr">
+      <x:c r="C85" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.13.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D84" s="14" t="inlineStr">
+      <x:c r="D85" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增三种找液位方式，调整找水位动作</x:t>
         </x:is>
       </x:c>
-      <x:c r="E84" s="14" t="inlineStr">
+      <x:c r="E85" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加三种连续找液位方式：按密度、按相对频率、按固定频率。
 2.⁠屏幕增加相应选项。
 3.⁠找水位时，若探头已在水中，先向上离开水层，再低速向下寻找。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F84" s="20" t="inlineStr">
+      <x:c r="F85" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">两块板需配套升级；方式 3“超声”尚未启用。</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="85" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A85" s="34" t="n">
-        <x:v>46184</x:v>
-      </x:c>
-      <x:c r="B85" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.13.2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C85" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.12.1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D85" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">阻止越界移动和参数错误后的反复重测</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E85" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠普通移动和点动都会先检查目标位置，超出允许范围时不启动。
-2.⁠参数设置错误时，不再反复自动重测。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F85" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -3946,120 +3937,121 @@
       </x:c>
       <x:c r="B86" s="13" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.13.2.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C86" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.12.1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D86" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">阻止越界移动和参数错误后的反复重测</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E86" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠普通移动和点动都会先检查目标位置，超出允许范围时不启动。
+2.⁠参数设置错误时，不再反复自动重测。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F86" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="87" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A87" s="34" t="n">
+        <x:v>46184</x:v>
+      </x:c>
+      <x:c r="B87" s="17" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.13.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C86" s="13" t="inlineStr">
+      <x:c r="C87" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.12.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D86" s="14" t="inlineStr">
+      <x:c r="D87" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修正瓦锡兰空气点判断及失败结果保留</x:t>
         </x:is>
       </x:c>
-      <x:c r="E86" s="14" t="inlineStr">
+      <x:c r="E87" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠调整测点间移动和空气点判断，避免将空气中的读数算入液体结果。
 2.⁠遇到空气点后，重新寻找液面。
 3.⁠本轮测量失败时，保留上次完整结果，避免结果被清零或只剩部分测点。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F86" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="87" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A87" s="34" t="n">
+      <x:c r="F87" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="88" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A88" s="33" t="n">
         <x:v>46184</x:v>
       </x:c>
-      <x:c r="B87" s="17" t="inlineStr">
+      <x:c r="B88" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.13.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C87" s="17" t="inlineStr">
+      <x:c r="C88" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.12.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D87" s="18" t="inlineStr">
+      <x:c r="D88" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复长按确认不灵敏和确认页误跳过</x:t>
         </x:is>
       </x:c>
-      <x:c r="E87" s="18" t="inlineStr">
+      <x:c r="E88" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠改善长按确认不灵敏的问题。
 2.⁠修复先按其他键，再长按确认无法进入菜单的问题。
 3.⁠长按后需松手再确认，避免不小心跳过确认页。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F87" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="88" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A88" s="33" t="n">
+      <x:c r="F88" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="89" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A89" s="34" t="n">
         <x:v>46184</x:v>
       </x:c>
-      <x:c r="B88" s="13" t="inlineStr">
+      <x:c r="B89" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.13.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C88" s="13" t="inlineStr">
+      <x:c r="C89" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.12.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D88" s="14" t="inlineStr">
+      <x:c r="D89" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增五挡亮度，修复显示恢复后的乱码</x:t>
         </x:is>
       </x:c>
-      <x:c r="E88" s="14" t="inlineStr">
+      <x:c r="E89" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增五挡屏幕亮度设置。
 2.⁠修复退出菜单或恢复显示后可能留下乱码的问题。
 3.⁠读数变化时短暂反白显示，方便查看。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F88" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="89" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A89" s="34" t="n">
-        <x:v>46184</x:v>
-      </x:c>
-      <x:c r="B89" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.13.0.1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C89" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.11.2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D89" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">程序整理</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E89" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠整理串口测试程序和编译流程，原有测试命令不变。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F89" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -4072,7 +4064,7 @@
       </x:c>
       <x:c r="B90" s="13" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">V1.13.0.0</x:t>
+          <x:t xml:space="preserve">V1.13.0.1</x:t>
         </x:is>
       </x:c>
       <x:c r="C90" s="13" t="inlineStr">
@@ -4082,13 +4074,12 @@
       </x:c>
       <x:c r="D90" s="14" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">新增长距离与指定位置移动测试</x:t>
+          <x:t xml:space="preserve">程序整理</x:t>
         </x:is>
       </x:c>
       <x:c r="E90" s="14" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.⁠新增长距离移动和移动到指定位置的测试命令。
-2.⁠接近目标时提前减速、停车，停稳后偏差过大会报错。</x:t>
+          <x:t xml:space="preserve">1.⁠整理串口测试程序和编译流程，原有测试命令不变。</x:t>
         </x:is>
       </x:c>
       <x:c r="F90" s="20" t="inlineStr">
@@ -4103,60 +4094,60 @@
       </x:c>
       <x:c r="B91" s="17" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.13.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C91" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.11.2.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D91" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">新增长距离与指定位置移动测试</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E91" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠新增长距离移动和移动到指定位置的测试命令。
+2.⁠接近目标时提前减速、停车，停稳后偏差过大会报错。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F91" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="92" s="28" customFormat="1" ht="16.5" customHeight="1">
+      <x:c r="A92" s="33" t="n">
+        <x:v>46184</x:v>
+      </x:c>
+      <x:c r="B92" s="13" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.12.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C91" s="17" t="inlineStr">
+      <x:c r="C92" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.11.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D91" s="18" t="inlineStr">
+      <x:c r="D92" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">部件参数持续刷新，避免混入旧读数</x:t>
         </x:is>
       </x:c>
-      <x:c r="E91" s="18" t="inlineStr">
+      <x:c r="E92" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠读取完成后，每秒继续更新部件参数，方便观察变化。
 2.⁠屏幕显示本次读数，不再混入其他测量的旧结果。
 3.⁠修正通过 DSM 通信接口读取角度和水电容的结果。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F91" s="19" t="inlineStr">
+      <x:c r="F92" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">旧接口名称“水位传感器电压”实际返回水电容。</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="92" s="28" customFormat="1" ht="16.5" customHeight="1">
-      <x:c r="A92" s="33" t="n">
-        <x:v>46183</x:v>
-      </x:c>
-      <x:c r="B92" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.12.1.3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C92" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.11.1.4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D92" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">恢复磁通量菜单名称并补充选项说明</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E92" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠将“密度修正、温度修正”恢复为“磁通量D、磁通量T”。
-2.⁠补充菜单各选项的含义。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F92" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -4171,15 +4162,46 @@
       </x:c>
       <x:c r="C93" s="17" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.11.1.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D93" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">恢复磁通量菜单名称并补充选项说明</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E93" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠将“密度修正、温度修正”恢复为“磁通量D、磁通量T”。
+2.⁠补充菜单各选项的含义。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F93" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="94" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A94" s="33" t="n">
+        <x:v>46183</x:v>
+      </x:c>
+      <x:c r="B94" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.12.1.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C94" s="13" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.11.1.3</x:t>
         </x:is>
       </x:c>
-      <x:c r="D93" s="18" t="inlineStr">
+      <x:c r="D94" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">调整出厂设置并增加状态页信息</x:t>
         </x:is>
       </x:c>
-      <x:c r="E93" s="18" t="inlineStr">
+      <x:c r="E94" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠调整 9 项出厂默认设置。
 2.⁠读取部件参数后，可同时显示频率、电容等读数。
@@ -4187,71 +4209,41 @@
 4.⁠修正瓦锡兰测量过程中的显示项目。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F93" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="94" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A94" s="33" t="n">
+      <x:c r="F94" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="95" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A95" s="34" t="n">
         <x:v>46182</x:v>
       </x:c>
-      <x:c r="B94" s="13" t="inlineStr">
+      <x:c r="B95" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.12.1.2</x:t>
         </x:is>
       </x:c>
-      <x:c r="C94" s="13" t="inlineStr">
+      <x:c r="C95" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.11.1.2</x:t>
         </x:is>
       </x:c>
-      <x:c r="D94" s="14" t="inlineStr">
+      <x:c r="D95" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复参数显示和大数值保存错误</x:t>
         </x:is>
       </x:c>
-      <x:c r="E94" s="14" t="inlineStr">
+      <x:c r="E95" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠补齐速度、频率、电容等设置的单位。
 2.⁠修正频率小数位和手输密度范围显示。
 3.⁠修复手工输入较大数值后，保存值变小或不完整的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F94" s="20" t="inlineStr">
+      <x:c r="F95" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">升级后显示和通信设置会恢复默认，需重新设置。</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="95" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A95" s="34" t="n">
-        <x:v>46182</x:v>
-      </x:c>
-      <x:c r="B95" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.12.1.2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C95" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.11.1.1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D95" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">报警单位随所选测量项目变化</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E95" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠报警值的单位随所选测量项目变化，位置用 mm，温度用 ℃。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F95" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -4266,18 +4258,17 @@
       </x:c>
       <x:c r="C96" s="13" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">V1.11.1.0</x:t>
+          <x:t xml:space="preserve">V1.11.1.1</x:t>
         </x:is>
       </x:c>
       <x:c r="D96" s="14" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">调整出厂参数，瓦锡兰默认不探底</x:t>
+          <x:t xml:space="preserve">报警单位随所选测量项目变化</x:t>
         </x:is>
       </x:c>
       <x:c r="E96" s="14" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.⁠调整 11 项出厂默认设置，涉及自动回零、扭力、盲区和分布测量等。
-2.⁠瓦锡兰探底间隔默认设为 0，表示不探底。</x:t>
+          <x:t xml:space="preserve">1.⁠报警值的单位随所选测量项目变化，位置用 mm，温度用 ℃。</x:t>
         </x:is>
       </x:c>
       <x:c r="F96" s="15" t="inlineStr">
@@ -4292,7 +4283,7 @@
       </x:c>
       <x:c r="B97" s="17" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">V1.12.1.1</x:t>
+          <x:t xml:space="preserve">V1.12.1.2</x:t>
         </x:is>
       </x:c>
       <x:c r="C97" s="17" t="inlineStr">
@@ -4302,13 +4293,13 @@
       </x:c>
       <x:c r="D97" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">统一程序版本和设备信息显示格式</x:t>
+          <x:t xml:space="preserve">调整出厂参数，瓦锡兰默认不探底</x:t>
         </x:is>
       </x:c>
       <x:c r="E97" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.⁠程序版本统一显示为 Vx.x.x.x，便于报修时记录。
-2.⁠整理设备信息的名称和数字格式，减少显示不全。</x:t>
+          <x:t xml:space="preserve">1.⁠调整 11 项出厂默认设置，涉及自动回零、扭力、盲区和分布测量等。
+2.⁠瓦锡兰探底间隔默认设为 0，表示不探底。</x:t>
         </x:is>
       </x:c>
       <x:c r="F97" s="19" t="inlineStr">
@@ -4328,15 +4319,46 @@
       </x:c>
       <x:c r="C98" s="13" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.11.1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D98" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">统一程序版本和设备信息显示格式</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E98" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠程序版本统一显示为 Vx.x.x.x，便于报修时记录。
+2.⁠整理设备信息的名称和数字格式，减少显示不全。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F98" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="99" s="28" customFormat="1" ht="16.5" customHeight="1">
+      <x:c r="A99" s="34" t="n">
+        <x:v>46182</x:v>
+      </x:c>
+      <x:c r="B99" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.12.1.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C99" s="17" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.11.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D98" s="14" t="inlineStr">
+      <x:c r="D99" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">重新分类菜单并增加关键参数确认</x:t>
         </x:is>
       </x:c>
-      <x:c r="E98" s="14" t="inlineStr">
+      <x:c r="E99" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠按测量、输出、通信、显示和维护重新整理菜单。
 2.⁠修改关键参数前增加确认，减少误操作。
@@ -4344,66 +4366,35 @@
 4.⁠修复状态页混入旧结果和文字超出屏幕的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F98" s="20" t="inlineStr">
+      <x:c r="F99" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">该版本修改通信设置会重新套用默认值。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="99" s="28" customFormat="1" ht="16.5" customHeight="1">
-      <x:c r="A99" s="34" t="n">
+    <x:row r="100" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A100" s="33" t="n">
         <x:v>46182</x:v>
       </x:c>
-      <x:c r="B99" s="17" t="inlineStr">
+      <x:c r="B100" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.12.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C99" s="17" t="inlineStr">
+      <x:c r="C100" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.10.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D99" s="18" t="inlineStr">
+      <x:c r="D100" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复停机等待和旧动作残留</x:t>
         </x:is>
       </x:c>
-      <x:c r="E99" s="18" t="inlineStr">
+      <x:c r="E100" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复电机已停稳，程序却一直等待的问题。
 2.⁠修复重新启动后可能继续跑向旧目标的问题。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F99" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="100" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A100" s="33" t="n">
-        <x:v>46181</x:v>
-      </x:c>
-      <x:c r="B100" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.12.0.2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C100" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.10.1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D100" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">开关和模式改用文字选项设置</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E100" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠开关、模式等设置可用上下键选择文字选项。
-2.⁠进入选择页时，自动选中当前设置。</x:t>
         </x:is>
       </x:c>
       <x:c r="F100" s="20" t="inlineStr">
@@ -4423,51 +4414,52 @@
       </x:c>
       <x:c r="C101" s="17" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.10.1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D101" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">开关和模式改用文字选项设置</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E101" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠开关、模式等设置可用上下键选择文字选项。
+2.⁠进入选择页时，自动选中当前设置。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F101" s="21" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="102" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A102" s="33" t="n">
+        <x:v>46181</x:v>
+      </x:c>
+      <x:c r="B102" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.12.0.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C102" s="13" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.10.0.2</x:t>
         </x:is>
       </x:c>
-      <x:c r="D101" s="18" t="inlineStr">
+      <x:c r="D102" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">电机通信失败时不再误判已停车</x:t>
         </x:is>
       </x:c>
-      <x:c r="E101" s="18" t="inlineStr">
+      <x:c r="E102" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复读不到电机状态时，被误认为电机已停止的问题。
 2.⁠电机通信失败时保留具体故障原因。
 3.⁠统一继电器报警菜单名称。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F101" s="21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="102" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A102" s="33" t="n">
-        <x:v>46179</x:v>
-      </x:c>
-      <x:c r="B102" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.12.0.1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C102" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.10.0.1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D102" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">程序整理</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E102" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠删除未使用的旧程序，正常测量、显示和通信功能不变。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F102" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -4480,20 +4472,50 @@
       </x:c>
       <x:c r="B103" s="17" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.12.0.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C103" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.10.0.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D103" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">程序整理</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E103" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠删除未使用的旧程序，正常测量、显示和通信功能不变。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F103" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="104" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A104" s="33" t="n">
+        <x:v>46179</x:v>
+      </x:c>
+      <x:c r="B104" s="13" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.12.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C103" s="17" t="inlineStr">
+      <x:c r="C104" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.10.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D103" s="18" t="inlineStr">
+      <x:c r="D104" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增四路继电器报警设置</x:t>
         </x:is>
       </x:c>
-      <x:c r="E103" s="18" t="inlineStr">
+      <x:c r="E104" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增四路继电器报警设置，屏幕可设置报警来源及上下限。
 2.⁠支持设置报警解除条件和接点形式。
@@ -4501,94 +4523,94 @@
 4.⁠原继电器报警设置改为新的继电器菜单。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F103" s="19" t="inlineStr">
+      <x:c r="F104" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">从 CPU2 V1.11.0.1 及更早版本升级会恢复出厂参数，升级前必须备份。第四路继电器需确认实际硬件是否支持。</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="104" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A104" s="33" t="n">
-        <x:v>46179</x:v>
-      </x:c>
-      <x:c r="B104" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.11.0.1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C104" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.9.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D104" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">程序整理</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E104" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠整理程序文件，方便研发维护，设备操作不变。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F104" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="105" s="28" customFormat="1" ht="33" customHeight="1">
       <x:c r="A105" s="34" t="n">
+        <x:v>46179</x:v>
+      </x:c>
+      <x:c r="B105" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.11.0.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C105" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.9.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D105" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">程序整理</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E105" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠整理程序文件，方便研发维护，设备操作不变。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F105" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="106" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A106" s="33" t="n">
         <x:v>46177</x:v>
       </x:c>
-      <x:c r="B105" s="17" t="inlineStr">
+      <x:c r="B106" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.11.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C105" s="17" t="inlineStr">
+      <x:c r="C106" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.9.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D105" s="18" t="inlineStr">
+      <x:c r="D106" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">往返测试可调速，改善复位后的启动</x:t>
         </x:is>
       </x:c>
-      <x:c r="E105" s="18" t="inlineStr">
+      <x:c r="E106" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠电机往返测试（BE）可以设置速度和加减速快慢。
 2.⁠修复往返测试范围逐次向下移动的问题。
 3.⁠改善电机断电、复位后一直提示“电机被禁止”的情况。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F105" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="106" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A106" s="33" t="n">
+      <x:c r="F106" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="107" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A107" s="34" t="n">
         <x:v>46176</x:v>
       </x:c>
-      <x:c r="B106" s="13" t="inlineStr">
+      <x:c r="B107" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.10.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C106" s="13" t="inlineStr">
+      <x:c r="C107" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.9.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D106" s="14" t="inlineStr">
+      <x:c r="D107" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">清除上电旧动作，可设置自动恢复次数</x:t>
         </x:is>
       </x:c>
-      <x:c r="E106" s="14" t="inlineStr">
+      <x:c r="E107" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠上电先清除上次遗留的运动，避免继续执行旧动作。
 2.⁠位置尚未确定时，不启动普通运动。
@@ -4596,37 +4618,6 @@
 4.⁠修复负空载扭力显示为异常大数的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F106" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="107" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A107" s="34" t="n">
-        <x:v>46175</x:v>
-      </x:c>
-      <x:c r="B107" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.9.1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C107" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.8.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D107" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">测量前拦截超出允许范围的目标位置</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E107" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠测量前先检查目标位置，超出零点或进入罐底盲区时，不再让探头继续移动。
-2.⁠瓦锡兰测后回固定点也会检查目标位置。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F107" s="21" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -4639,211 +4630,242 @@
       </x:c>
       <x:c r="B108" s="13" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.9.1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C108" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.8.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D108" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">测量前拦截超出允许范围的目标位置</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E108" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠测量前先检查目标位置，超出零点或进入罐底盲区时，不再让探头继续移动。
+2.⁠瓦锡兰测后回固定点也会检查目标位置。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F108" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="109" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A109" s="34" t="n">
+        <x:v>46175</x:v>
+      </x:c>
+      <x:c r="B109" s="17" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.9.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C108" s="13" t="inlineStr">
+      <x:c r="C109" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.8.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D108" s="14" t="inlineStr">
+      <x:c r="D109" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">适配 DSM V1.228通信协议与查询</x:t>
         </x:is>
       </x:c>
-      <x:c r="E108" s="14" t="inlineStr">
+      <x:c r="E109" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加与 DSM V1.228 对外通信协议的兼容。
 2.⁠修正设备状态、命令及参数查询的返回内容。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F108" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="109" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A109" s="34" t="n">
+      <x:c r="F109" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="110" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A110" s="33" t="n">
         <x:v>46165</x:v>
       </x:c>
-      <x:c r="B109" s="17" t="inlineStr">
+      <x:c r="B110" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.9.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C109" s="17" t="inlineStr">
+      <x:c r="C110" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.7.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D109" s="18" t="inlineStr">
+      <x:c r="D110" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增屏幕无线滑环匹配操作</x:t>
         </x:is>
       </x:c>
-      <x:c r="E109" s="18" t="inlineStr">
+      <x:c r="E110" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠屏幕新增“匹配无线滑环”，可自动选择附近信号较强的设备。
 2.⁠显示匹配进度、结果和连接设备地址。
 3.⁠增加匹配条件，减少连接到其他设备的情况。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F109" s="19" t="inlineStr">
+      <x:c r="F110" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">该版本固定点监测使用模拟数据，不能作为现场实测值。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="110" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A110" s="33" t="n">
+    <x:row r="111" s="28" customFormat="1" ht="82.5" customHeight="1">
+      <x:c r="A111" s="34" t="n">
         <x:v>46165</x:v>
       </x:c>
-      <x:c r="B110" s="13" t="inlineStr">
+      <x:c r="B111" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.8.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C110" s="13" t="inlineStr">
+      <x:c r="C111" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.6.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D110" s="14" t="inlineStr">
+      <x:c r="D111" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复往返测试启动和换向误判</x:t>
         </x:is>
       </x:c>
-      <x:c r="E110" s="14" t="inlineStr">
+      <x:c r="E111" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠调整电机运行和往返测试（B/BE），减少旧故障状态对测试启动的影响。
 2.⁠修复电机换向瞬间被误判已停稳的问题。
 3.⁠测试时按实际传感器类型检查通信。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F110" s="20" t="inlineStr">
+      <x:c r="F111" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">往返测试为调试功能，不能替代正常测量。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="111" s="28" customFormat="1" ht="82.5" customHeight="1">
-      <x:c r="A111" s="34" t="n">
+    <x:row r="112" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A112" s="33" t="n">
         <x:v>46158</x:v>
       </x:c>
-      <x:c r="B111" s="17" t="inlineStr">
+      <x:c r="B112" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.8.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C111" s="17" t="inlineStr">
+      <x:c r="C112" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.6.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D111" s="18" t="inlineStr">
+      <x:c r="D112" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增SI通信接口及测量结果查询</x:t>
         </x:is>
       </x:c>
-      <x:c r="E111" s="18" t="inlineStr">
+      <x:c r="E112" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增 SI 通信接口，可读取结果、完成时间和设备状态。
 2.⁠不支持的命令不再回复成功。
 3.⁠修复读取分布结果时带入上一次测点的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F111" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="112" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A112" s="33" t="n">
+      <x:c r="F112" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="113" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A113" s="34" t="n">
         <x:v>46161</x:v>
       </x:c>
-      <x:c r="B112" s="13" t="inlineStr">
+      <x:c r="B113" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.7.3.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C112" s="13" t="inlineStr">
+      <x:c r="C113" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.5.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D112" s="14" t="inlineStr">
+      <x:c r="D113" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加探底超程停机，修复回零碰撞误报</x:t>
         </x:is>
       </x:c>
-      <x:c r="E112" s="14" t="inlineStr">
+      <x:c r="E113" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠探底超过允许下行长度仍未找到罐底时，停机并报错。
 2.⁠接近罐底时降低速度。
 3.⁠修复正常到达零点时误报碰撞的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F112" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="113" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A113" s="34" t="n">
+      <x:c r="F113" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="114" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A114" s="33" t="n">
         <x:v>46158</x:v>
       </x:c>
-      <x:c r="B113" s="17" t="inlineStr">
+      <x:c r="B114" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.7.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C113" s="17" t="inlineStr">
+      <x:c r="C114" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.5.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D113" s="18" t="inlineStr">
+      <x:c r="D114" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">液位校正后立即刷新，修复负数显示</x:t>
         </x:is>
       </x:c>
-      <x:c r="E113" s="18" t="inlineStr">
+      <x:c r="E114" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修正液位后，立即更新液位和探头位置。
 2.⁠修复负数位置或读数变成异常大数的问题。
 3.⁠瓦锡兰测后回固定点最多尝试 3 次，失败后跳过探底并转回固定点监测。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F113" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="114" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A114" s="33" t="n">
+      <x:c r="F114" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="115" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A115" s="34" t="n">
         <x:v>46158</x:v>
       </x:c>
-      <x:c r="B114" s="13" t="inlineStr">
+      <x:c r="B115" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.7.1.2</x:t>
         </x:is>
       </x:c>
-      <x:c r="C114" s="13" t="inlineStr">
+      <x:c r="C115" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.5.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D114" s="14" t="inlineStr">
+      <x:c r="D115" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复传感器切换及探头离底时的误报</x:t>
         </x:is>
       </x:c>
-      <x:c r="E114" s="14" t="inlineStr">
+      <x:c r="E115" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复 LTD 传感器（V2 协议）切换模式、读取部件参数时误报 13-13 的问题。
 2.⁠修正 DSM 传感器电压过低的提示。
@@ -4851,37 +4873,6 @@
 4.⁠减少探头离底时误报扭力故障的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F114" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="115" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A115" s="34" t="n">
-        <x:v>46157</x:v>
-      </x:c>
-      <x:c r="B115" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.7.1.1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C115" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.5.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D115" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">故障后自动重测最多3 次</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E115" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠同一次测量自动恢复后，最多重新测量 3 次。
-2.⁠达到上限后保持故障，避免一直重复测量。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F115" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -4894,7 +4885,7 @@
       </x:c>
       <x:c r="B116" s="13" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">V1.7.1.0</x:t>
+          <x:t xml:space="preserve">V1.7.1.1</x:t>
         </x:is>
       </x:c>
       <x:c r="C116" s="13" t="inlineStr">
@@ -4904,13 +4895,13 @@
       </x:c>
       <x:c r="D116" s="14" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">减少罐底误判和探头离底时的碰撞误报</x:t>
+          <x:t xml:space="preserve">故障后自动重测最多3 次</x:t>
         </x:is>
       </x:c>
       <x:c r="E116" s="14" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.⁠找罐底前先确认探头已离开罐底，避免一开始就误判找到。
-2.⁠减少探头离开罐底时误报扭力碰撞的问题。</x:t>
+          <x:t xml:space="preserve">1.⁠同一次测量自动恢复后，最多重新测量 3 次。
+2.⁠达到上限后保持故障，避免一直重复测量。</x:t>
         </x:is>
       </x:c>
       <x:c r="F116" s="20" t="inlineStr">
@@ -4925,179 +4916,210 @@
       </x:c>
       <x:c r="B117" s="17" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.7.1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C117" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.5.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D117" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">减少罐底误判和探头离底时的碰撞误报</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E117" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠找罐底前先确认探头已离开罐底，避免一开始就误判找到。
+2.⁠减少探头离开罐底时误报扭力碰撞的问题。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F117" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="118" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A118" s="33" t="n">
+        <x:v>46157</x:v>
+      </x:c>
+      <x:c r="B118" s="13" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.7.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C117" s="17" t="inlineStr">
+      <x:c r="C118" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.5.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D117" s="18" t="inlineStr">
+      <x:c r="D118" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增探底修正罐高与位置校正</x:t>
         </x:is>
       </x:c>
-      <x:c r="E117" s="18" t="inlineStr">
+      <x:c r="E118" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增“探底修正罐高”，用于探底后校正探头位置。
 2.⁠测得的罐高偏差过大时，不进行位置校正。
 3.⁠调整瓦锡兰测量结束后回固定点及探底的先后过程。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F117" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="118" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A118" s="33" t="n">
+      <x:c r="F118" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="119" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A119" s="34" t="n">
         <x:v>46157</x:v>
       </x:c>
-      <x:c r="B118" s="13" t="inlineStr">
+      <x:c r="B119" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.6.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C118" s="13" t="inlineStr">
+      <x:c r="C119" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.4.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D118" s="14" t="inlineStr">
+      <x:c r="D119" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增长按返回停止测量和查看故障</x:t>
         </x:is>
       </x:c>
-      <x:c r="E118" s="14" t="inlineStr">
+      <x:c r="E119" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠状态页长按返回键，再确认，可以停止测量并回到待机。
 2.⁠停止测量时，同时取消自动恢复。
 3.⁠故障时长按返回键，可以查看原因。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F118" s="20" t="inlineStr">
+      <x:c r="F119" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">两块板需配套升级；旧主控程序不支持新增停止命令。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="119" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A119" s="34" t="n">
+    <x:row r="120" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A120" s="33" t="n">
         <x:v>46157</x:v>
       </x:c>
-      <x:c r="B119" s="17" t="inlineStr">
+      <x:c r="B120" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.5.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C119" s="17" t="inlineStr">
+      <x:c r="C120" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.3.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D119" s="18" t="inlineStr">
+      <x:c r="D120" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">拦截错误传感器数据，修复回零误报</x:t>
         </x:is>
       </x:c>
-      <x:c r="E119" s="18" t="inlineStr">
+      <x:c r="E120" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠收到不完整或错误的传感器数据时，不再当成正常读数。
 2.⁠新增传感器通信测试（SC），方便检查传感器连接。
 3.⁠修复 LTD 传感器（V2 协议）回零时，因不支持某些附加功能而误报故障的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F119" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="120" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A120" s="33" t="n">
+      <x:c r="F120" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="121" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A121" s="34" t="n">
         <x:v>46157</x:v>
       </x:c>
-      <x:c r="B120" s="13" t="inlineStr">
+      <x:c r="B121" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.5.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C120" s="13" t="inlineStr">
+      <x:c r="C121" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.3.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D120" s="14" t="inlineStr">
+      <x:c r="D121" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">屏幕新增中文故障原因显示</x:t>
         </x:is>
       </x:c>
-      <x:c r="E120" s="14" t="inlineStr">
+      <x:c r="E121" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠屏幕除了故障编号，还能显示中文原因。
 2.⁠较长的原因会分行显示，并补齐缺失文字。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F120" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="121" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A121" s="34" t="n">
+      <x:c r="F121" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="122" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A122" s="33" t="n">
         <x:v>46156</x:v>
       </x:c>
-      <x:c r="B121" s="17" t="inlineStr">
+      <x:c r="B122" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.5.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C121" s="17" t="inlineStr">
+      <x:c r="C122" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.2.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D121" s="18" t="inlineStr">
+      <x:c r="D122" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">分布测量由 100 点增加到 200 点</x:t>
         </x:is>
       </x:c>
-      <x:c r="E121" s="18" t="inlineStr">
+      <x:c r="E122" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠分布测量最多可测 200 点，原来最多 100 点。
 2.⁠屏幕可设置 200 点，瓦锡兰系统也可读取新增测点。
 3.⁠状态页增加两块板通信不匹配的提示。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F121" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="122" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A122" s="33" t="n">
+      <x:c r="F122" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="123" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A123" s="34" t="n">
         <x:v>46156</x:v>
       </x:c>
-      <x:c r="B122" s="13" t="inlineStr">
+      <x:c r="B123" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.4.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C122" s="13" t="inlineStr">
+      <x:c r="C123" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.1.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D122" s="14" t="inlineStr">
+      <x:c r="D123" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">切换操作及时响应，修复误报与漏报</x:t>
         </x:is>
       </x:c>
-      <x:c r="E122" s="14" t="inlineStr">
+      <x:c r="E123" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠等待读数稳定时，也能响应新的操作命令。
 2.⁠正常切换操作不再被误记为故障。
@@ -5105,100 +5127,69 @@
 4.⁠修复固定点密度读取失败却没有报错的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F122" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="123" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A123" s="34" t="n">
+      <x:c r="F123" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="124" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A124" s="33" t="n">
         <x:v>46155</x:v>
       </x:c>
-      <x:c r="B123" s="17" t="inlineStr">
+      <x:c r="B124" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.4.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C123" s="17" t="inlineStr">
+      <x:c r="C124" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.1.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D123" s="18" t="inlineStr">
+      <x:c r="D124" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">日志区分重试过程与最终故障</x:t>
         </x:is>
       </x:c>
-      <x:c r="E123" s="18" t="inlineStr">
+      <x:c r="E124" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠日志会分开显示正在重试、重试成功和最终故障。
 2.⁠修复实际故障原因被笼统的“失败”提示盖住的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F123" s="19" t="inlineStr">
+      <x:c r="F124" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">日志中的“重试”不代表设备最终报故障。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="124" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A124" s="33" t="n">
+    <x:row r="125" s="28" customFormat="1" ht="16.5" customHeight="1">
+      <x:c r="A125" s="34" t="n">
         <x:v>46154</x:v>
       </x:c>
-      <x:c r="B124" s="13" t="inlineStr">
+      <x:c r="B125" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.3.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C124" s="13" t="inlineStr">
+      <x:c r="C125" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.1.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D124" s="14" t="inlineStr">
+      <x:c r="D125" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">测量失败后自动检查并尝试恢复</x:t>
         </x:is>
       </x:c>
-      <x:c r="E124" s="14" t="inlineStr">
+      <x:c r="E125" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠测量失败后自动检查各部件，恢复正常后再重新测量。
 2.⁠传感器通信失败后会重新尝试。
 3.⁠完善电机驱动复位后重新启动的处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F124" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="125" s="28" customFormat="1" ht="16.5" customHeight="1">
-      <x:c r="A125" s="34" t="n">
-        <x:v>46153</x:v>
-      </x:c>
-      <x:c r="B125" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.2.1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C125" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.1.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D125" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">液位信号变化后重新找液面并跟随</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E125" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠液位信号变化后，设备会重新找液面，找到后继续跟随。
-2.⁠连续读到异常频率时，会尝试切换测量模式恢复读数。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F125" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -5211,7 +5202,7 @@
       </x:c>
       <x:c r="B126" s="13" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">V1.2.0.0</x:t>
+          <x:t xml:space="preserve">V1.2.1.0</x:t>
         </x:is>
       </x:c>
       <x:c r="C126" s="13" t="inlineStr">
@@ -5221,13 +5212,13 @@
       </x:c>
       <x:c r="D126" s="14" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">新增电机往返运行测试</x:t>
+          <x:t xml:space="preserve">液位信号变化后重新找液面并跟随</x:t>
         </x:is>
       </x:c>
       <x:c r="E126" s="14" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.⁠新增电机往返测试（BE），可让电机在两个固定位置之间往返，方便检查运行距离。
-2.⁠修复新调试命令带入上一条命令内容的问题。</x:t>
+          <x:t xml:space="preserve">1.⁠液位信号变化后，设备会重新找液面，找到后继续跟随。
+2.⁠连续读到异常频率时，会尝试切换测量模式恢复读数。</x:t>
         </x:is>
       </x:c>
       <x:c r="F126" s="15" t="inlineStr">
@@ -5242,59 +5233,60 @@
       </x:c>
       <x:c r="B127" s="23" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.2.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C127" s="23" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.1.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C127" s="23" t="inlineStr">
+      <x:c r="D127" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">新增电机往返运行测试</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E127" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠新增电机往返测试（BE），可让电机在两个固定位置之间往返，方便检查运行距离。
+2.⁠修复新调试命令带入上一条命令内容的问题。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F127" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="128" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A128" s="36" t="n">
+        <x:v>46153</x:v>
+      </x:c>
+      <x:c r="B128" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.1.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D127" s="23" t="inlineStr">
+      <x:c r="C128" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.1.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D128" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">屏幕显示两板版本并提示不匹配</x:t>
         </x:is>
       </x:c>
-      <x:c r="E127" s="23" t="inlineStr">
+      <x:c r="E128" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠屏幕可以查看主控板和显示板的程序版本。
 2.⁠两块板程序不匹配时，屏幕会提示。
 3.⁠修复升级后仍显示旧程序版本的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F127" s="23" t="inlineStr">
+      <x:c r="F128" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">升级时使用配套程序包。</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="128" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A128" s="36" t="n">
-        <x:v>46153</x:v>
-      </x:c>
-      <x:c r="B128" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.0.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C128" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.0.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D128" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">主控板和显示板增加程序版本号</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E128" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠主控板、显示板都有程序版本号，方便确认设备用的程序。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F128" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">无版本号设备升级前先记录现场参数。</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -5304,377 +5296,376 @@
       </x:c>
       <x:c r="B129" s="23" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.0.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C129" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.0.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D129" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">主控板和显示板增加程序版本号</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E129" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠主控板、显示板都有程序版本号，方便确认设备用的程序。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F129" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">无版本号设备升级前先记录现场参数。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="130" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A130" s="36" t="n">
+        <x:v>46153</x:v>
+      </x:c>
+      <x:c r="B130" s="25" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V0.31.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C129" s="23" t="inlineStr">
+      <x:c r="C130" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.28.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D129" s="23" t="inlineStr">
+      <x:c r="D130" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">统一水位电容参数和跟随状态</x:t>
         </x:is>
       </x:c>
-      <x:c r="E129" s="23" t="inlineStr">
+      <x:c r="E130" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠统一主控板、显示板的水位寻找阈值和滞后阈值名称。
 2.⁠进入持续监测后才确认水位跟随状态。
 3.⁠调整等待超时和调试提示。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F129" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="130" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A130" s="36" t="n">
+      <x:c r="F130" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="131" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A131" s="35" t="n">
         <x:v>46151</x:v>
       </x:c>
-      <x:c r="B130" s="25" t="inlineStr">
+      <x:c r="B131" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.31.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C130" s="25" t="inlineStr">
+      <x:c r="C131" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.28.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D130" s="25" t="inlineStr">
+      <x:c r="D131" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加水位变化监测和定期探底</x:t>
         </x:is>
       </x:c>
-      <x:c r="E130" s="25" t="inlineStr">
+      <x:c r="E131" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠水位跟随稳定后继续监测水位变化。
 2.⁠水位寻找阈值和跟随滞后阈值分开设置。
 3.⁠瓦锡兰密度测量可设置每隔若干次重新探底。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F130" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="131" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A131" s="35" t="n">
+      <x:c r="F131" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="132" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A132" s="36" t="n">
         <x:v>46151</x:v>
       </x:c>
-      <x:c r="B131" s="23" t="inlineStr">
+      <x:c r="B132" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.30.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C131" s="23" t="inlineStr">
+      <x:c r="C132" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.27.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D131" s="23" t="inlineStr">
+      <x:c r="D132" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加电机驱动通信测试和状态上报</x:t>
         </x:is>
       </x:c>
-      <x:c r="E131" s="23" t="inlineStr">
+      <x:c r="E132" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加电机驱动芯片（TMC5130）静态通信测试。
 2.⁠电机状态改为由主循环统一刷新。
 3.⁠补充屏幕菜单说明。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F131" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="132" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A132" s="36" t="n">
+      <x:c r="F132" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="133" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A133" s="35" t="n">
         <x:v>46150</x:v>
       </x:c>
-      <x:c r="B132" s="25" t="inlineStr">
+      <x:c r="B133" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.29.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C132" s="25" t="inlineStr">
+      <x:c r="C133" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.26.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D132" s="25" t="inlineStr">
+      <x:c r="D133" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">完善电机测试和驱动故障诊断</x:t>
         </x:is>
       </x:c>
-      <x:c r="E132" s="25" t="inlineStr">
+      <x:c r="E133" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠电机往返测试可设置更多运行参数。
 2.⁠完善电机驱动芯片（TMC5130）的到位确认和故障状态读取。
 3.⁠检测到驱动异常时停机。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F132" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="133" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A133" s="35" t="n">
+      <x:c r="F133" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="134" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A134" s="36" t="n">
         <x:v>46148</x:v>
       </x:c>
-      <x:c r="B133" s="23" t="inlineStr">
+      <x:c r="B134" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.28.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C133" s="23" t="inlineStr">
+      <x:c r="C134" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.26.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D133" s="23" t="inlineStr">
+      <x:c r="D134" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加位置来源切换和屏幕字库</x:t>
         </x:is>
       </x:c>
-      <x:c r="E133" s="23" t="inlineStr">
+      <x:c r="E134" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加电机位置来源自动切换。
 2.⁠增加找罐底后的编码器位置修正和失步检测设置。
 3.⁠显示板补齐新增菜单所需中文字。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F133" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="134" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A134" s="36" t="n">
+      <x:c r="F134" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="135" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A135" s="35" t="n">
         <x:v>46142</x:v>
       </x:c>
-      <x:c r="B134" s="25" t="inlineStr">
+      <x:c r="B135" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.27.3.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C134" s="25" t="inlineStr">
+      <x:c r="C135" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.25.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D134" s="25" t="inlineStr">
+      <x:c r="D135" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复回零和记步状态</x:t>
         </x:is>
       </x:c>
-      <x:c r="E134" s="25" t="inlineStr">
+      <x:c r="E135" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修正粗找零点、精找零点和停稳判断。
 2.⁠修正回零过程中的速度更新。
 3.⁠回零后清除旧的记步基准并更新参数校验。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F134" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="135" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A135" s="35" t="n">
+      <x:c r="F135" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="136" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A136" s="36" t="n">
         <x:v>46141</x:v>
       </x:c>
-      <x:c r="B135" s="23" t="inlineStr">
+      <x:c r="B136" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.27.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C135" s="23" t="inlineStr">
+      <x:c r="C136" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.25.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D135" s="23" t="inlineStr">
+      <x:c r="D136" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">加强电机位置读数保护</x:t>
         </x:is>
       </x:c>
-      <x:c r="E135" s="23" t="inlineStr">
+      <x:c r="E136" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠拆分电机驱动设置、运动控制和位置换算。
 2.⁠电机驱动芯片（TMC5130）位置读数增加稳定检查。
 3.⁠位置写入失败时不采用错误结果，并调整回零减速。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F135" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="136" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A136" s="36" t="n">
+      <x:c r="F136" s="26" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="137" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A137" s="35" t="n">
         <x:v>46140</x:v>
       </x:c>
-      <x:c r="B136" s="25" t="inlineStr">
+      <x:c r="B137" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.27.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C136" s="25" t="inlineStr">
+      <x:c r="C137" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.25.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D136" s="25" t="inlineStr">
+      <x:c r="D137" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复电机状态显示并让电流立即生效</x:t>
         </x:is>
       </x:c>
-      <x:c r="E136" s="25" t="inlineStr">
+      <x:c r="E137" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠根据电机驱动状态和目标位置判断是否正在运行。
 2.⁠修改电机运行电流后立即下发。
 3.⁠屏幕显示、保存值和电机实际设置保持一致。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F136" s="26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="137" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A137" s="35" t="n">
+      <x:c r="F137" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="138" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A138" s="36" t="n">
         <x:v>46140</x:v>
       </x:c>
-      <x:c r="B137" s="23" t="inlineStr">
+      <x:c r="B138" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.27.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C137" s="23" t="inlineStr">
+      <x:c r="C138" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.25.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D137" s="23" t="inlineStr">
+      <x:c r="D138" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">统一电机位置和测量参数</x:t>
         </x:is>
       </x:c>
-      <x:c r="E137" s="23" t="inlineStr">
+      <x:c r="E138" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠统一电机驱动、位置读取和编码器换算。
 2.⁠调整测量流程使用的电机参数。
 3.⁠主控板、显示板同步更新状态、菜单和参数。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F137" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="138" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A138" s="36" t="n">
+      <x:c r="F138" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="139" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A139" s="35" t="n">
         <x:v>46137</x:v>
       </x:c>
-      <x:c r="B138" s="25" t="inlineStr">
+      <x:c r="B139" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.27.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C138" s="25" t="inlineStr">
+      <x:c r="C139" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.25.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D138" s="25" t="inlineStr">
+      <x:c r="D139" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加固定点演示模式</x:t>
         </x:is>
       </x:c>
-      <x:c r="E138" s="25" t="inlineStr">
+      <x:c r="E139" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加固定点模拟测量和周期数据刷新。
 2.⁠可用串口调试命令启动演示。
 3.⁠演示过程可被新命令中止。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F138" s="25" t="inlineStr">
+      <x:c r="F139" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">演示模式使用模拟数据，不能作为现场实测值。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="139" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A139" s="35" t="n">
+    <x:row r="140" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A140" s="36" t="n">
         <x:v>46137</x:v>
       </x:c>
-      <x:c r="B139" s="23" t="inlineStr">
+      <x:c r="B140" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.26.3.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C139" s="23" t="inlineStr">
+      <x:c r="C140" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.25.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D139" s="23" t="inlineStr">
+      <x:c r="D140" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">调整故障处理顺序并增强探底容错</x:t>
         </x:is>
       </x:c>
-      <x:c r="E139" s="23" t="inlineStr">
+      <x:c r="E140" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠调整新命令和故障状态的处理先后。
 2.⁠找罐底增加陀螺仪基准取值和二次精找。
 3.⁠探底异常时增加退出处理，并调整水位跟随判断。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F139" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="140" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A140" s="36" t="n">
-        <x:v>46125</x:v>
-      </x:c>
-      <x:c r="B140" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.26.2.1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C140" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.25.1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D140" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">减少显示板参数重复保存</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E140" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠短时间内连续修改的显示板参数合并保存。
-2.⁠减少存储器重复写入和通信等待。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F140" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -5687,51 +5678,82 @@
       </x:c>
       <x:c r="B141" s="23" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V0.26.2.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C141" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V0.25.1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D141" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">减少显示板参数重复保存</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E141" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠短时间内连续修改的显示板参数合并保存。
+2.⁠减少存储器重复写入和通信等待。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F141" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="142" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A142" s="36" t="n">
+        <x:v>46125</x:v>
+      </x:c>
+      <x:c r="B142" s="25" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V0.26.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C141" s="23" t="inlineStr">
+      <x:c r="C142" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.25.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D141" s="23" t="inlineStr">
+      <x:c r="D142" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">调试操作可被新命令中止</x:t>
         </x:is>
       </x:c>
-      <x:c r="E141" s="23" t="inlineStr">
+      <x:c r="E142" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠串口调试操作也会检查是否收到新命令。
 2.⁠持续运行测试和电机等待过程中收到新命令会退出并停机。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F141" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="142" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A142" s="36" t="n">
+      <x:c r="F142" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="143" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A143" s="35" t="n">
         <x:v>46122</x:v>
       </x:c>
-      <x:c r="B142" s="25" t="inlineStr">
+      <x:c r="B143" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.26.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C142" s="25" t="inlineStr">
+      <x:c r="C143" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.25.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D142" s="25" t="inlineStr">
+      <x:c r="D143" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">完善液位重试和电机状态显示</x:t>
         </x:is>
       </x:c>
-      <x:c r="E142" s="25" t="inlineStr">
+      <x:c r="E143" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠传感器通信失败时按统一方式重试。
 2.⁠完善液位模式恢复和盲区等待退出。
@@ -5739,355 +5761,324 @@
 4.⁠屏幕电机图标与主控板实际状态保持一致。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F142" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="143" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A143" s="35" t="n">
+      <x:c r="F143" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="144" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A144" s="36" t="n">
         <x:v>46121</x:v>
       </x:c>
-      <x:c r="B143" s="23" t="inlineStr">
+      <x:c r="B144" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.26.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C143" s="23" t="inlineStr">
+      <x:c r="C144" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.25.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D143" s="23" t="inlineStr">
+      <x:c r="D144" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加罐高标定和屏幕联动</x:t>
         </x:is>
       </x:c>
-      <x:c r="E143" s="23" t="inlineStr">
+      <x:c r="E144" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加罐高标定操作、状态和参数。
 2.⁠屏幕增加罐高标定入口。
 3.⁠修正找罐底、水位和液位角度等数据显示。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F143" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="144" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A144" s="36" t="n">
+      <x:c r="F144" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="145" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A145" s="35" t="n">
         <x:v>46111</x:v>
       </x:c>
-      <x:c r="B144" s="25" t="inlineStr">
+      <x:c r="B145" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.25.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C144" s="25" t="inlineStr">
+      <x:c r="C145" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.24.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D144" s="25" t="inlineStr">
+      <x:c r="D145" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">水位长时间未稳定仍进入监测</x:t>
         </x:is>
       </x:c>
-      <x:c r="E144" s="25" t="inlineStr">
+      <x:c r="E145" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加等待水位稳定的最长时间。
 2.⁠超过等待时间后仍进入水位跟随监测，避免流程一直停在等待状态。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F144" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="145" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A145" s="35" t="n">
+      <x:c r="F145" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="146" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A146" s="36" t="n">
         <x:v>46109</x:v>
       </x:c>
-      <x:c r="B145" s="23" t="inlineStr">
+      <x:c r="B146" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.25.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C145" s="23" t="inlineStr">
+      <x:c r="C146" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.24.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D145" s="23" t="inlineStr">
+      <x:c r="D146" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">水位标定后恢复跟随</x:t>
         </x:is>
       </x:c>
-      <x:c r="E145" s="23" t="inlineStr">
+      <x:c r="E146" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠水位标定完成后恢复原来的跟随状态。
 2.⁠统一检查水位标定结果是否有效。
 3.⁠密度分布结束后的单点监测可被新操作中止。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F145" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="146" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A146" s="36" t="n">
+      <x:c r="F146" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="147" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A147" s="35" t="n">
         <x:v>46109</x:v>
       </x:c>
-      <x:c r="B146" s="25" t="inlineStr">
+      <x:c r="B147" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.25.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C146" s="25" t="inlineStr">
+      <x:c r="C147" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.24.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D146" s="25" t="inlineStr">
+      <x:c r="D147" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加编码器断线和称重超时检测</x:t>
         </x:is>
       </x:c>
-      <x:c r="E146" s="25" t="inlineStr">
+      <x:c r="E147" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠电机位置编码器读数异常或断线时可识别并重试。
 2.⁠称重通信长时间无回复时会报错。
 3.⁠显示板同步增加对应故障提示。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F146" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="147" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A147" s="35" t="n">
+      <x:c r="F147" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="148" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A148" s="36" t="n">
         <x:v>46109</x:v>
       </x:c>
-      <x:c r="B147" s="23" t="inlineStr">
+      <x:c r="B148" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.24.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C147" s="23" t="inlineStr">
+      <x:c r="C148" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.23.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D147" s="23" t="inlineStr">
+      <x:c r="D148" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">改善板间通信恢复和液位流程</x:t>
         </x:is>
       </x:c>
-      <x:c r="E147" s="23" t="inlineStr">
+      <x:c r="E148" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠显示板串口收发切换和异常恢复更稳定。
 2.⁠调整主控板水位跟随和找液位过程。
 3.⁠完善两块板状态同步和传感器异常处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F147" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="148" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A148" s="36" t="n">
+      <x:c r="F148" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="149" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A149" s="35" t="n">
         <x:v>46108</x:v>
       </x:c>
-      <x:c r="B148" s="25" t="inlineStr">
+      <x:c r="B149" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.24.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C148" s="25" t="inlineStr">
+      <x:c r="C149" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.23.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D148" s="25" t="inlineStr">
+      <x:c r="D149" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">完善水位跟随和切换操作</x:t>
         </x:is>
       </x:c>
-      <x:c r="E148" s="25" t="inlineStr">
+      <x:c r="E149" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠统一测量过程中切换新操作的判断。
 2.⁠水位稳定判断时间可设置。
 3.⁠调整水位跟随步长和传感器异常处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F148" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="149" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A149" s="35" t="n">
+      <x:c r="F149" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="150" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A150" s="36" t="n">
         <x:v>46108</x:v>
       </x:c>
-      <x:c r="B149" s="23" t="inlineStr">
+      <x:c r="B150" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.23.4.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C149" s="23" t="inlineStr">
+      <x:c r="C150" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.23.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D149" s="23" t="inlineStr">
+      <x:c r="D150" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复密度分布测点范围和液位单位</x:t>
         </x:is>
       </x:c>
-      <x:c r="E149" s="23" t="inlineStr">
+      <x:c r="E150" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修正指定区间密度测量使用的上下限。
 2.⁠液位高度统一按 0.1 mm 保存。
 3.⁠当前操作不再被误判为切换操作。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F149" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="150" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A150" s="36" t="n">
+      <x:c r="F150" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="151" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A151" s="35" t="n">
         <x:v>46106</x:v>
       </x:c>
-      <x:c r="B150" s="25" t="inlineStr">
+      <x:c r="B151" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.23.3.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C150" s="25" t="inlineStr">
+      <x:c r="C151" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.23.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D150" s="25" t="inlineStr">
+      <x:c r="D151" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">清理程序编译告警</x:t>
         </x:is>
       </x:c>
-      <x:c r="E150" s="25" t="inlineStr">
+      <x:c r="E151" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠清理主控板程序中的声明、数据读取和未使用调试功能告警。
 2.⁠清理显示板数据校验、显示和瓦锡兰参数转发告警。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F150" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="151" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A151" s="35" t="n">
+      <x:c r="F151" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="152" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A152" s="36" t="n">
         <x:v>46098</x:v>
       </x:c>
-      <x:c r="B151" s="23" t="inlineStr">
+      <x:c r="B152" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.23.3.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C151" s="23" t="inlineStr">
+      <x:c r="C152" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.23.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D151" s="23" t="inlineStr">
+      <x:c r="D152" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">改善两块板通信恢复和参数同步</x:t>
         </x:is>
       </x:c>
-      <x:c r="E151" s="23" t="inlineStr">
+      <x:c r="E152" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠显示板通信异常后可恢复收发。
 2.⁠完善显示板参数保存和批量同步。
 3.⁠修正主控板数据轮询和命令处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F151" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="152" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A152" s="36" t="n">
+      <x:c r="F152" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="153" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A153" s="35" t="n">
         <x:v>46097</x:v>
       </x:c>
-      <x:c r="B152" s="25" t="inlineStr">
+      <x:c r="B153" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.23.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C152" s="25" t="inlineStr">
+      <x:c r="C153" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.23.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D152" s="25" t="inlineStr">
+      <x:c r="D153" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">细分无线和传感器通信故障</x:t>
         </x:is>
       </x:c>
-      <x:c r="E152" s="25" t="inlineStr">
+      <x:c r="E153" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠无线滑环主机、无线从机和传感器通信故障可分别提示。
 2.⁠修正 DSM 传感器、LTD 传感器及无线通信回复的长度和完整性检查。
 3.⁠修正通信错误与故障提示的对应关系。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F152" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="153" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A153" s="35" t="n">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="B153" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.23.1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C153" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.23.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D153" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">恢复回零水位和探底分段变速</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E153" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠统一电机带速度运行的调用方式。
-2.⁠恢复回零、找水位和找罐底过程中的分段变速。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F153" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -6100,120 +6091,120 @@
       </x:c>
       <x:c r="B154" s="25" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V0.23.1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C154" s="25" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V0.23.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C154" s="25" t="inlineStr">
+      <x:c r="D154" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">恢复回零水位和探底分段变速</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E154" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠统一电机带速度运行的调用方式。
+2.⁠恢复回零、找水位和找罐底过程中的分段变速。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F154" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="155" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A155" s="35" t="n">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="B155" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.23.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D154" s="25" t="inlineStr">
+      <x:c r="C155" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V0.23.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D155" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加按条件运行和临时速度控制</x:t>
         </x:is>
       </x:c>
-      <x:c r="E154" s="25" t="inlineStr">
+      <x:c r="E155" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠电机可运行到指定条件满足后停止。
 2.⁠单次运动可指定临时速度。
 3.⁠临时运动结束后恢复原设置速度。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F154" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="155" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A155" s="35" t="n">
+      <x:c r="F155" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="156" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A156" s="36" t="n">
         <x:v>46093</x:v>
       </x:c>
-      <x:c r="B155" s="23" t="inlineStr">
+      <x:c r="B156" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.22.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C155" s="23" t="inlineStr">
+      <x:c r="C156" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.23.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D155" s="23" t="inlineStr">
+      <x:c r="D156" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复无线滑环主机编译缺少声明</x:t>
         </x:is>
       </x:c>
-      <x:c r="E155" s="23" t="inlineStr">
+      <x:c r="E156" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠补齐无线滑环主机通信程序的函数声明。
 2.⁠修复相关程序编译时找不到通信接口的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F155" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="156" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A156" s="36" t="n">
+      <x:c r="F156" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="157" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A157" s="35" t="n">
         <x:v>46087</x:v>
       </x:c>
-      <x:c r="B156" s="25" t="inlineStr">
+      <x:c r="B157" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.22.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C156" s="25" t="inlineStr">
+      <x:c r="C157" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.23.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D156" s="25" t="inlineStr">
+      <x:c r="D157" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加恒线速度和失步检测</x:t>
         </x:is>
       </x:c>
-      <x:c r="E156" s="25" t="inlineStr">
+      <x:c r="E157" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠根据尺带卷径变化自动调整电机速度，使探头升降速度更稳定。
 2.⁠增加电机实际位置与记录不一致的失步检测。
 3.⁠增加速度限制和运行中速度修正。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F156" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="157" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A157" s="35" t="n">
-        <x:v>46087</x:v>
-      </x:c>
-      <x:c r="B157" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.21.0.1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C157" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.22.0.1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D157" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">增加开发资料入口</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E157" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠在项目说明中增加开发资料入口。
-2.⁠更新仓库程序资料清单。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F157" s="27" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -6226,121 +6217,121 @@
       </x:c>
       <x:c r="B158" s="25" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V0.21.0.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C158" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V0.22.0.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D158" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">增加开发资料入口</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E158" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠在项目说明中增加开发资料入口。
+2.⁠更新仓库程序资料清单。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F158" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="159" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A159" s="35" t="n">
+        <x:v>46087</x:v>
+      </x:c>
+      <x:c r="B159" s="23" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V0.21.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C158" s="25" t="inlineStr">
+      <x:c r="C159" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.22.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D158" s="25" t="inlineStr">
+      <x:c r="D159" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">设备参数和位置记录增加双份保存</x:t>
         </x:is>
       </x:c>
-      <x:c r="E158" s="25" t="inlineStr">
+      <x:c r="E159" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠设备参数和电机位置记录各保存两份。
 2.⁠一份记录损坏时可改用另一份。
 3.⁠增加双份记录损坏时的恢复检查。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F158" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="159" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A159" s="35" t="n">
+      <x:c r="F159" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="160" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A160" s="36" t="n">
         <x:v>46086</x:v>
       </x:c>
-      <x:c r="B159" s="23" t="inlineStr">
+      <x:c r="B160" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.20.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C159" s="23" t="inlineStr">
+      <x:c r="C160" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.22.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D159" s="23" t="inlineStr">
+      <x:c r="D160" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加液位水位和尺带补偿参数</x:t>
         </x:is>
       </x:c>
-      <x:c r="E159" s="23" t="inlineStr">
+      <x:c r="E160" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加液位变化滞后时间和水位修正设置。
 2.⁠增加气相温度和尺带温度补偿设置。
 3.⁠主控板、显示板同步增加参数和菜单。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F159" s="23" t="inlineStr">
+      <x:c r="F160" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">升级后会恢复默认参数；升级前记录现场参数，升级后重新设置并复核。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="160" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A160" s="36" t="n">
+    <x:row r="161" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A161" s="35" t="n">
         <x:v>46086</x:v>
       </x:c>
-      <x:c r="B160" s="25" t="inlineStr">
+      <x:c r="B161" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.19.4.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C160" s="25" t="inlineStr">
+      <x:c r="C161" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.21.1.2</x:t>
         </x:is>
       </x:c>
-      <x:c r="D160" s="25" t="inlineStr">
+      <x:c r="D161" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">恢复运动碰撞检测并整理运行流程</x:t>
         </x:is>
       </x:c>
-      <x:c r="E160" s="25" t="inlineStr">
+      <x:c r="E161" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠恢复探头运动时的称重碰撞检测。
 2.⁠整理主控板运行和测试入口。
 3.⁠调整电机驱动设置。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F160" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="161" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A161" s="35" t="n">
-        <x:v>46085</x:v>
-      </x:c>
-      <x:c r="B161" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.19.3.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C161" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.21.1.1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D161" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">增加显示板自动编译检查</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E161" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠增加显示板程序的自动编译配置。
-2.⁠自动构建检查同时覆盖主控板和显示板。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F161" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -6358,84 +6349,84 @@
       </x:c>
       <x:c r="C162" s="25" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V0.21.1.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D162" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">增加显示板自动编译检查</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E162" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠增加显示板程序的自动编译配置。
+2.⁠自动构建检查同时覆盖主控板和显示板。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F162" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="163" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A163" s="35" t="n">
+        <x:v>46085</x:v>
+      </x:c>
+      <x:c r="B163" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V0.19.3.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C163" s="23" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V0.21.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D162" s="25" t="inlineStr">
+      <x:c r="D163" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复不同开发环境下的编译问题</x:t>
         </x:is>
       </x:c>
-      <x:c r="E162" s="25" t="inlineStr">
+      <x:c r="E163" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠统一主控板、显示板程序文件名称的大小写。
 2.⁠避免在区分大小写的开发环境中找不到文件。
 3.⁠同步调整水位电容换算和位置更新引用。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F162" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="163" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A163" s="35" t="n">
+      <x:c r="F163" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="164" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A164" s="36" t="n">
         <x:v>46085</x:v>
       </x:c>
-      <x:c r="B163" s="23" t="inlineStr">
+      <x:c r="B164" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.19.2.6</x:t>
         </x:is>
       </x:c>
-      <x:c r="C163" s="23" t="inlineStr">
+      <x:c r="C164" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.21.0.2</x:t>
         </x:is>
       </x:c>
-      <x:c r="D163" s="23" t="inlineStr">
+      <x:c r="D164" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">补充开发资料和称重接口说明</x:t>
         </x:is>
       </x:c>
-      <x:c r="E163" s="23" t="inlineStr">
+      <x:c r="E164" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠整理仓库导览资料。
 2.⁠增加主控板程序拆分方案。
 3.⁠补充称重接口说明。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F163" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="164" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A164" s="36" t="n">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="B164" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.19.2.5</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C164" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.21.0.2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D164" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">清理旧验证工程和历史副本</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E164" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠删除不再使用的文本、电机、水位等验证工程。
-2.⁠保留当前主控板、显示板和无线滑环主机工程作为维护入口。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F164" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -6448,23 +6439,23 @@
       </x:c>
       <x:c r="B165" s="23" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">V0.19.2.4</x:t>
+          <x:t xml:space="preserve">V0.19.2.5</x:t>
         </x:is>
       </x:c>
       <x:c r="C165" s="23" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">V0.21.0.1</x:t>
+          <x:t xml:space="preserve">V0.21.0.2</x:t>
         </x:is>
       </x:c>
       <x:c r="D165" s="23" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">停止维护旧工程目录</x:t>
+          <x:t xml:space="preserve">清理旧验证工程和历史副本</x:t>
         </x:is>
       </x:c>
       <x:c r="E165" s="23" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.⁠旧工程目录不再作为当前程序维护内容。
-2.⁠同步整理忽略规则、编辑器设置和构建配置。</x:t>
+          <x:t xml:space="preserve">1.⁠删除不再使用的文本、电机、水位等验证工程。
+2.⁠保留当前主控板、显示板和无线滑环主机工程作为维护入口。</x:t>
         </x:is>
       </x:c>
       <x:c r="F165" s="23" t="inlineStr">
@@ -6479,23 +6470,23 @@
       </x:c>
       <x:c r="B166" s="25" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">V0.19.2.3</x:t>
+          <x:t xml:space="preserve">V0.19.2.4</x:t>
         </x:is>
       </x:c>
       <x:c r="C166" s="25" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">V0.21.0.0</x:t>
+          <x:t xml:space="preserve">V0.21.0.1</x:t>
         </x:is>
       </x:c>
       <x:c r="D166" s="25" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">主控板接入自动构建</x:t>
+          <x:t xml:space="preserve">停止维护旧工程目录</x:t>
         </x:is>
       </x:c>
       <x:c r="E166" s="25" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.⁠合并主控板的两套自动编译配置。
-2.⁠增加持续自动构建检查。</x:t>
+          <x:t xml:space="preserve">1.⁠旧工程目录不再作为当前程序维护内容。
+2.⁠同步整理忽略规则、编辑器设置和构建配置。</x:t>
         </x:is>
       </x:c>
       <x:c r="F166" s="25" t="inlineStr">
@@ -6510,7 +6501,7 @@
       </x:c>
       <x:c r="B167" s="23" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">V0.19.2.2</x:t>
+          <x:t xml:space="preserve">V0.19.2.3</x:t>
         </x:is>
       </x:c>
       <x:c r="C167" s="23" t="inlineStr">
@@ -6520,13 +6511,13 @@
       </x:c>
       <x:c r="D167" s="23" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">完善主控板自动编译基础</x:t>
+          <x:t xml:space="preserve">主控板接入自动构建</x:t>
         </x:is>
       </x:c>
       <x:c r="E167" s="23" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.⁠补齐主控板自动编译所需的工程配置。
-2.⁠增加编译预设、程序链接设置和基础说明。</x:t>
+          <x:t xml:space="preserve">1.⁠合并主控板的两套自动编译配置。
+2.⁠增加持续自动构建检查。</x:t>
         </x:is>
       </x:c>
       <x:c r="F167" s="23" t="inlineStr">
@@ -6541,7 +6532,7 @@
       </x:c>
       <x:c r="B168" s="25" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">V0.19.2.1</x:t>
+          <x:t xml:space="preserve">V0.19.2.2</x:t>
         </x:is>
       </x:c>
       <x:c r="C168" s="25" t="inlineStr">
@@ -6551,13 +6542,13 @@
       </x:c>
       <x:c r="D168" s="25" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">增加主控板自动编译检查</x:t>
+          <x:t xml:space="preserve">完善主控板自动编译基础</x:t>
         </x:is>
       </x:c>
       <x:c r="E168" s="25" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.⁠增加主控板程序的自动编译配置。
-2.⁠补充本机构建说明。</x:t>
+          <x:t xml:space="preserve">1.⁠补齐主控板自动编译所需的工程配置。
+2.⁠增加编译预设、程序链接设置和基础说明。</x:t>
         </x:is>
       </x:c>
       <x:c r="F168" s="25" t="inlineStr">
@@ -6572,438 +6563,438 @@
       </x:c>
       <x:c r="B169" s="23" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V0.19.2.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C169" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V0.21.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D169" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">增加主控板自动编译检查</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E169" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠增加主控板程序的自动编译配置。
+2.⁠补充本机构建说明。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F169" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="170" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A170" s="36" t="n">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="B170" s="25" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V0.19.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C169" s="23" t="inlineStr">
+      <x:c r="C170" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.21.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D169" s="23" t="inlineStr">
+      <x:c r="D170" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加罐高显示并修复水位跟随状态</x:t>
         </x:is>
       </x:c>
-      <x:c r="E169" s="23" t="inlineStr">
+      <x:c r="E170" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠屏幕增加罐高结果显示。
 2.⁠修正部分参数写入后的数值。
 3.⁠每次快速寻找水位前清除上一次判断记录。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F169" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="170" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A170" s="36" t="n">
+      <x:c r="F170" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="171" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A171" s="35" t="n">
         <x:v>46080</x:v>
       </x:c>
-      <x:c r="B170" s="25" t="inlineStr">
+      <x:c r="B171" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.19.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C170" s="25" t="inlineStr">
+      <x:c r="C171" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.20.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D170" s="25" t="inlineStr">
+      <x:c r="D171" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复显示板参数写入数值错误</x:t>
         </x:is>
       </x:c>
-      <x:c r="E170" s="25" t="inlineStr">
+      <x:c r="E171" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复显示板写入部分参数后数值不正确的问题。
 2.⁠统一串口接收长度和参数转发处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F170" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="171" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A171" s="35" t="n">
+      <x:c r="F171" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="172" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A172" s="36" t="n">
         <x:v>46079</x:v>
       </x:c>
-      <x:c r="B171" s="23" t="inlineStr">
+      <x:c r="B172" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.19.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C171" s="23" t="inlineStr">
+      <x:c r="C172" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.20.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D171" s="23" t="inlineStr">
+      <x:c r="D172" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加水位快速寻找和跟随</x:t>
         </x:is>
       </x:c>
-      <x:c r="E171" s="23" t="inlineStr">
+      <x:c r="E172" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加水位快速寻找。
 2.⁠根据水位信号变化判断是否找到水面。
 3.⁠找到水面后进入持续跟随。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F171" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="172" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A172" s="36" t="n">
+      <x:c r="F172" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="173" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A173" s="35" t="n">
         <x:v>46056</x:v>
       </x:c>
-      <x:c r="B172" s="25" t="inlineStr">
+      <x:c r="B173" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.18.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C172" s="25" t="inlineStr">
+      <x:c r="C173" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.19.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D172" s="25" t="inlineStr">
+      <x:c r="D173" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复福建LNG现场通信和状态显示</x:t>
         </x:is>
       </x:c>
-      <x:c r="E172" s="25" t="inlineStr">
+      <x:c r="E173" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修正瓦锡兰系统读取数据和下发参数时的回复。
 2.⁠修正设备工作状态对应关系。
 3.⁠调整密度测量、单点监测和传感器有效值处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F172" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="173" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A173" s="35" t="n">
+      <x:c r="F173" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="174" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A174" s="36" t="n">
         <x:v>46055</x:v>
       </x:c>
-      <x:c r="B173" s="23" t="inlineStr">
+      <x:c r="B174" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.18.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C173" s="23" t="inlineStr">
+      <x:c r="C174" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.19.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D173" s="23" t="inlineStr">
+      <x:c r="D174" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加多种液位测量方式</x:t>
         </x:is>
       </x:c>
-      <x:c r="E173" s="23" t="inlineStr">
+      <x:c r="E174" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加相对频率、固定频率、密度和超声液位测量方式。
 2.⁠增加液位跟随所需的频率和密度设置。
 3.⁠完善密度读数稳定判断。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F173" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="174" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A174" s="36" t="n">
+      <x:c r="F174" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="175" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A175" s="35" t="n">
         <x:v>46046</x:v>
       </x:c>
-      <x:c r="B174" s="25" t="inlineStr">
+      <x:c r="B175" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.17.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C174" s="25" t="inlineStr">
+      <x:c r="C175" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.18.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D174" s="25" t="inlineStr">
+      <x:c r="D175" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复版本显示和液位参数单位</x:t>
         </x:is>
       </x:c>
-      <x:c r="E174" s="25" t="inlineStr">
+      <x:c r="E175" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修正显示板程序版本显示。
 2.⁠修正液位方式及相关修正参数的单位。
 3.⁠调整探头角度的显示条件。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F174" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="175" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A175" s="35" t="n">
+      <x:c r="F175" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="176" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A176" s="36" t="n">
         <x:v>46045</x:v>
       </x:c>
-      <x:c r="B175" s="23" t="inlineStr">
+      <x:c r="B176" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.17.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C175" s="23" t="inlineStr">
+      <x:c r="C176" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.18.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D175" s="23" t="inlineStr">
+      <x:c r="D176" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复电机定位和无效密度采用</x:t>
         </x:is>
       </x:c>
-      <x:c r="E175" s="23" t="inlineStr">
+      <x:c r="E176" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠按尺带卷绕变化修正电机位置换算。
 2.⁠修复电机到位停止判断。
 3.⁠密度读数无效时不再作为测量结果。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F175" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="176" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A176" s="36" t="n">
+      <x:c r="F176" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="177" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A177" s="35" t="n">
         <x:v>46041</x:v>
       </x:c>
-      <x:c r="B176" s="25" t="inlineStr">
+      <x:c r="B177" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.17.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C176" s="25" t="inlineStr">
+      <x:c r="C177" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.18.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D176" s="25" t="inlineStr">
+      <x:c r="D177" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加上电默认操作和水位零点参数</x:t>
         </x:is>
       </x:c>
-      <x:c r="E176" s="25" t="inlineStr">
+      <x:c r="E177" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠可设置设备上电后的默认操作。
 2.⁠增加水位零点电容和瓦锡兰密度参数。
 3.⁠完善水位标定、瓦锡兰状态和电机控制。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F176" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="177" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A177" s="35" t="n">
+      <x:c r="F177" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="178" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A178" s="36" t="n">
         <x:v>46037</x:v>
       </x:c>
-      <x:c r="B177" s="23" t="inlineStr">
+      <x:c r="B178" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.16.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C177" s="23" t="inlineStr">
+      <x:c r="C178" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.17.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D177" s="23" t="inlineStr">
+      <x:c r="D178" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加水位调试操作和探底角度显示</x:t>
         </x:is>
       </x:c>
-      <x:c r="E177" s="23" t="inlineStr">
+      <x:c r="E178" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加水位跟随、运行到位、强制运动和水位标定调试操作。
 2.⁠屏幕增加探底方式选择。
 3.⁠屏幕可查看陀螺仪角度。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F177" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="178" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A178" s="36" t="n">
+      <x:c r="F178" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="179" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A179" s="35" t="n">
         <x:v>46034</x:v>
       </x:c>
-      <x:c r="B178" s="25" t="inlineStr">
+      <x:c r="B179" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.15.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C178" s="25" t="inlineStr">
+      <x:c r="C179" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.16.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D178" s="25" t="inlineStr">
+      <x:c r="D179" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">整理屏幕菜单和测量流程</x:t>
         </x:is>
       </x:c>
-      <x:c r="E178" s="25" t="inlineStr">
+      <x:c r="E179" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠重新整理显示板参数分组、命令状态显示和中文字库检查。
 2.⁠完善主控板测量调度、电机位置、称重和水位处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F178" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="179" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A179" s="35" t="n">
+      <x:c r="F179" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="180" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A180" s="36" t="n">
         <x:v>46031</x:v>
       </x:c>
-      <x:c r="B179" s="23" t="inlineStr">
+      <x:c r="B180" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.15.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C179" s="23" t="inlineStr">
+      <x:c r="C180" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.16.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D179" s="23" t="inlineStr">
+      <x:c r="D180" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">补齐设备参数和屏幕设置</x:t>
         </x:is>
       </x:c>
-      <x:c r="E179" s="23" t="inlineStr">
+      <x:c r="E180" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠补齐设备、机械、称重、液位、水位和罐底设置。
 2.⁠显示板同步增加菜单和参数读写。
 3.⁠两块板的参数保存内容保持对应。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F179" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="180" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A180" s="36" t="n">
+      <x:c r="F180" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="181" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A181" s="35" t="n">
         <x:v>46031</x:v>
       </x:c>
-      <x:c r="B180" s="25" t="inlineStr">
+      <x:c r="B181" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.14.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C180" s="25" t="inlineStr">
+      <x:c r="C181" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.15.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D180" s="25" t="inlineStr">
+      <x:c r="D181" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复显示板本机参数被错写</x:t>
         </x:is>
       </x:c>
-      <x:c r="E180" s="25" t="inlineStr">
+      <x:c r="E181" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠显示板批量读取主控板参数时，不再覆盖显示板自己的通信设置。
 2.⁠补充找罐底状态检查。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F180" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="181" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A181" s="35" t="n">
+      <x:c r="F181" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="182" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A182" s="36" t="n">
         <x:v>46028</x:v>
       </x:c>
-      <x:c r="B181" s="23" t="inlineStr">
+      <x:c r="B182" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.14.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C181" s="23" t="inlineStr">
+      <x:c r="C182" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.15.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D181" s="23" t="inlineStr">
+      <x:c r="D182" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">调整水位跟随稳定判断</x:t>
         </x:is>
       </x:c>
-      <x:c r="E181" s="23" t="inlineStr">
+      <x:c r="E182" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠调整水位跟随的移动步长和变化滞后。
 2.⁠调整水位信号丢失判断。
 3.⁠同步电机相关设置并增加内部中文编码检查资料。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F181" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="182" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A182" s="36" t="n">
-        <x:v>46022</x:v>
-      </x:c>
-      <x:c r="B182" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.14.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C182" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.15.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D182" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">增加电机测试并调整运行保护</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E182" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠增加电机往返和测量流程测试。
-2.⁠调整找罐底、找液位、回零时的电机保护。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F182" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -7016,116 +7007,147 @@
       </x:c>
       <x:c r="B183" s="23" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V0.14.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C183" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V0.15.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D183" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">增加电机测试并调整运行保护</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E183" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠增加电机往返和测量流程测试。
+2.⁠调整找罐底、找液位、回零时的电机保护。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F183" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="184" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A184" s="36" t="n">
+        <x:v>46022</x:v>
+      </x:c>
+      <x:c r="B184" s="25" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V0.13.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C183" s="23" t="inlineStr">
+      <x:c r="C184" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.15.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D183" s="23" t="inlineStr">
+      <x:c r="D184" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加陀螺仪探底方式</x:t>
         </x:is>
       </x:c>
-      <x:c r="E183" s="23" t="inlineStr">
+      <x:c r="E184" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加根据探头倾斜角度判断罐底的方式。
 2.⁠保留原有称重探底方式。
 3.⁠增加角度读取、基准保存和探底设置。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F183" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="184" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A184" s="36" t="n">
+      <x:c r="F184" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="185" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A185" s="35" t="n">
         <x:v>46021</x:v>
       </x:c>
-      <x:c r="B184" s="25" t="inlineStr">
+      <x:c r="B185" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.12.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C184" s="25" t="inlineStr">
+      <x:c r="C185" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.15.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D184" s="25" t="inlineStr">
+      <x:c r="D185" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加多种密度分布测量方式</x:t>
         </x:is>
       </x:c>
-      <x:c r="E184" s="25" t="inlineStr">
+      <x:c r="E185" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加普通分布、国标、每米和指定区间密度测量。
 2.⁠统一测点生成、单点取值和结果汇总。
 3.⁠显示板可读取各种分布测量结果。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F184" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="185" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A185" s="35" t="n">
+      <x:c r="F185" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="186" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A186" s="36" t="n">
         <x:v>46017</x:v>
       </x:c>
-      <x:c r="B185" s="23" t="inlineStr">
+      <x:c r="B186" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.11.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C185" s="23" t="inlineStr">
+      <x:c r="C186" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.14.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D185" s="23" t="inlineStr">
+      <x:c r="D186" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复水位重新寻找和通信解析</x:t>
         </x:is>
       </x:c>
-      <x:c r="E185" s="23" t="inlineStr">
+      <x:c r="E186" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠水位状态异常时，探头分步上行重新寻找水面。
 2.⁠修正显示板接收 DSM 数据和主控板数据时的解析问题。
 3.⁠删除重复的菜单处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F185" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="186" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A186" s="36" t="n">
+      <x:c r="F186" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="187" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A187" s="35" t="n">
         <x:v>46016</x:v>
       </x:c>
-      <x:c r="B186" s="25" t="inlineStr">
+      <x:c r="B187" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.11.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C186" s="25" t="inlineStr">
+      <x:c r="C187" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.14.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D186" s="25" t="inlineStr">
+      <x:c r="D187" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">改善多路通信并减少数据冲突</x:t>
         </x:is>
       </x:c>
-      <x:c r="E186" s="25" t="inlineStr">
+      <x:c r="E187" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠不同外部通信按端口设置分别处理。
 2.⁠多条待发送数据改为排队发送，减少互相占用。
@@ -7133,642 +7155,611 @@
 4.⁠完善主控板水位测量流程。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F186" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="187" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A187" s="35" t="n">
+      <x:c r="F187" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="188" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A188" s="36" t="n">
         <x:v>46011</x:v>
       </x:c>
-      <x:c r="B187" s="23" t="inlineStr">
+      <x:c r="B188" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.11.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C187" s="23" t="inlineStr">
+      <x:c r="C188" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.13.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D187" s="23" t="inlineStr">
+      <x:c r="D188" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加水位测量和通信设置菜单</x:t>
         </x:is>
       </x:c>
-      <x:c r="E187" s="23" t="inlineStr">
+      <x:c r="E188" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠主控板增加找水位、水位标定和水位跟随。
 2.⁠显示板增加波特率、校验方式、停止位和通信类型设置。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F187" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="188" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A188" s="36" t="n">
+      <x:c r="F188" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="189" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A189" s="35" t="n">
         <x:v>46007</x:v>
       </x:c>
-      <x:c r="B188" s="25" t="inlineStr">
+      <x:c r="B189" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.10.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C188" s="25" t="inlineStr">
+      <x:c r="C189" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.12.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D188" s="25" t="inlineStr">
+      <x:c r="D189" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">统一主控板和显示板工程名称</x:t>
         </x:is>
       </x:c>
-      <x:c r="E188" s="25" t="inlineStr">
+      <x:c r="E189" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠现用主控板工程统一命名为 CPU2。
 2.⁠现用显示板工程统一命名为 CPU3。
 3.⁠旧工程移入历史目录。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F188" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="189" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A189" s="35" t="n">
+      <x:c r="F189" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="190" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A190" s="36" t="n">
         <x:v>46006</x:v>
       </x:c>
-      <x:c r="B189" s="23" t="inlineStr">
+      <x:c r="B190" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.10.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C189" s="23" t="inlineStr">
+      <x:c r="C190" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.12.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D189" s="23" t="inlineStr">
+      <x:c r="D190" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复显示板通信中断后的恢复</x:t>
         </x:is>
       </x:c>
-      <x:c r="E189" s="23" t="inlineStr">
+      <x:c r="E190" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠显示板串口接收异常后可重新启动接收。
 2.⁠调整三路 RS485 发送后的收发切换时间。
 3.⁠修正部分参数转发。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F189" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="190" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A190" s="36" t="n">
+      <x:c r="F190" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="191" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A191" s="35" t="n">
         <x:v>46003</x:v>
       </x:c>
-      <x:c r="B190" s="25" t="inlineStr">
+      <x:c r="B191" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.10.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C190" s="25" t="inlineStr">
+      <x:c r="C191" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.12.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D190" s="25" t="inlineStr">
+      <x:c r="D191" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">整理显示板参数同步和菜单</x:t>
         </x:is>
       </x:c>
-      <x:c r="E190" s="25" t="inlineStr">
+      <x:c r="E191" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠将显示板本机设置与主控板参数分开同步。
 2.⁠整理罐上操作菜单。
 3.⁠调整外部通信和两板内部通信处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F190" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="191" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A191" s="35" t="n">
+      <x:c r="F191" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="192" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A192" s="36" t="n">
         <x:v>46002</x:v>
       </x:c>
-      <x:c r="B191" s="23" t="inlineStr">
+      <x:c r="B192" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.10.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C191" s="23" t="inlineStr">
+      <x:c r="C192" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.12.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D191" s="23" t="inlineStr">
+      <x:c r="D192" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">通信设置可保存并增加运行看护</x:t>
         </x:is>
       </x:c>
-      <x:c r="E191" s="23" t="inlineStr">
+      <x:c r="E192" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠显示板的三路通信方式、波特率等设置可保存，重启后继续使用。
 2.⁠通信设置修改后可自动重新配置。
 3.⁠主控板和显示板增加运行看护，程序异常卡住时可自动复位。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F191" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="192" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A192" s="36" t="n">
+      <x:c r="F192" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="193" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A193" s="35" t="n">
         <x:v>46000</x:v>
       </x:c>
-      <x:c r="B192" s="25" t="inlineStr">
+      <x:c r="B193" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.9.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C192" s="25" t="inlineStr">
+      <x:c r="C193" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.11.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D192" s="25" t="inlineStr">
+      <x:c r="D193" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加无线传感器通信重试</x:t>
         </x:is>
       </x:c>
-      <x:c r="E192" s="25" t="inlineStr">
+      <x:c r="E193" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠主控板增加无线传感器通信。
 2.⁠通信超时或数据不完整时会重新尝试。
 3.⁠显示板同步读取无线连接状态和相关参数。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F192" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="193" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A193" s="35" t="n">
+      <x:c r="F193" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="194" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A194" s="36" t="n">
         <x:v>45999</x:v>
       </x:c>
-      <x:c r="B193" s="23" t="inlineStr">
+      <x:c r="B194" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.8.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C193" s="23" t="inlineStr">
+      <x:c r="C194" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.10.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D193" s="23" t="inlineStr">
+      <x:c r="D194" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">完善瓦锡兰密度分布测量</x:t>
         </x:is>
       </x:c>
-      <x:c r="E193" s="23" t="inlineStr">
+      <x:c r="E194" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠完善密度分布测量的测点安排和稳定取值。
 2.⁠显示板可按实际测点数分段读取全部结果。
 3.⁠同步无线滑环主机的相关程序。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F193" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="194" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A194" s="36" t="n">
+      <x:c r="F194" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="195" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A195" s="35" t="n">
         <x:v>45995</x:v>
       </x:c>
-      <x:c r="B194" s="25" t="inlineStr">
+      <x:c r="B195" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.7.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C194" s="25" t="inlineStr">
+      <x:c r="C195" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.9.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D194" s="25" t="inlineStr">
+      <x:c r="D195" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">统一设备参数和运行状态</x:t>
         </x:is>
       </x:c>
-      <x:c r="E194" s="25" t="inlineStr">
+      <x:c r="E195" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠统一主控板、显示板的设备参数、操作命令和运行状态。
 2.⁠调整屏幕菜单分组和称重显示。
 3.⁠完善瓦锡兰参数及数据同步。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F194" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="195" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A195" s="35" t="n">
+      <x:c r="F195" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="196" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A196" s="36" t="n">
         <x:v>45992</x:v>
       </x:c>
-      <x:c r="B195" s="23" t="inlineStr">
+      <x:c r="B196" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.6.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C195" s="23" t="inlineStr">
+      <x:c r="C196" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.8.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D195" s="23" t="inlineStr">
+      <x:c r="D196" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">调整测量命令并增加密度参数</x:t>
         </x:is>
       </x:c>
-      <x:c r="E195" s="23" t="inlineStr">
+      <x:c r="E196" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠重新编排主控板、显示板的测量和调试命令。
 2.⁠增加密度计算和显示所需参数。
 3.⁠增加瓦锡兰测量所需参数。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F195" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="196" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A196" s="36" t="n">
+      <x:c r="F196" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="197" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A197" s="35" t="n">
         <x:v>45987</x:v>
       </x:c>
-      <x:c r="B196" s="25" t="inlineStr">
+      <x:c r="B197" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.5.1.2</x:t>
         </x:is>
       </x:c>
-      <x:c r="C196" s="25" t="inlineStr">
+      <x:c r="C197" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.7.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D196" s="25" t="inlineStr">
+      <x:c r="D197" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">调整中文程序编码</x:t>
         </x:is>
       </x:c>
-      <x:c r="E196" s="25" t="inlineStr">
+      <x:c r="E197" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠调整主控板、显示板中文程序文件的编码。
 2.⁠保证中文菜单和调试文字可在原开发工具中正常显示。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F196" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="197" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A197" s="35" t="n">
+      <x:c r="F197" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="198" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A198" s="36" t="n">
         <x:v>45981</x:v>
       </x:c>
-      <x:c r="B197" s="23" t="inlineStr">
+      <x:c r="B198" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.5.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C197" s="23" t="inlineStr">
+      <x:c r="C198" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.7.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D197" s="23" t="inlineStr">
+      <x:c r="D198" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">显示板增加瓦锡兰通信</x:t>
         </x:is>
       </x:c>
-      <x:c r="E197" s="23" t="inlineStr">
+      <x:c r="E198" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠显示板增加与瓦锡兰系统的通信。
 2.⁠支持瓦锡兰系统读取结果、设备状态和相关参数。
 3.⁠将外部通信和两板内部通信分开处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F197" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="198" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A198" s="36" t="n">
+      <x:c r="F198" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="199" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A199" s="35" t="n">
         <x:v>45980</x:v>
       </x:c>
-      <x:c r="B198" s="25" t="inlineStr">
+      <x:c r="B199" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.5.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C198" s="25" t="inlineStr">
+      <x:c r="C199" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.6.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D198" s="25" t="inlineStr">
+      <x:c r="D199" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">整理显示板运行入口和主控板传感器程序</x:t>
         </x:is>
       </x:c>
-      <x:c r="E198" s="25" t="inlineStr">
+      <x:c r="E199" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠显示板增加统一的开机初始化和运行入口。
 2.⁠整理主控板串口、传感器和电机程序。
 3.⁠移除未使用的采集驱动文件。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F198" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="199" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A199" s="35" t="n">
+      <x:c r="F199" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="200" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A200" s="36" t="n">
         <x:v>45979</x:v>
       </x:c>
-      <x:c r="B199" s="23" t="inlineStr">
+      <x:c r="B200" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.5.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C199" s="23" t="inlineStr">
+      <x:c r="C200" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.6.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D199" s="23" t="inlineStr">
+      <x:c r="D200" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复液位更新和回零卡住</x:t>
         </x:is>
       </x:c>
-      <x:c r="E199" s="23" t="inlineStr">
+      <x:c r="E200" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修正液位更新、下行距离和盲区处理。
 2.⁠修正部分参数显示的小数位。
 3.⁠零点标定卡住时会报错并让探头上行退出。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F199" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="200" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A200" s="36" t="n">
+      <x:c r="F200" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="201" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A201" s="35" t="n">
         <x:v>45971</x:v>
       </x:c>
-      <x:c r="B200" s="25" t="inlineStr">
+      <x:c r="B201" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.5.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C200" s="25" t="inlineStr">
+      <x:c r="C201" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.6.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D200" s="25" t="inlineStr">
+      <x:c r="D201" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">传感器通信按类型分开处理</x:t>
         </x:is>
       </x:c>
-      <x:c r="E200" s="25" t="inlineStr">
+      <x:c r="E201" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠DSM 传感器和 LTD 传感器改为分别处理。
 2.⁠增加密度测量入口。
 3.⁠统一主控板、显示板的命令、状态和参数对应关系。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F200" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="201" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A201" s="35" t="n">
+      <x:c r="F201" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="202" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A202" s="36" t="n">
         <x:v>45965</x:v>
       </x:c>
-      <x:c r="B201" s="23" t="inlineStr">
+      <x:c r="B202" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.4.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C201" s="23" t="inlineStr">
+      <x:c r="C202" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.5.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D201" s="23" t="inlineStr">
+      <x:c r="D202" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">完善测量流程和两板通信</x:t>
         </x:is>
       </x:c>
-      <x:c r="E201" s="23" t="inlineStr">
+      <x:c r="E202" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠继续完善回零、找罐底、液位、电机和传感器处理。
 2.⁠调整主控板与显示板的 RS485 收发控制。
 3.⁠完善 HART 通信处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F201" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="202" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A202" s="36" t="n">
+      <x:c r="F202" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="203" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A203" s="35" t="n">
         <x:v>45953</x:v>
       </x:c>
-      <x:c r="B202" s="25" t="inlineStr">
+      <x:c r="B203" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.4.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C202" s="25" t="inlineStr">
+      <x:c r="C203" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.5.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D202" s="25" t="inlineStr">
+      <x:c r="D203" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">完善电机称重和回零故障处理</x:t>
         </x:is>
       </x:c>
-      <x:c r="E202" s="25" t="inlineStr">
+      <x:c r="E203" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠完善电机运动和称重采样处理。
 2.⁠调整回零、找罐底和液位测量过程。
 3.⁠补充相应故障提示。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F202" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="203" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A203" s="35" t="n">
+      <x:c r="F203" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="204" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A204" s="36" t="n">
         <x:v>45948</x:v>
       </x:c>
-      <x:c r="B203" s="23" t="inlineStr">
+      <x:c r="B204" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.4.0.2</x:t>
         </x:is>
       </x:c>
-      <x:c r="C203" s="23" t="inlineStr">
+      <x:c r="C204" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.5.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D203" s="23" t="inlineStr">
+      <x:c r="D204" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">整理主控板程序结构</x:t>
         </x:is>
       </x:c>
-      <x:c r="E203" s="23" t="inlineStr">
+      <x:c r="E204" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠整理主控板的驱动、服务和应用程序目录。
 2.⁠调整故障、测量、传感器和电机程序之间的调用关系。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F203" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="204" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A204" s="36" t="n">
+      <x:c r="F204" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="205" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A205" s="35" t="n">
         <x:v>45947</x:v>
       </x:c>
-      <x:c r="B204" s="25" t="inlineStr">
+      <x:c r="B205" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.4.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C204" s="25" t="inlineStr">
+      <x:c r="C205" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.5.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D204" s="25" t="inlineStr">
+      <x:c r="D205" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">调整找液位和液位跟随流程</x:t>
         </x:is>
       </x:c>
-      <x:c r="E204" s="25" t="inlineStr">
+      <x:c r="E205" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠调整找液位、液位跟随、称重和传感器配合过程。
 2.⁠整理主控板程序目录。
 3.⁠同步显示板与主控板的数据对应关系。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F204" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="205" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A205" s="35" t="n">
+      <x:c r="F205" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="206" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A206" s="36" t="n">
         <x:v>45910</x:v>
       </x:c>
-      <x:c r="B205" s="23" t="inlineStr">
+      <x:c r="B206" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.4.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C205" s="23" t="inlineStr">
+      <x:c r="C206" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.5.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D205" s="23" t="inlineStr">
+      <x:c r="D206" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">主控板增加HART通信和电流输出支持</x:t>
         </x:is>
       </x:c>
-      <x:c r="E205" s="23" t="inlineStr">
+      <x:c r="E206" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠主控板接入 HART 通信。
 2.⁠完善 4-20mA 电流输出及相关接口控制。
 3.⁠同步无线滑环主机的通信处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F205" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="206" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A206" s="36" t="n">
-        <x:v>45905</x:v>
-      </x:c>
-      <x:c r="B206" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.3.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C206" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.5.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D206" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">显示板增加一体机通信</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E206" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠显示板可与一体机上位系统通信。
-2.⁠支持设备参数读取、设置和数据回复。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F206" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -7786,210 +7777,241 @@
       </x:c>
       <x:c r="C207" s="23" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V0.5.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D207" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">显示板增加一体机通信</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E207" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠显示板可与一体机上位系统通信。
+2.⁠支持设备参数读取、设置和数据回复。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F207" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="208" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A208" s="36" t="n">
+        <x:v>45905</x:v>
+      </x:c>
+      <x:c r="B208" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V0.3.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C208" s="25" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V0.4.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D207" s="23" t="inlineStr">
+      <x:c r="D208" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加4-20mA电流输出</x:t>
         </x:is>
       </x:c>
-      <x:c r="E207" s="23" t="inlineStr">
+      <x:c r="E208" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠主控板增加 4-20mA 电流输出。
 2.⁠补充电流输出和 HART 通信所需的硬件接口设置。
 3.⁠显示板增加对应的通信接口设置。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F207" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="208" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A208" s="36" t="n">
+      <x:c r="F208" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="209" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A209" s="35" t="n">
         <x:v>45903</x:v>
       </x:c>
-      <x:c r="B208" s="25" t="inlineStr">
+      <x:c r="B209" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.2.0.2</x:t>
         </x:is>
       </x:c>
-      <x:c r="C208" s="25" t="inlineStr">
+      <x:c r="C209" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.3.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D208" s="25" t="inlineStr">
+      <x:c r="D209" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">降低无线滑环主机运行频率</x:t>
         </x:is>
       </x:c>
-      <x:c r="E208" s="25" t="inlineStr">
+      <x:c r="E209" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠降低无线滑环主机运行频率，减少运行功耗。
 2.⁠同步调整主控板测量和显示板通信设置。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F208" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="209" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A209" s="35" t="n">
+      <x:c r="F209" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="210" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A210" s="36" t="n">
         <x:v>45901</x:v>
       </x:c>
-      <x:c r="B209" s="23" t="inlineStr">
+      <x:c r="B210" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.2.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C209" s="23" t="inlineStr">
+      <x:c r="C210" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.3.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D209" s="23" t="inlineStr">
+      <x:c r="D210" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">显示板启用第三路通信接口</x:t>
         </x:is>
       </x:c>
-      <x:c r="E209" s="23" t="inlineStr">
+      <x:c r="E210" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠显示板增加第三路 RS485 通信接口。
 2.⁠接入数据接收和主板通信处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F209" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="210" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A210" s="36" t="n">
+      <x:c r="F210" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="211">
+      <x:c r="A211" s="35" t="n">
         <x:v>45898</x:v>
       </x:c>
-      <x:c r="B210" s="25" t="inlineStr">
+      <x:c r="B211" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.2.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C210" s="25" t="inlineStr">
+      <x:c r="C211" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.2.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D210" s="25" t="inlineStr">
+      <x:c r="D211" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">显示板增加对外通信和罐上操作</x:t>
         </x:is>
       </x:c>
-      <x:c r="E210" s="25" t="inlineStr">
+      <x:c r="E211" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠显示板增加与上位系统的通信。
 2.⁠完善罐上操作菜单、按键和状态显示。
 3.⁠同步主控板与显示板之间的操作传递。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F210" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="211">
-      <x:c r="A211" s="35" t="n">
+      <x:c r="F211" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" t="n">
         <x:v>45876</x:v>
       </x:c>
-      <x:c r="B211" s="23" t="inlineStr">
+      <x:c r="B212" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.2.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C211" s="23" t="inlineStr">
+      <x:c r="C212" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.1.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D211" s="23" t="inlineStr">
+      <x:c r="D212" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">显示板增加菜单和主控通信</x:t>
         </x:is>
       </x:c>
-      <x:c r="E211" s="23" t="inlineStr">
+      <x:c r="E212" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠显示板增加菜单、按键和参数设置。
 2.⁠建立显示板与主控板的数据读取和操作控制。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F211" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="212">
-      <x:c r="A212" t="n">
+      <x:c r="F212" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" t="n">
         <x:v>45873</x:v>
       </x:c>
-      <x:c r="B212" t="inlineStr">
+      <x:c r="B213" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.1.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C212" t="inlineStr">
+      <x:c r="C213" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.0.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D212" t="inlineStr">
+      <x:c r="D213" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">主控板建立基础测量与故障处理</x:t>
         </x:is>
       </x:c>
-      <x:c r="E212" t="inlineStr">
+      <x:c r="E213" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠主控板增加基础测量调度和故障处理。
 2.⁠接入传感器、电机、称重和设备参数保存。
 3.⁠同步整理显示板和无线滑环相关程序。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F212" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="213">
-      <x:c r="A213" t="n">
+      <x:c r="F213" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" t="n">
         <x:v>45841</x:v>
       </x:c>
-      <x:c r="B213" t="inlineStr">
+      <x:c r="B214" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.0.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C213" t="inlineStr">
+      <x:c r="C214" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.0.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D213" t="inlineStr">
+      <x:c r="D214" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">建立首个程序基础版本</x:t>
         </x:is>
       </x:c>
-      <x:c r="E213" t="inlineStr">
+      <x:c r="E214" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠建立主控板、显示板和无线滑环主机的初始程序。
 2.⁠加入早期外围部件检查工程，作为后续开发基础。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F213" t="inlineStr">
+      <x:c r="F214" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
         </x:is>
@@ -8002,7 +8024,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46635382345b4191"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc9634e87f8f4d96"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/00_构建与版本/版本改动与测试/Ⅱ代储罐在线计量仪版本升级记录.xlsx
+++ b/docs/00_构建与版本/版本改动与测试/Ⅱ代储罐在线计量仪版本升级记录.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本改动" sheetId="1" r:id="R8c8c62ce251b4ce2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本改动" sheetId="1" r:id="Rfedd5d1d640a4cab"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1323,134 +1323,156 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="4" s="28" customFormat="1" ht="82.5" customHeight="1">
+    <x:row r="4" s="28" customFormat="1" ht="190" customHeight="1">
       <x:c r="A4" s="33" t="n">
         <x:v>46289</x:v>
       </x:c>
       <x:c r="B4" s="13" t="str">
-        <x:v>V1.45.0.0</x:v>
+        <x:v>V1.45.1.0</x:v>
       </x:c>
       <x:c r="C4" s="13" t="str">
         <x:v>V1.44.0.0</x:v>
       </x:c>
       <x:c r="D4" s="14" t="str">
+        <x:v>无线状态格式异常增加完整事务重试</x:v>
+      </x:c>
+      <x:c r="E4" s="14" t="str">
+        <x:v>1. 读取部件参数刷新无线状态遇到格式异常时，最多重新执行 3 次完整查询，每次安全结束后再重试。
+2. 连续 3 次格式异常但 UART6 已恢复透明传输时，发布无线无效快照并继续其它部件诊断，不再因单项诊断数据异常直接停止测量。
+3. RSSI 清理、退出 AT 或透明交接失败仍立即停止后续 UART6 访问，并修正故障日志，避免把内容格式错误误报为交接失败。</x:v>
+      </x:c>
+      <x:c r="F4" s="15" t="str">
+        <x:v>仅升级 CPU2，CPU3 保持 V1.44.0.0；共享协议和参数均不变、无需重设。升级后需在台架注入短帧、粘包、丢 ACK 和异步 RSSI 残留，确认重试间无串口污染。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" s="28" customFormat="1" ht="82.5" customHeight="1">
+      <x:c r="A5" s="33" t="n">
+        <x:v>46289</x:v>
+      </x:c>
+      <x:c r="B5" s="13" t="str">
+        <x:v>V1.45.0.0</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="str">
+        <x:v>V1.44.0.0</x:v>
+      </x:c>
+      <x:c r="D5" s="14" t="str">
         <x:v>维护模式成为继电器报警唯一屏蔽入口</x:v>
       </x:c>
-      <x:c r="E4" s="14" t="str">
+      <x:c r="E5" s="14" t="str">
         <x:v>1. 未进入维护时，普通或强制上下行不再自动关闭继电器报警，可继续按位置和报警条件实时动作。
 2. 进入维护后仍屏蔽四路继电器最终动作，退出维护后按当前报警条件或锁存状态恢复。
 3. 手动报警抑制字段固定为 0 兼容保留；共享协议升级到 38，双板需配套使用。</x:v>
       </x:c>
-      <x:c r="F4" s="15" t="str">
+      <x:c r="F5" s="15" t="str">
         <x:v>CPU2/CPU3 必须配套升级；参数地址和现场设置不变、无需重设。升级后需实测上下行跨阈值、维护进入/退出、物理继电器和 AO 故障电流。</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" s="28" customFormat="1" ht="82.5" customHeight="1">
-      <x:c r="A5" s="33" t="n">
+    <x:row r="6" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A6" s="33" t="n">
         <x:v>46289</x:v>
       </x:c>
-      <x:c r="B5" s="13" t="str">
+      <x:c r="B6" s="13" t="str">
         <x:v>V1.44.2.0</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="str">
+      <x:c r="C6" s="13" t="str">
         <x:v>V1.43.1.0</x:v>
       </x:c>
-      <x:c r="D5" s="14" t="str">
+      <x:c r="D6" s="14" t="str">
         <x:v>修复继电器参数非对齐访问风险</x:v>
       </x:c>
-      <x:c r="E5" s="14" t="str">
+      <x:c r="E6" s="14" t="str">
         <x:v>1. 继电器报警参数明确按 1 字节对齐，避免固件读取非对齐浮点配置时触发 HardFault 重启。
 2. 参数总大小、继电器配置位置、CRC 范围和现场保存值保持不变，升级不清参数。
 3. 增加编译期布局检查，后续布局变化会在构建阶段直接失败。</x:v>
       </x:c>
-      <x:c r="F5" s="15" t="str">
+      <x:c r="F6" s="15" t="str">
         <x:v>CPU2 PATCH 版本；CPU3 保持 V1.43.1.0。升级前记录现场继电器设置，升级后核对并实测报警输出；目标板长期运行待验证。</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A6" s="33" t="n">
+    <x:row r="7" s="28" customFormat="1" ht="16.5" customHeight="1">
+      <x:c r="A7" s="34" t="n">
         <x:v>46286</x:v>
       </x:c>
-      <x:c r="B6" s="13" t="inlineStr">
+      <x:c r="B7" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.44.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C6" s="13" t="inlineStr">
+      <x:c r="C7" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.43.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D6" s="14" t="inlineStr">
+      <x:c r="D7" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复液位跟随自动恢复重跑计数</x:t>
         </x:is>
       </x:c>
-      <x:c r="E6" s="14" t="inlineStr">
+      <x:c r="E7" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1. 液位成功进入 STATE_FLOWOIL 后，活动自动恢复上下文清零业务重跑计数。
 2. 后续再次无法进入跟随状态时，从零开始按既有上限连续计数并报警。
 3. 恢复检查失败计数、命令切换取消恢复及参数/协议保持不变。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F6" s="15" t="inlineStr">
+      <x:c r="F7" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">CPU2 PATCH 版本；目标板、传感器与现场故障恢复时序待验证。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="7" s="28" customFormat="1" ht="16.5" customHeight="1">
-      <x:c r="A7" s="34" t="n">
+    <x:row r="8" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A8" s="33" t="n">
         <x:v>46279</x:v>
       </x:c>
-      <x:c r="B7" s="17" t="inlineStr">
+      <x:c r="B8" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.44.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C7" s="17" t="inlineStr">
+      <x:c r="C8" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.43.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D7" s="18" t="inlineStr">
+      <x:c r="D8" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复外部COM长期运行后通信无响应</x:t>
         </x:is>
       </x:c>
-      <x:c r="E7" s="18" t="inlineStr">
+      <x:c r="E8" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1. 外部COM启动保护结束后锁存就绪状态，避免设备长时间运行跨计时回绕后停止处理通信。
 2. 保留原有三路串口收发和1秒启动保护，不阻塞屏幕和CPU2通信。
 3. 补充长期运行、计时回绕和发送完成恢复检查。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F7" s="19" t="inlineStr">
+      <x:c r="F8" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">CPU3修复版本；升级前确认CPU2配套版本，参数无需重设；RS485长期运行需现场验证。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="8" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A8" s="33" t="n">
+    <x:row r="9" s="28" customFormat="1" ht="82.5" customHeight="1">
+      <x:c r="A9" s="34" t="n">
         <x:v>46272</x:v>
       </x:c>
-      <x:c r="B8" s="13" t="inlineStr">
+      <x:c r="B9" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.44.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C8" s="13" t="inlineStr">
+      <x:c r="C9" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.43.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D8" s="14" t="inlineStr">
+      <x:c r="D9" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">称重探底与下行保护</x:t>
         </x:is>
       </x:c>
-      <x:c r="E8" s="14" t="inlineStr">
+      <x:c r="E9" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠探底扭力阈值改为开始检测后需要减少的重量，名称不变。
 2.⁠接近预计罐底才检测并分段减速，减少低速运行距离。
@@ -1461,32 +1483,32 @@
 7.⁠SI 分布首点必须高于探底释放位置，不再自动改写首点。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F8" s="20" t="inlineStr">
+      <x:c r="F9" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">两块板需配套升级；称重探底阈值不能为 0。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="9" s="28" customFormat="1" ht="82.5" customHeight="1">
-      <x:c r="A9" s="34" t="n">
+    <x:row r="10" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A10" s="33" t="n">
         <x:v>46272</x:v>
       </x:c>
-      <x:c r="B9" s="17" t="inlineStr">
+      <x:c r="B10" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.43.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C9" s="17" t="inlineStr">
+      <x:c r="C10" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.42.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D9" s="18" t="inlineStr">
+      <x:c r="D10" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">液位定时矫正</x:t>
         </x:is>
       </x:c>
-      <x:c r="E9" s="18" t="inlineStr">
+      <x:c r="E10" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增“定时矫正”和“矫正周期”设置。
 2.⁠设备稳定跟随液位后，可按周期重新检查找液位所用的参考频率。
@@ -1495,68 +1517,38 @@
 5.⁠矫正失败会尝试恢复，多次失败后报故障。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F9" s="19" t="inlineStr">
+      <x:c r="F10" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">两块板需配套升级；液位定时矫正升级后默认关闭。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="10" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A10" s="33" t="n">
+    <x:row r="11" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A11" s="34" t="n">
         <x:v>46270</x:v>
       </x:c>
-      <x:c r="B10" s="13" t="inlineStr">
+      <x:c r="B11" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.42.11.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C10" s="13" t="inlineStr">
+      <x:c r="C11" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.41.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D10" s="14" t="inlineStr">
+      <x:c r="D11" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复液位跟随时的丢步误报</x:t>
         </x:is>
       </x:c>
-      <x:c r="E10" s="14" t="inlineStr">
+      <x:c r="E11" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复固定频率找液位方式（方式5）换向、变速时，误报电机没有走够距离（丢步）的问题。
 2.⁠停止等待时不再按仍在运动计算，减少误报。
 3.⁠探头抖动或回退时，不重复计算前进距离。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F10" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="11" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A11" s="34" t="n">
-        <x:v>46270</x:v>
-      </x:c>
-      <x:c r="B11" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.42.10.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C11" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.41.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D11" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">新增两路常亮面板指示灯</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E11" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠新增两路面板指示灯控制，按现有接线保持常亮。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F11" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -1565,56 +1557,86 @@
     </x:row>
     <x:row r="12" s="28" customFormat="1" ht="49.5" customHeight="1">
       <x:c r="A12" s="33" t="n">
+        <x:v>46270</x:v>
+      </x:c>
+      <x:c r="B12" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.42.10.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C12" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.41.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D12" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">新增两路常亮面板指示灯</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E12" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠新增两路面板指示灯控制，按现有接线保持常亮。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F12" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="13" s="28" customFormat="1" ht="16.5" customHeight="1">
+      <x:c r="A13" s="34" t="n">
         <x:v>46269</x:v>
       </x:c>
-      <x:c r="B12" s="13" t="inlineStr">
+      <x:c r="B13" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.42.10.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C12" s="13" t="inlineStr">
+      <x:c r="C13" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D12" s="14" t="inlineStr">
+      <x:c r="D13" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">调整SI分布测量首个测点和读数等待</x:t>
         </x:is>
       </x:c>
-      <x:c r="E12" s="14" t="inlineStr">
+      <x:c r="E13" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠探底后，上提 100 mm 的停机位置直接作为第 0 测点，不再多向下走一次。
 2.⁠到达每个测点后，先切密度模式，再按设置时间等待。
 3.⁠读数为零或还不能使用时先继续等待，不立即认定探头已在空气中。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F12" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="13" s="28" customFormat="1" ht="16.5" customHeight="1">
-      <x:c r="A13" s="34" t="n">
+      <x:c r="F13" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="14" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A14" s="33" t="n">
         <x:v>46268</x:v>
       </x:c>
-      <x:c r="B13" s="17" t="inlineStr">
+      <x:c r="B14" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.42.9.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C13" s="17" t="inlineStr">
+      <x:c r="C14" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D13" s="18" t="inlineStr">
+      <x:c r="D14" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加DM4传感器通信重试和液位读数等待</x:t>
         </x:is>
       </x:c>
-      <x:c r="E13" s="18" t="inlineStr">
+      <x:c r="E14" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠DM4 传感器（V4 协议）通信失败后，允许重复发送的读取命令最多尝试 3 次。
 2.⁠液位频率为 0 时，先停机等待读数稳定。
@@ -1622,66 +1644,35 @@
 4.⁠记录失败时收到的数据，方便售后提供给研发排查。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F13" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="14" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A14" s="33" t="n">
+      <x:c r="F14" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="15" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A15" s="34" t="n">
         <x:v>46261</x:v>
       </x:c>
-      <x:c r="B14" s="13" t="inlineStr">
+      <x:c r="B15" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.42.8.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C14" s="13" t="inlineStr">
+      <x:c r="C15" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D14" s="14" t="inlineStr">
+      <x:c r="D15" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加DM4传感器通信间隔和读数不稳定提示</x:t>
         </x:is>
       </x:c>
-      <x:c r="E14" s="14" t="inlineStr">
+      <x:c r="E15" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠每次与 DM4 传感器（V4 协议）通信后，留出至少 30 毫秒间隔，避免请求过密。
 2.⁠读到负频率时，提示当前频率不稳定。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F14" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="15" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A15" s="34" t="n">
-        <x:v>46260</x:v>
-      </x:c>
-      <x:c r="B15" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.42.7.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C15" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.40.1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D15" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">修复DM4传感器读数未稳时的通信误报</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E15" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠修复 DM4 传感器（V4 协议）读数暂未稳定时，被误报为通信故障的问题。
-2.⁠传感器自动发送数据、主控请求后传感器再回复，这两种方式都按相同规则处理暂时没有有效读数的情况。</x:t>
         </x:is>
       </x:c>
       <x:c r="F15" s="19" t="inlineStr">
@@ -1696,59 +1687,60 @@
       </x:c>
       <x:c r="B16" s="13" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.42.7.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C16" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.40.1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D16" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">修复DM4传感器读数未稳时的通信误报</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E16" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠修复 DM4 传感器（V4 协议）读数暂未稳定时，被误报为通信故障的问题。
+2.⁠传感器自动发送数据、主控请求后传感器再回复，这两种方式都按相同规则处理暂时没有有效读数的情况。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F16" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="17" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A17" s="34" t="n">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="B17" s="17" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.42.6.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C16" s="13" t="inlineStr">
+      <x:c r="C17" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D16" s="14" t="inlineStr">
+      <x:c r="D17" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">区分调试版和发布版程序包</x:t>
         </x:is>
       </x:c>
-      <x:c r="E16" s="14" t="inlineStr">
+      <x:c r="E17" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠程序文件区分 DEBUG 调试版和 RELEASE 发布版。
 2.⁠调试版可接收串口调试命令，发布版不接收这些命令。
 3.⁠发布版仍保留日志发送、正常测量和业务通信。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F16" s="20" t="inlineStr">
+      <x:c r="F17" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">串口调试使用 DEBUG 包；RELEASE 包不响应调试命令。</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="17" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A17" s="34" t="n">
-        <x:v>46260</x:v>
-      </x:c>
-      <x:c r="B17" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.42.5.1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C17" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.40.1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D17" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">调整调试串口未接线时的设置</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E17" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠调整调试串口未连接设备时的输入设置。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F17" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1758,119 +1750,118 @@
       </x:c>
       <x:c r="B18" s="13" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.42.5.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C18" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.40.1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D18" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">调整调试串口未接线时的设置</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E18" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠调整调试串口未连接设备时的输入设置。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F18" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="19" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A19" s="34" t="n">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="B19" s="17" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.42.5.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C18" s="13" t="inlineStr">
+      <x:c r="C19" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D18" s="14" t="inlineStr">
+      <x:c r="D19" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复DM4传感器通信测试的冲突与误判</x:t>
         </x:is>
       </x:c>
-      <x:c r="E18" s="14" t="inlineStr">
+      <x:c r="E19" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复传感器通信测试（SC）与 DM4 传感器（V4 协议）自动发送数据互相影响的问题。
 2.⁠探头在空气中暂时测不出密度时，可仍判断通信正常。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F18" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="19" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A19" s="34" t="n">
+      <x:c r="F19" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="20" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A20" s="33" t="n">
         <x:v>46259</x:v>
       </x:c>
-      <x:c r="B19" s="17" t="inlineStr">
+      <x:c r="B20" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.42.4.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C19" s="17" t="inlineStr">
+      <x:c r="C20" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D19" s="18" t="inlineStr">
+      <x:c r="D20" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">读取部件参数前先切密度模式</x:t>
         </x:is>
       </x:c>
-      <x:c r="E19" s="18" t="inlineStr">
+      <x:c r="E20" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠读取部件参数前先切换到密度模式。
 2.⁠通信自检前也会确认密度模式，减少从液位模式切入时的误报。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F19" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="20" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A20" s="33" t="n">
+      <x:c r="F20" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="21" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A21" s="34" t="n">
         <x:v>46258</x:v>
       </x:c>
-      <x:c r="B20" s="13" t="inlineStr">
+      <x:c r="B21" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.42.3.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C20" s="13" t="inlineStr">
+      <x:c r="C21" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D20" s="14" t="inlineStr">
+      <x:c r="D21" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复运动完成误判，密度未出时等待</x:t>
         </x:is>
       </x:c>
-      <x:c r="E20" s="14" t="inlineStr">
+      <x:c r="E21" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复探头仍在连续移动，却被程序误判已完成的问题。
 2.⁠电机收到启动要求后仍不转，会停止并报错。
 3.⁠DM4 传感器在密度模式下暂时读到频率 0 时，继续等待测量结果。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F20" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="21" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A21" s="34" t="n">
-        <x:v>46255</x:v>
-      </x:c>
-      <x:c r="B21" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.42.2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C21" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.40.1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D21" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">防止把旧温度、黏度当作新读数</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E21" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠温度还未更新时，不把旧温度当作新结果。
-2.⁠黏度还未更新时，不把旧黏度当作新结果。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F21" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -1883,116 +1874,147 @@
       </x:c>
       <x:c r="B22" s="13" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.42.2.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C22" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.40.1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D22" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">防止把旧温度、黏度当作新读数</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E22" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠温度还未更新时，不把旧温度当作新结果。
+2.⁠黏度还未更新时，不把旧黏度当作新结果。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F22" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="23" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A23" s="34" t="n">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="B23" s="17" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.42.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C22" s="13" t="inlineStr">
+      <x:c r="C23" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D22" s="14" t="inlineStr">
+      <x:c r="D23" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">切换操作先停机，探底失败沿用罐高</x:t>
         </x:is>
       </x:c>
-      <x:c r="E22" s="14" t="inlineStr">
+      <x:c r="E23" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠切换操作时先停机退出，不再误记为测量故障。
 2.⁠恢复原有做法：探底失败或偏差过大时，使用已设置的罐高作为后续参考。
 3.⁠统一液位、水位变化后电流数据的更新。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F22" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="23" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A23" s="34" t="n">
+      <x:c r="F23" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="24" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A24" s="33" t="n">
         <x:v>46253</x:v>
       </x:c>
-      <x:c r="B23" s="17" t="inlineStr">
+      <x:c r="B24" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.42.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C23" s="17" t="inlineStr">
+      <x:c r="C24" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D23" s="18" t="inlineStr">
+      <x:c r="D24" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增多参数传感器参数修改与读回确认</x:t>
         </x:is>
       </x:c>
-      <x:c r="E23" s="18" t="inlineStr">
+      <x:c r="E24" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增通过调试串口修改多参数传感器（V3/V4 协议）参数的命令。
 2.⁠修改后重新读取，确认实际值。
 3.⁠DM4 传感器（V4 协议）只允许在识别成功、通信方式正确时修改指定范围的参数。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F23" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="24" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A24" s="33" t="n">
+      <x:c r="F24" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="25" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A25" s="34" t="n">
         <x:v>46253</x:v>
       </x:c>
-      <x:c r="B24" s="13" t="inlineStr">
+      <x:c r="B25" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.41.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C24" s="13" t="inlineStr">
+      <x:c r="C25" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D24" s="14" t="inlineStr">
+      <x:c r="D25" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">滑环匹配完成前先确认传感器</x:t>
         </x:is>
       </x:c>
-      <x:c r="E24" s="14" t="inlineStr">
+      <x:c r="E25" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠无线滑环连上后，继续检查传感器类型和编号，全部识别成功才显示匹配完成。
 2.⁠修复识别不采用 V4 协议的传感器时，短暂误报 13-3 的问题。
 3.⁠无法确认传感器时，测量前会重新识别。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F24" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="25" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A25" s="34" t="n">
+      <x:c r="F25" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="26" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A26" s="33" t="n">
         <x:v>46252</x:v>
       </x:c>
-      <x:c r="B25" s="17" t="inlineStr">
+      <x:c r="B26" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.41.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C25" s="17" t="inlineStr">
+      <x:c r="C26" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D25" s="18" t="inlineStr">
+      <x:c r="D26" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">改善DM4传感器无线连接并增加测试命令</x:t>
         </x:is>
       </x:c>
-      <x:c r="E25" s="18" t="inlineStr">
+      <x:c r="E26" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增 DM4 传感器（V4 协议）的通信、模式和参数测试命令。
 2.⁠改善 DM4 传感器通过无线滑环连接时的识别和数据接收。
@@ -2000,133 +2022,102 @@
 4.⁠增加丢失数据和错误数据的记录，方便排查。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F25" s="19" t="inlineStr">
+      <x:c r="F26" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">测水操作与磁零点检测不能同时开启。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="26" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A26" s="33" t="n">
+    <x:row r="27" s="28" customFormat="1" ht="16.5" customHeight="1">
+      <x:c r="A27" s="34" t="n">
         <x:v>46251</x:v>
       </x:c>
-      <x:c r="B26" s="13" t="inlineStr">
+      <x:c r="B27" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C26" s="13" t="inlineStr">
+      <x:c r="C27" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D26" s="14" t="inlineStr">
+      <x:c r="D27" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复屏幕残影和确认键多按一次</x:t>
         </x:is>
       </x:c>
-      <x:c r="E26" s="14" t="inlineStr">
+      <x:c r="E27" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复屏幕异常恢复后可能留下旧画面或残影的问题。
 2.⁠限制连续恢复次数，避免一直反复重启屏幕。
 3.⁠修复操作确认页还需额外多按一次确认的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F26" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="27" s="28" customFormat="1" ht="16.5" customHeight="1">
-      <x:c r="A27" s="34" t="n">
+      <x:c r="F27" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="28" s="28" customFormat="1" ht="16.5" customHeight="1">
+      <x:c r="A28" s="33" t="n">
         <x:v>46251</x:v>
       </x:c>
-      <x:c r="B27" s="17" t="inlineStr">
+      <x:c r="B28" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C27" s="17" t="inlineStr">
+      <x:c r="C28" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D27" s="18" t="inlineStr">
+      <x:c r="D28" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">液位跟随支持更细的低速调整</x:t>
         </x:is>
       </x:c>
-      <x:c r="E27" s="18" t="inlineStr">
+      <x:c r="E28" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠固定频率找液位方式（方式5）跟随液位时，可更慢、更细地调整速度。
 2.⁠改变方向前先慢停，减少低速阶段误报丢步。
 3.⁠关闭电流输出后，不再继续操作电流输出硬件。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F27" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="28" s="28" customFormat="1" ht="16.5" customHeight="1">
-      <x:c r="A28" s="33" t="n">
+      <x:c r="F28" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="29" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A29" s="34" t="n">
         <x:v>46248</x:v>
       </x:c>
-      <x:c r="B28" s="13" t="inlineStr">
+      <x:c r="B29" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C28" s="13" t="inlineStr">
+      <x:c r="C29" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.40.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D28" s="14" t="inlineStr">
+      <x:c r="D29" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加位置异常检查与故障提示</x:t>
         </x:is>
       </x:c>
-      <x:c r="E28" s="14" t="inlineStr">
+      <x:c r="E29" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加上电位置变化检查，发现保存位置与当前情况不符时提示故障。
 2.⁠运行中位置突然跳变时，增加检查和保护。
 3.⁠完善位置保存和掉电保存，屏幕增加相关故障原因。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F28" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="29" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A29" s="34" t="n">
-        <x:v>46247</x:v>
-      </x:c>
-      <x:c r="B29" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.39.2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C29" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.39.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D29" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">新增协议查询，减少连接选错</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E29" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠新增查询当前通信协议的功能。
-2.⁠与设备连接的电脑或控制系统可据此识别设备，减少自动连接时选错协议。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F29" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -2144,60 +2135,61 @@
       </x:c>
       <x:c r="C30" s="13" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.39.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D30" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">新增协议查询，减少连接选错</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E30" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠新增查询当前通信协议的功能。
+2.⁠与设备连接的电脑或控制系统可据此识别设备，减少自动连接时选错协议。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F30" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="31" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A31" s="34" t="n">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="B31" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.39.2.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C31" s="17" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.38.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D30" s="14" t="inlineStr">
+      <x:c r="D31" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修正固定频率找液位的方向和停点</x:t>
         </x:is>
       </x:c>
-      <x:c r="E30" s="14" t="inlineStr">
+      <x:c r="E31" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修正固定频率找液位方式（方式5）根据设定频率选择移动方向和速度的处理。
 2.⁠找到液体后，不再固定多向下走 100 mm。
 3.⁠到达低液位盲区时停止下行，避免继续向下找。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F30" s="20" t="inlineStr">
+      <x:c r="F31" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">升级后核对固定频率找液位的频率和阈值设置。</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="31" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A31" s="34" t="n">
-        <x:v>46247</x:v>
-      </x:c>
-      <x:c r="B31" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.39.1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C31" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.38.2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D31" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">减少两块板命令过密造成的通信异常</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E31" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠连续查询或操作之间增加必要间隔，减少命令发得过密造成的通信异常。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F31" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="32" s="28" customFormat="1" ht="66" customHeight="1">
       <x:c r="A32" s="33" t="n">
-        <x:v>46246</x:v>
+        <x:v>46247</x:v>
       </x:c>
       <x:c r="B32" s="13" t="inlineStr">
         <x:is>
@@ -2206,17 +2198,17 @@
       </x:c>
       <x:c r="C32" s="13" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">V1.38.1.1</x:t>
+          <x:t xml:space="preserve">V1.38.2.0</x:t>
         </x:is>
       </x:c>
       <x:c r="D32" s="14" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">显示文字整理</x:t>
+          <x:t xml:space="preserve">减少两块板命令过密造成的通信异常</x:t>
         </x:is>
       </x:c>
       <x:c r="E32" s="14" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.⁠整理重复的显示文字数据，节省程序空间，文字外观不变。</x:t>
+          <x:t xml:space="preserve">1.⁠连续查询或操作之间增加必要间隔，减少命令发得过密造成的通信异常。</x:t>
         </x:is>
       </x:c>
       <x:c r="F32" s="20" t="inlineStr">
@@ -2227,120 +2219,150 @@
     </x:row>
     <x:row r="33" s="28" customFormat="1" ht="49.5" customHeight="1">
       <x:c r="A33" s="34" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="B33" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.39.1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C33" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.38.1.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D33" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">显示文字整理</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E33" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠整理重复的显示文字数据，节省程序空间，文字外观不变。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F33" s="21" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="34" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A34" s="33" t="n">
         <x:v>46245</x:v>
       </x:c>
-      <x:c r="B33" s="17" t="inlineStr">
+      <x:c r="B34" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.39.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C33" s="17" t="inlineStr">
+      <x:c r="C34" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.38.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D33" s="18" t="inlineStr">
+      <x:c r="D34" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修正传感器识别并统一故障名称</x:t>
         </x:is>
       </x:c>
-      <x:c r="E33" s="18" t="inlineStr">
+      <x:c r="E34" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修正多参数传感器（V3/V4 协议）和 DSM 传感器的识别顺序及编号判断。
 2.⁠识别完 DM4 传感器（V4 协议）后，恢复原来的通信方式。
 3.⁠统一 49 项屏幕、日志和故障表的名称。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F33" s="21" t="inlineStr">
+      <x:c r="F34" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">编号为 0 的 DM4 传感器需使用后续版本。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="34" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A34" s="33" t="n">
+    <x:row r="35" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A35" s="34" t="n">
         <x:v>46244</x:v>
       </x:c>
-      <x:c r="B34" s="13" t="inlineStr">
+      <x:c r="B35" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.39.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C34" s="13" t="inlineStr">
+      <x:c r="C35" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.38.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D34" s="14" t="inlineStr">
+      <x:c r="D35" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">提高电流微调精度，补齐DM4传感器读数</x:t>
         </x:is>
       </x:c>
-      <x:c r="E34" s="14" t="inlineStr">
+      <x:c r="E35" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠电流修正可以精细到 0.001 mA，屏幕显示三位小数。
 2.⁠读取 DM4 传感器（V4 协议）数据前先检查测量模式，减少模式不对时的错误读数。
 3.⁠补齐水电容、姿态、黏度等读取。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F34" s="20" t="inlineStr">
+      <x:c r="F35" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">两块板及连接的电脑或控制系统需配套；旧电流修正值会自动换算。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="35" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A35" s="34" t="n">
+    <x:row r="36" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A36" s="33" t="n">
         <x:v>46242</x:v>
       </x:c>
-      <x:c r="B35" s="17" t="inlineStr">
+      <x:c r="B36" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.38.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C35" s="17" t="inlineStr">
+      <x:c r="C36" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.37.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D35" s="18" t="inlineStr">
+      <x:c r="D36" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增DSM传感器版本及更多部件信息查询</x:t>
         </x:is>
       </x:c>
-      <x:c r="E35" s="18" t="inlineStr">
+      <x:c r="E36" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加 DSM 传感器版本识别。
 2.⁠读取部件参数时，增加供电电压、黏度等信息。
 3.⁠附加信息读不到时，不阻断原有主要参数读取。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F35" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="36" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A36" s="33" t="n">
+      <x:c r="F36" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="37" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A37" s="34" t="n">
         <x:v>46242</x:v>
       </x:c>
-      <x:c r="B36" s="13" t="inlineStr">
+      <x:c r="B37" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.37.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C36" s="13" t="inlineStr">
+      <x:c r="C37" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.37.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D36" s="14" t="inlineStr">
+      <x:c r="D37" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增DM4传感器（V4协议）支持</x:t>
         </x:is>
       </x:c>
-      <x:c r="E36" s="14" t="inlineStr">
+      <x:c r="E37" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增 DM4 传感器（V4 协议）支持，屏幕类型名称为“多参数V4”。
 2.⁠支持传感器自动发送数据，也支持主控请求后传感器再回复。
@@ -2348,129 +2370,98 @@
 4.⁠部分纯运动操作在传感器离线时也可执行。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F36" s="20" t="inlineStr">
+      <x:c r="F37" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">退回旧程序前，先将传感器参数 65（发送方式）改为“交互方式”，并改回旧程序支持的传感器类型。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="37" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A37" s="34" t="n">
+    <x:row r="38" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A38" s="33" t="n">
         <x:v>46241</x:v>
       </x:c>
-      <x:c r="B37" s="17" t="inlineStr">
+      <x:c r="B38" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.36.4.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C37" s="17" t="inlineStr">
+      <x:c r="C38" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.36.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D37" s="18" t="inlineStr">
+      <x:c r="D38" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复DSM传感器通信误报和异常倾角显示</x:t>
         </x:is>
       </x:c>
-      <x:c r="E37" s="18" t="inlineStr">
+      <x:c r="E38" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复收到完整传感器回复，却误报数据不完整或通信错误的问题。
 2.⁠查完蓝牙状态后，确认传感器通信已恢复再继续测量。
 3.⁠传感器返回的错误提示值，不再显示成真实倾角。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F37" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="38" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A38" s="33" t="n">
+      <x:c r="F38" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="39" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A39" s="34" t="n">
         <x:v>46241</x:v>
       </x:c>
-      <x:c r="B38" s="13" t="inlineStr">
+      <x:c r="B39" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.36.3.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C38" s="13" t="inlineStr">
+      <x:c r="C39" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.36.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D38" s="14" t="inlineStr">
+      <x:c r="D39" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复长距离低速移动过早报超时</x:t>
         </x:is>
       </x:c>
-      <x:c r="E38" s="14" t="inlineStr">
+      <x:c r="E39" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复低速、长距离移动还没到目标，就在 1 小时被判超时的问题。
 2.⁠按实际距离和速度安排允许时间，日志可查看已用时间和允许时间。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F38" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="39" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A39" s="34" t="n">
+      <x:c r="F39" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="40" s="28" customFormat="1" ht="82.5" customHeight="1">
+      <x:c r="A40" s="33" t="n">
         <x:v>46238</x:v>
       </x:c>
-      <x:c r="B39" s="17" t="inlineStr">
+      <x:c r="B40" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.36.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C39" s="17" t="inlineStr">
+      <x:c r="C40" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.36.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D39" s="18" t="inlineStr">
+      <x:c r="D40" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">液位标定后同步调整电流量程</x:t>
         </x:is>
       </x:c>
-      <x:c r="E39" s="18" t="inlineStr">
+      <x:c r="E40" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠液位标定改变罐高后，电流量程会相应调整，不超过新罐高。
 2.⁠修复旧量程影响电流输出或阻止后续修改参数的问题。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F39" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="40" s="28" customFormat="1" ht="82.5" customHeight="1">
-      <x:c r="A40" s="33" t="n">
-        <x:v>46232</x:v>
-      </x:c>
-      <x:c r="B40" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.36.1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C40" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.36.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D40" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">修复蓝牙查询干扰传感器通信</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E40" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠修复查完蓝牙信号后，残留回复干扰传感器通信的问题。
-2.⁠查询中途被新操作打断时，也会恢复传感器通信。</x:t>
         </x:is>
       </x:c>
       <x:c r="F40" s="20" t="inlineStr">
@@ -2485,20 +2476,51 @@
       </x:c>
       <x:c r="B41" s="17" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.36.1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C41" s="17" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.36.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C41" s="17" t="inlineStr">
+      <x:c r="D41" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">修复蓝牙查询干扰传感器通信</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E41" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠修复查完蓝牙信号后，残留回复干扰传感器通信的问题。
+2.⁠查询中途被新操作打断时，也会恢复传感器通信。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F41" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="42" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A42" s="33" t="n">
+        <x:v>46232</x:v>
+      </x:c>
+      <x:c r="B42" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.36.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D41" s="18" t="inlineStr">
+      <x:c r="C42" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.36.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D42" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增扭力温度显示，修正标定保存</x:t>
         </x:is>
       </x:c>
-      <x:c r="E41" s="18" t="inlineStr">
+      <x:c r="E42" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠读取部件参数、获取空载或满载扭力时，可查看扭力模块温度。
 2.⁠收到错误的扭力数据时，不再当作通信恢复正常。
@@ -2506,32 +2528,32 @@
 4.⁠罐高标定完成规定动作后，才保存新罐高。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F41" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="42" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A42" s="33" t="n">
+      <x:c r="F42" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="43" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A43" s="34" t="n">
         <x:v>46231</x:v>
       </x:c>
-      <x:c r="B42" s="13" t="inlineStr">
+      <x:c r="B43" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.35.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C42" s="13" t="inlineStr">
+      <x:c r="C43" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.35.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D42" s="14" t="inlineStr">
+      <x:c r="D43" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加低电压停机和位置保护</x:t>
         </x:is>
       </x:c>
-      <x:c r="E42" s="14" t="inlineStr">
+      <x:c r="E43" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加 24 V 供电检查，电压过低时禁止运动并尝试保存位置。
 2.⁠供电检测异常后，设备会有限次数地尝试恢复。
@@ -2539,32 +2561,32 @@
 4.⁠增加供电故障的屏幕提示。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F42" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="43" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A43" s="34" t="n">
+      <x:c r="F43" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="44" s="28" customFormat="1" ht="132" customHeight="1">
+      <x:c r="A44" s="33" t="n">
         <x:v>46228</x:v>
       </x:c>
-      <x:c r="B43" s="17" t="inlineStr">
+      <x:c r="B44" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.34.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C43" s="17" t="inlineStr">
+      <x:c r="C44" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.34.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D43" s="18" t="inlineStr">
+      <x:c r="D44" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">调整故障编号并提高密度允许上限</x:t>
         </x:is>
       </x:c>
-      <x:c r="E43" s="18" t="inlineStr">
+      <x:c r="E44" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠调整扭力、电流输出等故障的编号和分类。
 2.⁠密度允许上限从 2000.0 调整为 3000.0 kg/m3。
@@ -2572,32 +2594,32 @@
 4.⁠减少上电显示等待，改善外部通信启动。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F43" s="19" t="inlineStr">
+      <x:c r="F44" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">两块板需配套，并使用对应版本的故障代码表。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="44" s="28" customFormat="1" ht="132" customHeight="1">
-      <x:c r="A44" s="33" t="n">
+    <x:row r="45" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A45" s="34" t="n">
         <x:v>46228</x:v>
       </x:c>
-      <x:c r="B44" s="13" t="inlineStr">
+      <x:c r="B45" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.33.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C44" s="13" t="inlineStr">
+      <x:c r="C45" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.33.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D44" s="14" t="inlineStr">
+      <x:c r="D45" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">防止测量目标被改，检查报警设置</x:t>
         </x:is>
       </x:c>
-      <x:c r="E44" s="14" t="inlineStr">
+      <x:c r="E45" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠测量开始后固定使用本次输入的目标，后续修改不会改变正在测量的目标。
 2.⁠自动恢复重测也使用本次目标。
@@ -2605,32 +2627,32 @@
 4.⁠参数更新期间，其他可用的状态数据可以继续读取。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F44" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="45" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A45" s="34" t="n">
+      <x:c r="F45" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="46" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A46" s="33" t="n">
         <x:v>46226</x:v>
       </x:c>
-      <x:c r="B45" s="17" t="inlineStr">
+      <x:c r="B46" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.32.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C45" s="17" t="inlineStr">
+      <x:c r="C46" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.32.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D45" s="18" t="inlineStr">
+      <x:c r="D46" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增液位测试，修复区间测量结果</x:t>
         </x:is>
       </x:c>
-      <x:c r="E45" s="18" t="inlineStr">
+      <x:c r="E46" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增固定频率找液位测试命令（LF）。
 2.⁠修复区间测点数量计算错误的问题。
@@ -2638,64 +2660,64 @@
 4.⁠传感器内部出错时，明确返回故障。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F45" s="19" t="inlineStr">
+      <x:c r="F46" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">LH 通信接口的“读线圈”固定返回全 0，不能用于判断实际开关状态。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="46" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A46" s="33" t="n">
+    <x:row r="47" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A47" s="34" t="n">
         <x:v>46226</x:v>
       </x:c>
-      <x:c r="B46" s="13" t="inlineStr">
+      <x:c r="B47" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.31.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C46" s="13" t="inlineStr">
+      <x:c r="C47" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.31.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D46" s="14" t="inlineStr">
+      <x:c r="D47" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">测量期间限制修改设备设置</x:t>
         </x:is>
       </x:c>
-      <x:c r="E46" s="14" t="inlineStr">
+      <x:c r="E47" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠测量或自动恢复期间，不允许修改普通设备设置。
 2.⁠设备停在故障状态且没有继续执行任务时，可以修正参数。
 3.⁠调整程序运行监测，缩短检查间隔。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F46" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="47" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A47" s="34" t="n">
+      <x:c r="F47" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="48" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A48" s="33" t="n">
         <x:v>46226</x:v>
       </x:c>
-      <x:c r="B47" s="17" t="inlineStr">
+      <x:c r="B48" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.31.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C47" s="17" t="inlineStr">
+      <x:c r="C48" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.31.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D47" s="18" t="inlineStr">
+      <x:c r="D48" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增屏幕维护操作和报警清除</x:t>
         </x:is>
       </x:c>
-      <x:c r="E47" s="18" t="inlineStr">
+      <x:c r="E48" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠屏幕可进入、退出维护模式。
 2.⁠屏幕可清除全部继电器锁存报警，即报警条件消失后仍保持的报警。
@@ -2703,32 +2725,32 @@
 4.⁠继电器页可查看是否禁止动作，以及程序要求的最终动作。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F47" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="48" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A48" s="33" t="n">
+      <x:c r="F48" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="49" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A49" s="34" t="n">
         <x:v>46225</x:v>
       </x:c>
-      <x:c r="B48" s="13" t="inlineStr">
+      <x:c r="B49" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.31.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C48" s="13" t="inlineStr">
+      <x:c r="C49" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.30.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D48" s="14" t="inlineStr">
+      <x:c r="D49" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增LH通信接口及电流、报警维护操作</x:t>
         </x:is>
       </x:c>
-      <x:c r="E48" s="14" t="inlineStr">
+      <x:c r="E49" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增 LH 通信接口。
 2.⁠新增电流修正操作。
@@ -2738,64 +2760,64 @@
 6.⁠调整通信地址。LTD 通信接口默认改为波特率 4800、8 位数据、无校验、1 位停止（4800 8N1）。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F48" s="20" t="inlineStr">
+      <x:c r="F49" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">两块板需配套升级；升级后核对 LTD 通信接口地址和波特率。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="49" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A49" s="34" t="n">
+    <x:row r="50" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A50" s="33" t="n">
         <x:v>46224</x:v>
       </x:c>
-      <x:c r="B49" s="17" t="inlineStr">
+      <x:c r="B50" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.30.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C49" s="17" t="inlineStr">
+      <x:c r="C50" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.29.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D49" s="18" t="inlineStr">
+      <x:c r="D50" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复通信数据异常导致设备卡住</x:t>
         </x:is>
       </x:c>
-      <x:c r="E49" s="18" t="inlineStr">
+      <x:c r="E50" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复连续收到大量数据或错误数据后，设备可能卡住不响应的问题。
 2.⁠通信异常的端口会单独尝试恢复。
 3.⁠收到过长或不完整的数据时，丢弃后重新接收。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F49" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="50" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A50" s="33" t="n">
+      <x:c r="F50" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="51" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A51" s="34" t="n">
         <x:v>46223</x:v>
       </x:c>
-      <x:c r="B50" s="13" t="inlineStr">
+      <x:c r="B51" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.30.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C50" s="13" t="inlineStr">
+      <x:c r="C51" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.29.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D50" s="14" t="inlineStr">
+      <x:c r="D51" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增水位设置项并调整菜单操作</x:t>
         </x:is>
       </x:c>
-      <x:c r="E50" s="14" t="inlineStr">
+      <x:c r="E51" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增“水位滞后时间”设置项。
 2.⁠进入菜单的长按确认时间改为约 3 秒。
@@ -2803,95 +2825,95 @@
 4.⁠更新液位频率、水位电容和 SI 分布测量第一个测点的部分出厂默认值。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F50" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="51" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A51" s="34" t="n">
+      <x:c r="F51" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="52" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A52" s="33" t="n">
         <x:v>46221</x:v>
       </x:c>
-      <x:c r="B51" s="17" t="inlineStr">
+      <x:c r="B52" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.29.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C51" s="17" t="inlineStr">
+      <x:c r="C52" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.28.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D51" s="18" t="inlineStr">
+      <x:c r="D52" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复测量完成后结果仍旧或不全</x:t>
         </x:is>
       </x:c>
-      <x:c r="E51" s="18" t="inlineStr">
+      <x:c r="E52" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复已显示测量完成，但测点还是旧数据或没有收齐的问题。
 2.⁠结果传输失败后可以重试，成功后清除对应传输故障。
 3.⁠输出调试日志时，减少对正常通信的影响。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F51" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="52" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A52" s="33" t="n">
+      <x:c r="F52" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="53" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A53" s="34" t="n">
         <x:v>46220</x:v>
       </x:c>
-      <x:c r="B52" s="13" t="inlineStr">
+      <x:c r="B53" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.29.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C52" s="13" t="inlineStr">
+      <x:c r="C53" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.27.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D52" s="14" t="inlineStr">
+      <x:c r="D53" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">等待读数时保持电流，增加通信统计</x:t>
         </x:is>
       </x:c>
-      <x:c r="E52" s="14" t="inlineStr">
+      <x:c r="E53" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠重新找液位、切换操作或读数暂未稳定时，保持上次正常过程电流。
 2.⁠屏幕增加主控通信次数、失败比例和失败原因，方便检查连接。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F52" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="53" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A53" s="34" t="n">
+      <x:c r="F53" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="54" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A54" s="33" t="n">
         <x:v>46219</x:v>
       </x:c>
-      <x:c r="B53" s="17" t="inlineStr">
+      <x:c r="B54" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.28.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C53" s="17" t="inlineStr">
+      <x:c r="C54" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.26.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D53" s="18" t="inlineStr">
+      <x:c r="D54" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加故障电流选择，修复通信提示</x:t>
         </x:is>
       </x:c>
-      <x:c r="E53" s="18" t="inlineStr">
+      <x:c r="E54" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠电流故障时可选择输出设定的故障电流，或保持上次正常电流。
 2.⁠修复两块板程序不匹配时一直显示“通信尝试”的问题。
@@ -2899,32 +2921,32 @@
 4.⁠设备重启后，不继续使用重启前的旧测点。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F53" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="54" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A54" s="33" t="n">
+      <x:c r="F54" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="55" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A55" s="34" t="n">
         <x:v>46219</x:v>
       </x:c>
-      <x:c r="B54" s="13" t="inlineStr">
+      <x:c r="B55" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.27.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C54" s="13" t="inlineStr">
+      <x:c r="C55" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.25.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D54" s="14" t="inlineStr">
+      <x:c r="D55" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">扩展电流输出设置，防止混入旧结果</x:t>
         </x:is>
       </x:c>
-      <x:c r="E54" s="14" t="inlineStr">
+      <x:c r="E55" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠电流输出可设置测量来源、固定电流、变化快慢、故障动作和模拟测试。
 2.⁠修复固定点结果中混入不同次测量数据的问题。
@@ -2932,32 +2954,32 @@
 4.⁠自动恢复后，只有真正测量成功才记录“重试成功”。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F54" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="55" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A55" s="34" t="n">
+      <x:c r="F55" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="56" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A56" s="33" t="n">
         <x:v>46218</x:v>
       </x:c>
-      <x:c r="B55" s="17" t="inlineStr">
+      <x:c r="B56" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.26.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C55" s="17" t="inlineStr">
+      <x:c r="C56" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.24.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D55" s="18" t="inlineStr">
+      <x:c r="D56" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修正SI分布测量完成时机及新旧结果混用</x:t>
         </x:is>
       </x:c>
-      <x:c r="E55" s="18" t="inlineStr">
+      <x:c r="E56" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠SI 分布测量测完各点后，先回到液面并停稳，再显示测量完成。
 2.⁠取消或失败时，不把本轮结果当作完整结果。
@@ -2965,128 +2987,128 @@
 4.⁠完善跨日自动测量及站 2 通信兼容。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F55" s="19" t="inlineStr">
+      <x:c r="F56" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">升级前记录 SI 分布测量和串口通信设置；该版本存在旧设置保存失败风险。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="56" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A56" s="33" t="n">
+    <x:row r="57" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A57" s="34" t="n">
         <x:v>46217</x:v>
       </x:c>
-      <x:c r="B56" s="13" t="inlineStr">
+      <x:c r="B57" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.25.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C56" s="13" t="inlineStr">
+      <x:c r="C57" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.23.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D56" s="14" t="inlineStr">
+      <x:c r="D57" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">重新编排故障编号和中文原因</x:t>
         </x:is>
       </x:c>
-      <x:c r="E56" s="14" t="inlineStr">
+      <x:c r="E57" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠按二代设备的部件重新整理故障编号。
 2.⁠补充中文故障原因，日志与屏幕使用相同名称。
 3.⁠删除重复或已被更具体原因替代的故障项。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F56" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="57" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A57" s="34" t="n">
+      <x:c r="F57" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="58" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A58" s="33" t="n">
         <x:v>46216</x:v>
       </x:c>
-      <x:c r="B57" s="17" t="inlineStr">
+      <x:c r="B58" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.24.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C57" s="17" t="inlineStr">
+      <x:c r="C58" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.22.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D57" s="18" t="inlineStr">
+      <x:c r="D58" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增安全传感器支持并兼容旧类型</x:t>
         </x:is>
       </x:c>
-      <x:c r="E57" s="18" t="inlineStr">
+      <x:c r="E58" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增安全传感器的识别、测量和参数读取。
 2.⁠仍可识别原有 DSM 传感器、LTD 传感器（V2 协议）。
 3.⁠传感器不支持某些附加功能时，不再因此阻断原有测量。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F57" s="19" t="inlineStr">
+      <x:c r="F58" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">退回旧程序前，先改回旧程序支持的传感器类型。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="58" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A58" s="33" t="n">
+    <x:row r="59" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A59" s="34" t="n">
         <x:v>46215</x:v>
       </x:c>
-      <x:c r="B58" s="13" t="inlineStr">
+      <x:c r="B59" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.23.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C58" s="13" t="inlineStr">
+      <x:c r="C59" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.22.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D58" s="14" t="inlineStr">
+      <x:c r="D59" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">细分故障原因，支持远程切换协议</x:t>
         </x:is>
       </x:c>
-      <x:c r="E58" s="14" t="inlineStr">
+      <x:c r="E59" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠故障原因分类更细，方便区分电机、传感器、存储和电流输出问题。
 2.⁠减少同一故障反复刷日志。
 3.⁠可由外部设备切换通信协议，保存失败会提示并恢复原设置。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F58" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="59" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A59" s="34" t="n">
+      <x:c r="F59" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="60" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A60" s="33" t="n">
         <x:v>46214</x:v>
       </x:c>
-      <x:c r="B59" s="17" t="inlineStr">
+      <x:c r="B60" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.22.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C59" s="17" t="inlineStr">
+      <x:c r="C60" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.21.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D59" s="18" t="inlineStr">
+      <x:c r="D60" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">支持通过LTD通信接口查询数据和设置参数</x:t>
         </x:is>
       </x:c>
-      <x:c r="E59" s="18" t="inlineStr">
+      <x:c r="E60" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠LTD 通信接口可以查询测量数据、读取和修改参数。
 2.⁠主控确认接收参数后，才回复修改成功。
@@ -3094,32 +3116,32 @@
 4.⁠新增停止、版本、状态和故障查询命令。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F59" s="19" t="inlineStr">
+      <x:c r="F60" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">原设置为 LTD 通信协议的端口，升级后会开始回复数据；需核对连接设备设置。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="60" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A60" s="33" t="n">
+    <x:row r="61" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A61" s="34" t="n">
         <x:v>46213</x:v>
       </x:c>
-      <x:c r="B60" s="13" t="inlineStr">
+      <x:c r="B61" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.21.6.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C60" s="13" t="inlineStr">
+      <x:c r="C61" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.20.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D60" s="14" t="inlineStr">
+      <x:c r="D61" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复上电通信等待和操作误报成功</x:t>
         </x:is>
       </x:c>
-      <x:c r="E60" s="14" t="inlineStr">
+      <x:c r="E61" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复蓝牙持续收数据时，设备上电一直等待的问题。
 2.⁠修复传感器低电压回复被误认成编号错误的问题。
@@ -3127,69 +3149,38 @@
 4.⁠通信恢复后重新读取设备数据，避免显示断线前的旧数据。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F60" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="61" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A61" s="34" t="n">
+      <x:c r="F61" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="62" s="28" customFormat="1" ht="82.5" customHeight="1">
+      <x:c r="A62" s="33" t="n">
         <x:v>46211</x:v>
       </x:c>
-      <x:c r="B61" s="17" t="inlineStr">
+      <x:c r="B62" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.21.5.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C61" s="17" t="inlineStr">
+      <x:c r="C62" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.19.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D61" s="18" t="inlineStr">
+      <x:c r="D62" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">电流环重接后自动恢复输出</x:t>
         </x:is>
       </x:c>
-      <x:c r="E61" s="18" t="inlineStr">
+      <x:c r="E62" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠电流环断开后重新接上，设备会定期尝试恢复输出。
 2.⁠恢复成功后回到有效目标电流，不再继续输出故障电流。
 3.⁠电流输出故障单独记录，不再由后台检查直接中断整机测量。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F61" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="62" s="28" customFormat="1" ht="82.5" customHeight="1">
-      <x:c r="A62" s="33" t="n">
-        <x:v>46211</x:v>
-      </x:c>
-      <x:c r="B62" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.21.4.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C62" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.19.1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D62" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">修复长距离运行时探头越来越慢</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E62" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠修复编码轮方式下，探头长距离分段运行后越来越慢的问题。
-2.⁠修改速度、恢复速度和切换慢速时，也使用正确的尺带长度。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F62" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -3202,115 +3193,146 @@
       </x:c>
       <x:c r="B63" s="17" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.21.4.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C63" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.19.1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D63" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">修复长距离运行时探头越来越慢</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E63" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠修复编码轮方式下，探头长距离分段运行后越来越慢的问题。
+2.⁠修改速度、恢复速度和切换慢速时，也使用正确的尺带长度。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F63" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="64" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A64" s="33" t="n">
+        <x:v>46211</x:v>
+      </x:c>
+      <x:c r="B64" s="13" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.21.3.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C63" s="17" t="inlineStr">
+      <x:c r="C64" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.19.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D63" s="18" t="inlineStr">
+      <x:c r="D64" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">减少液位短时波动引起的反复动作</x:t>
         </x:is>
       </x:c>
-      <x:c r="E63" s="18" t="inlineStr">
+      <x:c r="E64" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠方式 0/1 等液位变化持续一段时间后再动作，减少短时波动影响。
 2.⁠重新找液位期间，屏幕仍显示跟随状态。
 3.⁠调整固定频率找液位方式（方式5）的运行方法。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F63" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="64" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A64" s="33" t="n">
+      <x:c r="F64" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="65" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A65" s="34" t="n">
         <x:v>46209</x:v>
       </x:c>
-      <x:c r="B64" s="13" t="inlineStr">
+      <x:c r="B65" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.21.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C64" s="13" t="inlineStr">
+      <x:c r="C65" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.19.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D64" s="14" t="inlineStr">
+      <x:c r="D65" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SI分布测量完成后自动返回液位跟随</x:t>
         </x:is>
       </x:c>
-      <x:c r="E64" s="14" t="inlineStr">
+      <x:c r="E65" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠SI 分布测量成功后，自动找液位并继续跟随。
 2.⁠测量中途收到新操作时，优先执行新操作。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F64" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="65" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A65" s="34" t="n">
+      <x:c r="F65" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="66" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A66" s="33" t="n">
         <x:v>46205</x:v>
       </x:c>
-      <x:c r="B65" s="17" t="inlineStr">
+      <x:c r="B66" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.21.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C65" s="17" t="inlineStr">
+      <x:c r="C66" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.19.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D65" s="18" t="inlineStr">
+      <x:c r="D66" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修正SI分布测量的测点位置和空气点判断</x:t>
         </x:is>
       </x:c>
-      <x:c r="E65" s="18" t="inlineStr">
+      <x:c r="E66" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复 SI 分布测量第一个测点的位置多加了一次罐底位置的问题。
 2.⁠后续测点按实际位置上报。
 3.⁠调整空气点的判断顺序，减少误报。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F65" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="66" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A66" s="33" t="n">
+      <x:c r="F66" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="67" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A67" s="34" t="n">
         <x:v>46204</x:v>
       </x:c>
-      <x:c r="B66" s="13" t="inlineStr">
+      <x:c r="B67" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.21.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C66" s="13" t="inlineStr">
+      <x:c r="C67" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.19.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D66" s="14" t="inlineStr">
+      <x:c r="D67" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增独立SI分布测量及自动测量</x:t>
         </x:is>
       </x:c>
-      <x:c r="E66" s="14" t="inlineStr">
+      <x:c r="E67" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增独立的 SI 分布测量，可设置第一个测点的位置、测点间距、停留时间和探底频次。
 2.⁠增加自动分布测量设置，最多测 200 点。
@@ -3318,96 +3340,96 @@
 4.⁠取消测量后，不把只测了一部分的结果显示为完成。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F66" s="20" t="inlineStr">
+      <x:c r="F67" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SI 接口读到 -200.00 ℃ 或密度 0，表示暂无有效读数，不能当作实测值。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="67" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A67" s="34" t="n">
+    <x:row r="68" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A68" s="33" t="n">
         <x:v>46204</x:v>
       </x:c>
-      <x:c r="B67" s="17" t="inlineStr">
+      <x:c r="B68" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.20.3.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C67" s="17" t="inlineStr">
+      <x:c r="C68" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.18.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D67" s="18" t="inlineStr">
+      <x:c r="D68" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">编码器通信失败后自动重试</x:t>
         </x:is>
       </x:c>
-      <x:c r="E67" s="18" t="inlineStr">
+      <x:c r="E68" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠编码器通信前几次失败时立即重试。
 2.⁠持续异常不再重复刷日志，但仍继续尝试读取，便于恢复。
 3.⁠取得正常位置后及时使用，减少上电等待。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F67" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="68" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A68" s="33" t="n">
+      <x:c r="F68" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="69" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A69" s="34" t="n">
         <x:v>46202</x:v>
       </x:c>
-      <x:c r="B68" s="13" t="inlineStr">
+      <x:c r="B69" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.20.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C68" s="13" t="inlineStr">
+      <x:c r="C69" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.18.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D68" s="14" t="inlineStr">
+      <x:c r="D69" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">减少上电编码器误报和蓝牙识别失败</x:t>
         </x:is>
       </x:c>
-      <x:c r="E68" s="14" t="inlineStr">
+      <x:c r="E69" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠减少编码器刚上电未稳定时的误报。
 2.⁠过滤传感器上电时的干扰内容，减少蓝牙识别失败。
 3.⁠增加故障记录，方便区分不同的通信问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F68" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="69" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A69" s="34" t="n">
+      <x:c r="F69" s="21" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="70" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A70" s="33" t="n">
         <x:v>46200</x:v>
       </x:c>
-      <x:c r="B69" s="17" t="inlineStr">
+      <x:c r="B70" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.20.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C69" s="17" t="inlineStr">
+      <x:c r="C70" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.18.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D69" s="18" t="inlineStr">
+      <x:c r="D70" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修正测点等待时间和菜单返回</x:t>
         </x:is>
       </x:c>
-      <x:c r="E69" s="18" t="inlineStr">
+      <x:c r="E70" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复分布测量每点停留时间的单位错误，按设置的秒数等待。
 2.⁠普通菜单 120 秒无操作，自动回到状态页。
@@ -3415,64 +3437,64 @@
 4.⁠参数日志可以查看修改前后的差别。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F69" s="21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="70" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A70" s="33" t="n">
+      <x:c r="F70" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="71" s="28" customFormat="1" ht="16.5" customHeight="1">
+      <x:c r="A71" s="34" t="n">
         <x:v>46199</x:v>
       </x:c>
-      <x:c r="B70" s="13" t="inlineStr">
+      <x:c r="B71" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.20.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C70" s="13" t="inlineStr">
+      <x:c r="C71" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.18.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D70" s="14" t="inlineStr">
+      <x:c r="D71" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">密度显示两位小数，保留频率判断的小数</x:t>
         </x:is>
       </x:c>
-      <x:c r="E70" s="14" t="inlineStr">
+      <x:c r="E71" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠密度读数和相关参数统一显示两位小数。
 2.⁠修复判断液位频率变化时丢失小数的问题。
 3.⁠继电器名称统一为 K1～K4，并调整菜单顺序。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F70" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="71" s="28" customFormat="1" ht="16.5" customHeight="1">
-      <x:c r="A71" s="34" t="n">
+      <x:c r="F71" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="72" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A72" s="33" t="n">
         <x:v>46199</x:v>
       </x:c>
-      <x:c r="B71" s="17" t="inlineStr">
+      <x:c r="B72" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.19.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C71" s="17" t="inlineStr">
+      <x:c r="C72" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.17.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D71" s="18" t="inlineStr">
+      <x:c r="D72" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复液位、水位标定多出 0.1 mm</x:t>
         </x:is>
       </x:c>
-      <x:c r="E71" s="18" t="inlineStr">
+      <x:c r="E72" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复液位、水位标定结果固定多出 0.1 mm 的问题。
 2.⁠取消“强制提零点”操作。
@@ -3480,132 +3502,102 @@
 4.⁠统一使用“液位”“扭力”等名称。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F71" s="19" t="inlineStr">
+      <x:c r="F72" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">瓦锡兰通信默认改为波特率 2400、8 位数据、偶校验、1 位停止位；命令 115 不再执行。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="72" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A72" s="33" t="n">
+    <x:row r="73" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A73" s="34" t="n">
         <x:v>46199</x:v>
       </x:c>
-      <x:c r="B72" s="13" t="inlineStr">
+      <x:c r="B73" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.18.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C72" s="13" t="inlineStr">
+      <x:c r="C73" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.16.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D72" s="14" t="inlineStr">
+      <x:c r="D73" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增电流量程与正反向输出设置</x:t>
         </x:is>
       </x:c>
-      <x:c r="E72" s="14" t="inlineStr">
+      <x:c r="E73" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠可以分别设置液位范围和对应电流值。
 2.⁠支持液位升高时电流增加，或电流降低。
 3.⁠电流报警和继电器报警可分别设置。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F72" s="20" t="inlineStr">
+      <x:c r="F73" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">两块板需配套升级；升级后核对电流量程和报警值。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="73" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A73" s="34" t="n">
+    <x:row r="74" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A74" s="33" t="n">
         <x:v>46198</x:v>
       </x:c>
-      <x:c r="B73" s="17" t="inlineStr">
+      <x:c r="B74" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.18.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C73" s="17" t="inlineStr">
+      <x:c r="C74" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.16.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D73" s="18" t="inlineStr">
+      <x:c r="D74" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复继电器读数误判，息屏设置立即生效</x:t>
         </x:is>
       </x:c>
-      <x:c r="E73" s="18" t="inlineStr">
+      <x:c r="E74" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复液位已恢复正常，继电器却仍认为液位无效的问题。
 2.⁠还未测得温度时，不把初始 0 值当作真实温度报警。
 3.⁠息屏开关保存后立即生效，无需重启。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F73" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="74" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A74" s="33" t="n">
+      <x:c r="F74" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="75" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A75" s="34" t="n">
         <x:v>46198</x:v>
       </x:c>
-      <x:c r="B74" s="13" t="inlineStr">
+      <x:c r="B75" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.18.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C74" s="13" t="inlineStr">
+      <x:c r="C75" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.16.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D74" s="14" t="inlineStr">
+      <x:c r="D75" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复标零误报及手动电流测试干扰</x:t>
         </x:is>
       </x:c>
-      <x:c r="E74" s="14" t="inlineStr">
+      <x:c r="E75" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复重新标零时，探头离开零点误报扭力故障的问题。
 2.⁠完善电流测试和故障记录。
 3.⁠修复自动电流更新干扰手动电流测试的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F74" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="75" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A75" s="34" t="n">
-        <x:v>46198</x:v>
-      </x:c>
-      <x:c r="B75" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.17.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C75" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.16.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D75" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">程序说明</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E75" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠补充程序内的中文说明，设备操作和程序版本不变。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F75" s="21" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -3614,24 +3606,54 @@
     </x:row>
     <x:row r="76" s="28" customFormat="1" ht="49.5" customHeight="1">
       <x:c r="A76" s="33" t="n">
+        <x:v>46198</x:v>
+      </x:c>
+      <x:c r="B76" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.17.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C76" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.16.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D76" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">程序说明</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E76" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠补充程序内的中文说明，设备操作和程序版本不变。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F76" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="77" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A77" s="34" t="n">
         <x:v>46197</x:v>
       </x:c>
-      <x:c r="B76" s="13" t="inlineStr">
+      <x:c r="B77" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.17.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C76" s="13" t="inlineStr">
+      <x:c r="C77" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.16.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D76" s="14" t="inlineStr">
+      <x:c r="D77" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复蓝牙查询后的通信恢复和菜单返回</x:t>
         </x:is>
       </x:c>
-      <x:c r="E76" s="14" t="inlineStr">
+      <x:c r="E77" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠统一检查蓝牙主机、从机的连接状态。
 2.⁠改善查完蓝牙状态后，传感器通信未恢复的问题。
@@ -3639,326 +3661,295 @@
 4.⁠尺带厚度增加常用材料选项和手工输入。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F76" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="77" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A77" s="34" t="n">
+      <x:c r="F77" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="78" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A78" s="33" t="n">
         <x:v>46197</x:v>
       </x:c>
-      <x:c r="B77" s="17" t="inlineStr">
+      <x:c r="B78" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.16.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C77" s="17" t="inlineStr">
+      <x:c r="C78" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.15.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D77" s="18" t="inlineStr">
+      <x:c r="D78" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复探头接近测点时过早停车</x:t>
         </x:is>
       </x:c>
-      <x:c r="E77" s="18" t="inlineStr">
+      <x:c r="E78" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠单点、固定点和分布测点改为先快后慢地接近目标。
 2.⁠修复低速阶段过早停车、未到目标的问题。
 3.⁠瓦锡兰测后回固定点采用同样的定位方法。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F77" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="78" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A78" s="33" t="n">
+      <x:c r="F78" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="79" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A79" s="34" t="n">
         <x:v>46196</x:v>
       </x:c>
-      <x:c r="B78" s="13" t="inlineStr">
+      <x:c r="B79" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.16.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C78" s="13" t="inlineStr">
+      <x:c r="C79" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.15.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D78" s="14" t="inlineStr">
+      <x:c r="D79" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复继电器报警设置保存后数值不对</x:t>
         </x:is>
       </x:c>
-      <x:c r="E78" s="14" t="inlineStr">
+      <x:c r="E79" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复屏幕输入的报警上下限，保存到主控板后数值不正确的问题。
 2.⁠修复报警解除范围等设置保存不正确的问题。
 3.⁠打印参数时补全报警设置，方便核对。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F78" s="20" t="inlineStr">
+      <x:c r="F79" s="21" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">曾用旧版设置过继电器报警值的设备，升级后需重新读取并核对。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="79" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A79" s="34" t="n">
+    <x:row r="80" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A80" s="33" t="n">
         <x:v>46191</x:v>
       </x:c>
-      <x:c r="B79" s="17" t="inlineStr">
+      <x:c r="B80" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.16.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C79" s="17" t="inlineStr">
+      <x:c r="C80" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.15.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D79" s="18" t="inlineStr">
+      <x:c r="D80" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复手动通信设置被默认值覆盖</x:t>
         </x:is>
       </x:c>
-      <x:c r="E79" s="18" t="inlineStr">
+      <x:c r="E80" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复手动设置的波特率、校验位等被默认值反复覆盖的问题。
 2.⁠选好通信协议后，可以单独修改串口设置并保存。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F79" s="21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="80" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A80" s="33" t="n">
+      <x:c r="F80" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="81" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A81" s="34" t="n">
         <x:v>46190</x:v>
       </x:c>
-      <x:c r="B80" s="13" t="inlineStr">
+      <x:c r="B81" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.16.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C80" s="13" t="inlineStr">
+      <x:c r="C81" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.15.0.2</x:t>
         </x:is>
       </x:c>
-      <x:c r="D80" s="14" t="inlineStr">
+      <x:c r="D81" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">可设置日期时间，有电池可断电保留</x:t>
         </x:is>
       </x:c>
-      <x:c r="E80" s="14" t="inlineStr">
+      <x:c r="E81" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增屏幕日期和时间设置。
 2.⁠带时钟电池的显示板可在断电后保留时间。
 3.⁠旧板没有外部时钟时，仍可正常启动。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F80" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="81" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A81" s="34" t="n">
+      <x:c r="F81" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="82" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A82" s="33" t="n">
         <x:v>46190</x:v>
       </x:c>
-      <x:c r="B81" s="17" t="inlineStr">
+      <x:c r="B82" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.16.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C81" s="17" t="inlineStr">
+      <x:c r="C82" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.15.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D81" s="18" t="inlineStr">
+      <x:c r="D82" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">减少屏幕闪烁，修复参数显示异常</x:t>
         </x:is>
       </x:c>
-      <x:c r="E81" s="18" t="inlineStr">
+      <x:c r="E82" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠减少状态页频繁闪烁和读数跳动。
 2.⁠修复参数范围显示异常、输入文字超出屏幕的问题。
 3.⁠罐底检测方式只允许选择有效的两种方式。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F81" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="82" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A82" s="33" t="n">
+      <x:c r="F82" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="83" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A83" s="34" t="n">
         <x:v>46188</x:v>
       </x:c>
-      <x:c r="B82" s="13" t="inlineStr">
+      <x:c r="B83" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.16.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C82" s="13" t="inlineStr">
+      <x:c r="C83" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.15.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D82" s="14" t="inlineStr">
+      <x:c r="D83" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增电流输出开关和状态显示</x:t>
         </x:is>
       </x:c>
-      <x:c r="E82" s="14" t="inlineStr">
+      <x:c r="E83" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增电流输出开关。
 2.⁠屏幕可查看电流输出状态和相关故障。
 3.⁠整理液位对应电流的计算和测试功能。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F82" s="20" t="inlineStr">
+      <x:c r="F83" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">两块板需配套升级；升级后电流输出默认关闭。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="83" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A83" s="34" t="n">
+    <x:row r="84" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A84" s="33" t="n">
         <x:v>46186</x:v>
       </x:c>
-      <x:c r="B83" s="17" t="inlineStr">
+      <x:c r="B84" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.15.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C83" s="17" t="inlineStr">
+      <x:c r="C84" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.14.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D83" s="18" t="inlineStr">
+      <x:c r="D84" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增蓝牙信号显示，调整测量菜单</x:t>
         </x:is>
       </x:c>
-      <x:c r="E83" s="18" t="inlineStr">
+      <x:c r="E84" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠读取部件参数时可以查看蓝牙信号强度。
 2.⁠重新整理测量和探头运动菜单，方便查找。
 3.⁠修复瓦锡兰测量时，把异常频率误当空气点的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F83" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="84" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A84" s="33" t="n">
+      <x:c r="F84" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="85" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A85" s="34" t="n">
         <x:v>46186</x:v>
       </x:c>
-      <x:c r="B84" s="13" t="inlineStr">
+      <x:c r="B85" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.14.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C84" s="13" t="inlineStr">
+      <x:c r="C85" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.13.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D84" s="14" t="inlineStr">
+      <x:c r="D85" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">统一移动目标检查和停车后位置更新</x:t>
         </x:is>
       </x:c>
-      <x:c r="E84" s="14" t="inlineStr">
+      <x:c r="E85" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠统一普通移动和点动的目标位置检查。
 2.⁠统一停车后的位置更新，以及变速后恢复原速度的处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F84" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="85" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A85" s="34" t="n">
+      <x:c r="F85" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="86" s="28" customFormat="1" ht="16.5" customHeight="1">
+      <x:c r="A86" s="33" t="n">
         <x:v>46185</x:v>
       </x:c>
-      <x:c r="B85" s="17" t="inlineStr">
+      <x:c r="B86" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.14.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C85" s="17" t="inlineStr">
+      <x:c r="C86" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.13.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D85" s="18" t="inlineStr">
+      <x:c r="D86" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增三种找液位方式，调整找水位动作</x:t>
         </x:is>
       </x:c>
-      <x:c r="E85" s="18" t="inlineStr">
+      <x:c r="E86" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加三种连续找液位方式：按密度、按相对频率、按固定频率。
 2.⁠屏幕增加相应选项。
 3.⁠找水位时，若探头已在水中，先向上离开水层，再低速向下寻找。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F85" s="19" t="inlineStr">
+      <x:c r="F86" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">两块板需配套升级；方式 3“超声”尚未启用。</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="86" s="28" customFormat="1" ht="16.5" customHeight="1">
-      <x:c r="A86" s="33" t="n">
-        <x:v>46184</x:v>
-      </x:c>
-      <x:c r="B86" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.13.2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C86" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.12.1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D86" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">阻止越界移动和参数错误后的反复重测</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E86" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠普通移动和点动都会先检查目标位置，超出允许范围时不启动。
-2.⁠参数设置错误时，不再反复自动重测。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F86" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -3968,120 +3959,121 @@
       </x:c>
       <x:c r="B87" s="17" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.13.2.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C87" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.12.1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D87" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">阻止越界移动和参数错误后的反复重测</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E87" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠普通移动和点动都会先检查目标位置，超出允许范围时不启动。
+2.⁠参数设置错误时，不再反复自动重测。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F87" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="88" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A88" s="33" t="n">
+        <x:v>46184</x:v>
+      </x:c>
+      <x:c r="B88" s="13" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.13.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C87" s="17" t="inlineStr">
+      <x:c r="C88" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.12.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D87" s="18" t="inlineStr">
+      <x:c r="D88" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修正瓦锡兰空气点判断及失败结果保留</x:t>
         </x:is>
       </x:c>
-      <x:c r="E87" s="18" t="inlineStr">
+      <x:c r="E88" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠调整测点间移动和空气点判断，避免将空气中的读数算入液体结果。
 2.⁠遇到空气点后，重新寻找液面。
 3.⁠本轮测量失败时，保留上次完整结果，避免结果被清零或只剩部分测点。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F87" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="88" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A88" s="33" t="n">
+      <x:c r="F88" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="89" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A89" s="34" t="n">
         <x:v>46184</x:v>
       </x:c>
-      <x:c r="B88" s="13" t="inlineStr">
+      <x:c r="B89" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.13.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C88" s="13" t="inlineStr">
+      <x:c r="C89" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.12.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D88" s="14" t="inlineStr">
+      <x:c r="D89" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复长按确认不灵敏和确认页误跳过</x:t>
         </x:is>
       </x:c>
-      <x:c r="E88" s="14" t="inlineStr">
+      <x:c r="E89" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠改善长按确认不灵敏的问题。
 2.⁠修复先按其他键，再长按确认无法进入菜单的问题。
 3.⁠长按后需松手再确认，避免不小心跳过确认页。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F88" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="89" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A89" s="34" t="n">
+      <x:c r="F89" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="90" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A90" s="33" t="n">
         <x:v>46184</x:v>
       </x:c>
-      <x:c r="B89" s="17" t="inlineStr">
+      <x:c r="B90" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.13.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C89" s="17" t="inlineStr">
+      <x:c r="C90" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.12.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D89" s="18" t="inlineStr">
+      <x:c r="D90" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增五挡亮度，修复显示恢复后的乱码</x:t>
         </x:is>
       </x:c>
-      <x:c r="E89" s="18" t="inlineStr">
+      <x:c r="E90" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增五挡屏幕亮度设置。
 2.⁠修复退出菜单或恢复显示后可能留下乱码的问题。
 3.⁠读数变化时短暂反白显示，方便查看。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F89" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="90" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A90" s="33" t="n">
-        <x:v>46184</x:v>
-      </x:c>
-      <x:c r="B90" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.13.0.1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C90" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.11.2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D90" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">程序整理</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E90" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠整理串口测试程序和编译流程，原有测试命令不变。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F90" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -4094,7 +4086,7 @@
       </x:c>
       <x:c r="B91" s="17" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">V1.13.0.0</x:t>
+          <x:t xml:space="preserve">V1.13.0.1</x:t>
         </x:is>
       </x:c>
       <x:c r="C91" s="17" t="inlineStr">
@@ -4104,13 +4096,12 @@
       </x:c>
       <x:c r="D91" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">新增长距离与指定位置移动测试</x:t>
+          <x:t xml:space="preserve">程序整理</x:t>
         </x:is>
       </x:c>
       <x:c r="E91" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.⁠新增长距离移动和移动到指定位置的测试命令。
-2.⁠接近目标时提前减速、停车，停稳后偏差过大会报错。</x:t>
+          <x:t xml:space="preserve">1.⁠整理串口测试程序和编译流程，原有测试命令不变。</x:t>
         </x:is>
       </x:c>
       <x:c r="F91" s="19" t="inlineStr">
@@ -4125,60 +4116,60 @@
       </x:c>
       <x:c r="B92" s="13" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.13.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C92" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.11.2.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D92" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">新增长距离与指定位置移动测试</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E92" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠新增长距离移动和移动到指定位置的测试命令。
+2.⁠接近目标时提前减速、停车，停稳后偏差过大会报错。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F92" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="93" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A93" s="34" t="n">
+        <x:v>46184</x:v>
+      </x:c>
+      <x:c r="B93" s="17" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.12.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C92" s="13" t="inlineStr">
+      <x:c r="C93" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.11.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D92" s="14" t="inlineStr">
+      <x:c r="D93" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">部件参数持续刷新，避免混入旧读数</x:t>
         </x:is>
       </x:c>
-      <x:c r="E92" s="14" t="inlineStr">
+      <x:c r="E93" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠读取完成后，每秒继续更新部件参数，方便观察变化。
 2.⁠屏幕显示本次读数，不再混入其他测量的旧结果。
 3.⁠修正通过 DSM 通信接口读取角度和水电容的结果。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F92" s="15" t="inlineStr">
+      <x:c r="F93" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">旧接口名称“水位传感器电压”实际返回水电容。</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="93" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A93" s="34" t="n">
-        <x:v>46183</x:v>
-      </x:c>
-      <x:c r="B93" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.12.1.3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C93" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.11.1.4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D93" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">恢复磁通量菜单名称并补充选项说明</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E93" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠将“密度修正、温度修正”恢复为“磁通量D、磁通量T”。
-2.⁠补充菜单各选项的含义。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F93" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -4193,15 +4184,46 @@
       </x:c>
       <x:c r="C94" s="13" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.11.1.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D94" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">恢复磁通量菜单名称并补充选项说明</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E94" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠将“密度修正、温度修正”恢复为“磁通量D、磁通量T”。
+2.⁠补充菜单各选项的含义。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F94" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="95" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A95" s="34" t="n">
+        <x:v>46183</x:v>
+      </x:c>
+      <x:c r="B95" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.12.1.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C95" s="17" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.11.1.3</x:t>
         </x:is>
       </x:c>
-      <x:c r="D94" s="14" t="inlineStr">
+      <x:c r="D95" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">调整出厂设置并增加状态页信息</x:t>
         </x:is>
       </x:c>
-      <x:c r="E94" s="14" t="inlineStr">
+      <x:c r="E95" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠调整 9 项出厂默认设置。
 2.⁠读取部件参数后，可同时显示频率、电容等读数。
@@ -4209,71 +4231,41 @@
 4.⁠修正瓦锡兰测量过程中的显示项目。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F94" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="95" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A95" s="34" t="n">
+      <x:c r="F95" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="96" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A96" s="33" t="n">
         <x:v>46182</x:v>
       </x:c>
-      <x:c r="B95" s="17" t="inlineStr">
+      <x:c r="B96" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.12.1.2</x:t>
         </x:is>
       </x:c>
-      <x:c r="C95" s="17" t="inlineStr">
+      <x:c r="C96" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.11.1.2</x:t>
         </x:is>
       </x:c>
-      <x:c r="D95" s="18" t="inlineStr">
+      <x:c r="D96" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复参数显示和大数值保存错误</x:t>
         </x:is>
       </x:c>
-      <x:c r="E95" s="18" t="inlineStr">
+      <x:c r="E96" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠补齐速度、频率、电容等设置的单位。
 2.⁠修正频率小数位和手输密度范围显示。
 3.⁠修复手工输入较大数值后，保存值变小或不完整的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F95" s="19" t="inlineStr">
+      <x:c r="F96" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">升级后显示和通信设置会恢复默认，需重新设置。</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="96" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A96" s="33" t="n">
-        <x:v>46182</x:v>
-      </x:c>
-      <x:c r="B96" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.12.1.2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C96" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.11.1.1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D96" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">报警单位随所选测量项目变化</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E96" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠报警值的单位随所选测量项目变化，位置用 mm，温度用 ℃。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F96" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -4288,18 +4280,17 @@
       </x:c>
       <x:c r="C97" s="17" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">V1.11.1.0</x:t>
+          <x:t xml:space="preserve">V1.11.1.1</x:t>
         </x:is>
       </x:c>
       <x:c r="D97" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">调整出厂参数，瓦锡兰默认不探底</x:t>
+          <x:t xml:space="preserve">报警单位随所选测量项目变化</x:t>
         </x:is>
       </x:c>
       <x:c r="E97" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.⁠调整 11 项出厂默认设置，涉及自动回零、扭力、盲区和分布测量等。
-2.⁠瓦锡兰探底间隔默认设为 0，表示不探底。</x:t>
+          <x:t xml:space="preserve">1.⁠报警值的单位随所选测量项目变化，位置用 mm，温度用 ℃。</x:t>
         </x:is>
       </x:c>
       <x:c r="F97" s="19" t="inlineStr">
@@ -4314,7 +4305,7 @@
       </x:c>
       <x:c r="B98" s="13" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">V1.12.1.1</x:t>
+          <x:t xml:space="preserve">V1.12.1.2</x:t>
         </x:is>
       </x:c>
       <x:c r="C98" s="13" t="inlineStr">
@@ -4324,13 +4315,13 @@
       </x:c>
       <x:c r="D98" s="14" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">统一程序版本和设备信息显示格式</x:t>
+          <x:t xml:space="preserve">调整出厂参数，瓦锡兰默认不探底</x:t>
         </x:is>
       </x:c>
       <x:c r="E98" s="14" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.⁠程序版本统一显示为 Vx.x.x.x，便于报修时记录。
-2.⁠整理设备信息的名称和数字格式，减少显示不全。</x:t>
+          <x:t xml:space="preserve">1.⁠调整 11 项出厂默认设置，涉及自动回零、扭力、盲区和分布测量等。
+2.⁠瓦锡兰探底间隔默认设为 0，表示不探底。</x:t>
         </x:is>
       </x:c>
       <x:c r="F98" s="20" t="inlineStr">
@@ -4350,15 +4341,46 @@
       </x:c>
       <x:c r="C99" s="17" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.11.1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D99" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">统一程序版本和设备信息显示格式</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E99" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠程序版本统一显示为 Vx.x.x.x，便于报修时记录。
+2.⁠整理设备信息的名称和数字格式，减少显示不全。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F99" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="100" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A100" s="33" t="n">
+        <x:v>46182</x:v>
+      </x:c>
+      <x:c r="B100" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.12.1.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C100" s="13" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.11.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D99" s="18" t="inlineStr">
+      <x:c r="D100" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">重新分类菜单并增加关键参数确认</x:t>
         </x:is>
       </x:c>
-      <x:c r="E99" s="18" t="inlineStr">
+      <x:c r="E100" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠按测量、输出、通信、显示和维护重新整理菜单。
 2.⁠修改关键参数前增加确认，减少误操作。
@@ -4366,66 +4388,35 @@
 4.⁠修复状态页混入旧结果和文字超出屏幕的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F99" s="19" t="inlineStr">
+      <x:c r="F100" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">该版本修改通信设置会重新套用默认值。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="100" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A100" s="33" t="n">
+    <x:row r="101" s="28" customFormat="1" ht="16.5" customHeight="1">
+      <x:c r="A101" s="34" t="n">
         <x:v>46182</x:v>
       </x:c>
-      <x:c r="B100" s="13" t="inlineStr">
+      <x:c r="B101" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.12.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C100" s="13" t="inlineStr">
+      <x:c r="C101" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.10.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D100" s="14" t="inlineStr">
+      <x:c r="D101" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复停机等待和旧动作残留</x:t>
         </x:is>
       </x:c>
-      <x:c r="E100" s="14" t="inlineStr">
+      <x:c r="E101" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复电机已停稳，程序却一直等待的问题。
 2.⁠修复重新启动后可能继续跑向旧目标的问题。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F100" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="101" s="28" customFormat="1" ht="16.5" customHeight="1">
-      <x:c r="A101" s="34" t="n">
-        <x:v>46181</x:v>
-      </x:c>
-      <x:c r="B101" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.12.0.2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C101" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.10.1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D101" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">开关和模式改用文字选项设置</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E101" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠开关、模式等设置可用上下键选择文字选项。
-2.⁠进入选择页时，自动选中当前设置。</x:t>
         </x:is>
       </x:c>
       <x:c r="F101" s="21" t="inlineStr">
@@ -4445,51 +4436,52 @@
       </x:c>
       <x:c r="C102" s="13" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.10.1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D102" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">开关和模式改用文字选项设置</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E102" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠开关、模式等设置可用上下键选择文字选项。
+2.⁠进入选择页时，自动选中当前设置。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F102" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="103" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A103" s="34" t="n">
+        <x:v>46181</x:v>
+      </x:c>
+      <x:c r="B103" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.12.0.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C103" s="17" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.10.0.2</x:t>
         </x:is>
       </x:c>
-      <x:c r="D102" s="14" t="inlineStr">
+      <x:c r="D103" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">电机通信失败时不再误判已停车</x:t>
         </x:is>
       </x:c>
-      <x:c r="E102" s="14" t="inlineStr">
+      <x:c r="E103" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复读不到电机状态时，被误认为电机已停止的问题。
 2.⁠电机通信失败时保留具体故障原因。
 3.⁠统一继电器报警菜单名称。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F102" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="103" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A103" s="34" t="n">
-        <x:v>46179</x:v>
-      </x:c>
-      <x:c r="B103" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.12.0.1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C103" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.10.0.1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D103" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">程序整理</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E103" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠删除未使用的旧程序，正常测量、显示和通信功能不变。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F103" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -4502,20 +4494,50 @@
       </x:c>
       <x:c r="B104" s="13" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.12.0.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C104" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.10.0.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D104" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">程序整理</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E104" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠删除未使用的旧程序，正常测量、显示和通信功能不变。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F104" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="105" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A105" s="34" t="n">
+        <x:v>46179</x:v>
+      </x:c>
+      <x:c r="B105" s="17" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.12.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C104" s="13" t="inlineStr">
+      <x:c r="C105" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.10.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D104" s="14" t="inlineStr">
+      <x:c r="D105" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增四路继电器报警设置</x:t>
         </x:is>
       </x:c>
-      <x:c r="E104" s="14" t="inlineStr">
+      <x:c r="E105" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增四路继电器报警设置，屏幕可设置报警来源及上下限。
 2.⁠支持设置报警解除条件和接点形式。
@@ -4523,94 +4545,94 @@
 4.⁠原继电器报警设置改为新的继电器菜单。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F104" s="20" t="inlineStr">
+      <x:c r="F105" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">从 CPU2 V1.11.0.1 及更早版本升级会恢复出厂参数，升级前必须备份。第四路继电器需确认实际硬件是否支持。</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="105" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A105" s="34" t="n">
-        <x:v>46179</x:v>
-      </x:c>
-      <x:c r="B105" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.11.0.1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C105" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.9.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D105" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">程序整理</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E105" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠整理程序文件，方便研发维护，设备操作不变。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F105" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="106" s="28" customFormat="1" ht="49.5" customHeight="1">
       <x:c r="A106" s="33" t="n">
+        <x:v>46179</x:v>
+      </x:c>
+      <x:c r="B106" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.11.0.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C106" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.9.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D106" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">程序整理</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E106" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠整理程序文件，方便研发维护，设备操作不变。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F106" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="107" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A107" s="34" t="n">
         <x:v>46177</x:v>
       </x:c>
-      <x:c r="B106" s="13" t="inlineStr">
+      <x:c r="B107" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.11.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C106" s="13" t="inlineStr">
+      <x:c r="C107" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.9.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D106" s="14" t="inlineStr">
+      <x:c r="D107" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">往返测试可调速，改善复位后的启动</x:t>
         </x:is>
       </x:c>
-      <x:c r="E106" s="14" t="inlineStr">
+      <x:c r="E107" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠电机往返测试（BE）可以设置速度和加减速快慢。
 2.⁠修复往返测试范围逐次向下移动的问题。
 3.⁠改善电机断电、复位后一直提示“电机被禁止”的情况。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F106" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="107" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A107" s="34" t="n">
+      <x:c r="F107" s="21" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="108" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A108" s="33" t="n">
         <x:v>46176</x:v>
       </x:c>
-      <x:c r="B107" s="17" t="inlineStr">
+      <x:c r="B108" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.10.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C107" s="17" t="inlineStr">
+      <x:c r="C108" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.9.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D107" s="18" t="inlineStr">
+      <x:c r="D108" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">清除上电旧动作，可设置自动恢复次数</x:t>
         </x:is>
       </x:c>
-      <x:c r="E107" s="18" t="inlineStr">
+      <x:c r="E108" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠上电先清除上次遗留的运动，避免继续执行旧动作。
 2.⁠位置尚未确定时，不启动普通运动。
@@ -4618,37 +4640,6 @@
 4.⁠修复负空载扭力显示为异常大数的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F107" s="21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="108" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A108" s="33" t="n">
-        <x:v>46175</x:v>
-      </x:c>
-      <x:c r="B108" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.9.1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C108" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.8.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D108" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">测量前拦截超出允许范围的目标位置</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E108" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠测量前先检查目标位置，超出零点或进入罐底盲区时，不再让探头继续移动。
-2.⁠瓦锡兰测后回固定点也会检查目标位置。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F108" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -4661,211 +4652,242 @@
       </x:c>
       <x:c r="B109" s="17" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.9.1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C109" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.8.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D109" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">测量前拦截超出允许范围的目标位置</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E109" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠测量前先检查目标位置，超出零点或进入罐底盲区时，不再让探头继续移动。
+2.⁠瓦锡兰测后回固定点也会检查目标位置。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F109" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="110" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A110" s="33" t="n">
+        <x:v>46175</x:v>
+      </x:c>
+      <x:c r="B110" s="13" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.9.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C109" s="17" t="inlineStr">
+      <x:c r="C110" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.8.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D109" s="18" t="inlineStr">
+      <x:c r="D110" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">适配 DSM V1.228通信协议与查询</x:t>
         </x:is>
       </x:c>
-      <x:c r="E109" s="18" t="inlineStr">
+      <x:c r="E110" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加与 DSM V1.228 对外通信协议的兼容。
 2.⁠修正设备状态、命令及参数查询的返回内容。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F109" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="110" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A110" s="33" t="n">
+      <x:c r="F110" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="111" s="28" customFormat="1" ht="82.5" customHeight="1">
+      <x:c r="A111" s="34" t="n">
         <x:v>46165</x:v>
       </x:c>
-      <x:c r="B110" s="13" t="inlineStr">
+      <x:c r="B111" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.9.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C110" s="13" t="inlineStr">
+      <x:c r="C111" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.7.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D110" s="14" t="inlineStr">
+      <x:c r="D111" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增屏幕无线滑环匹配操作</x:t>
         </x:is>
       </x:c>
-      <x:c r="E110" s="14" t="inlineStr">
+      <x:c r="E111" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠屏幕新增“匹配无线滑环”，可自动选择附近信号较强的设备。
 2.⁠显示匹配进度、结果和连接设备地址。
 3.⁠增加匹配条件，减少连接到其他设备的情况。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F110" s="20" t="inlineStr">
+      <x:c r="F111" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">该版本固定点监测使用模拟数据，不能作为现场实测值。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="111" s="28" customFormat="1" ht="82.5" customHeight="1">
-      <x:c r="A111" s="34" t="n">
+    <x:row r="112" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A112" s="33" t="n">
         <x:v>46165</x:v>
       </x:c>
-      <x:c r="B111" s="17" t="inlineStr">
+      <x:c r="B112" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.8.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C111" s="17" t="inlineStr">
+      <x:c r="C112" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.6.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D111" s="18" t="inlineStr">
+      <x:c r="D112" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复往返测试启动和换向误判</x:t>
         </x:is>
       </x:c>
-      <x:c r="E111" s="18" t="inlineStr">
+      <x:c r="E112" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠调整电机运行和往返测试（B/BE），减少旧故障状态对测试启动的影响。
 2.⁠修复电机换向瞬间被误判已停稳的问题。
 3.⁠测试时按实际传感器类型检查通信。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F111" s="19" t="inlineStr">
+      <x:c r="F112" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">往返测试为调试功能，不能替代正常测量。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="112" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A112" s="33" t="n">
+    <x:row r="113" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A113" s="34" t="n">
         <x:v>46158</x:v>
       </x:c>
-      <x:c r="B112" s="13" t="inlineStr">
+      <x:c r="B113" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.8.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C112" s="13" t="inlineStr">
+      <x:c r="C113" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.6.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D112" s="14" t="inlineStr">
+      <x:c r="D113" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增SI通信接口及测量结果查询</x:t>
         </x:is>
       </x:c>
-      <x:c r="E112" s="14" t="inlineStr">
+      <x:c r="E113" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增 SI 通信接口，可读取结果、完成时间和设备状态。
 2.⁠不支持的命令不再回复成功。
 3.⁠修复读取分布结果时带入上一次测点的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F112" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="113" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A113" s="34" t="n">
+      <x:c r="F113" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="114" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A114" s="33" t="n">
         <x:v>46161</x:v>
       </x:c>
-      <x:c r="B113" s="17" t="inlineStr">
+      <x:c r="B114" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.7.3.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C113" s="17" t="inlineStr">
+      <x:c r="C114" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.5.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D113" s="18" t="inlineStr">
+      <x:c r="D114" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加探底超程停机，修复回零碰撞误报</x:t>
         </x:is>
       </x:c>
-      <x:c r="E113" s="18" t="inlineStr">
+      <x:c r="E114" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠探底超过允许下行长度仍未找到罐底时，停机并报错。
 2.⁠接近罐底时降低速度。
 3.⁠修复正常到达零点时误报碰撞的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F113" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="114" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A114" s="33" t="n">
+      <x:c r="F114" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="115" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A115" s="34" t="n">
         <x:v>46158</x:v>
       </x:c>
-      <x:c r="B114" s="13" t="inlineStr">
+      <x:c r="B115" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.7.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C114" s="13" t="inlineStr">
+      <x:c r="C115" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.5.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D114" s="14" t="inlineStr">
+      <x:c r="D115" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">液位校正后立即刷新，修复负数显示</x:t>
         </x:is>
       </x:c>
-      <x:c r="E114" s="14" t="inlineStr">
+      <x:c r="E115" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修正液位后，立即更新液位和探头位置。
 2.⁠修复负数位置或读数变成异常大数的问题。
 3.⁠瓦锡兰测后回固定点最多尝试 3 次，失败后跳过探底并转回固定点监测。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F114" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="115" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A115" s="34" t="n">
+      <x:c r="F115" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="116" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A116" s="33" t="n">
         <x:v>46158</x:v>
       </x:c>
-      <x:c r="B115" s="17" t="inlineStr">
+      <x:c r="B116" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.7.1.2</x:t>
         </x:is>
       </x:c>
-      <x:c r="C115" s="17" t="inlineStr">
+      <x:c r="C116" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.5.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D115" s="18" t="inlineStr">
+      <x:c r="D116" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复传感器切换及探头离底时的误报</x:t>
         </x:is>
       </x:c>
-      <x:c r="E115" s="18" t="inlineStr">
+      <x:c r="E116" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复 LTD 传感器（V2 协议）切换模式、读取部件参数时误报 13-13 的问题。
 2.⁠修正 DSM 传感器电压过低的提示。
@@ -4873,37 +4895,6 @@
 4.⁠减少探头离底时误报扭力故障的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F115" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="116" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A116" s="33" t="n">
-        <x:v>46157</x:v>
-      </x:c>
-      <x:c r="B116" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.7.1.1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C116" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.5.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D116" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">故障后自动重测最多3 次</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E116" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠同一次测量自动恢复后，最多重新测量 3 次。
-2.⁠达到上限后保持故障，避免一直重复测量。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F116" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -4916,7 +4907,7 @@
       </x:c>
       <x:c r="B117" s="17" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">V1.7.1.0</x:t>
+          <x:t xml:space="preserve">V1.7.1.1</x:t>
         </x:is>
       </x:c>
       <x:c r="C117" s="17" t="inlineStr">
@@ -4926,13 +4917,13 @@
       </x:c>
       <x:c r="D117" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">减少罐底误判和探头离底时的碰撞误报</x:t>
+          <x:t xml:space="preserve">故障后自动重测最多3 次</x:t>
         </x:is>
       </x:c>
       <x:c r="E117" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.⁠找罐底前先确认探头已离开罐底，避免一开始就误判找到。
-2.⁠减少探头离开罐底时误报扭力碰撞的问题。</x:t>
+          <x:t xml:space="preserve">1.⁠同一次测量自动恢复后，最多重新测量 3 次。
+2.⁠达到上限后保持故障，避免一直重复测量。</x:t>
         </x:is>
       </x:c>
       <x:c r="F117" s="19" t="inlineStr">
@@ -4947,179 +4938,210 @@
       </x:c>
       <x:c r="B118" s="13" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.7.1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C118" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.5.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D118" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">减少罐底误判和探头离底时的碰撞误报</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E118" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠找罐底前先确认探头已离开罐底，避免一开始就误判找到。
+2.⁠减少探头离开罐底时误报扭力碰撞的问题。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F118" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="119" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A119" s="34" t="n">
+        <x:v>46157</x:v>
+      </x:c>
+      <x:c r="B119" s="17" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.7.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C118" s="13" t="inlineStr">
+      <x:c r="C119" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.5.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D118" s="14" t="inlineStr">
+      <x:c r="D119" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增探底修正罐高与位置校正</x:t>
         </x:is>
       </x:c>
-      <x:c r="E118" s="14" t="inlineStr">
+      <x:c r="E119" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠新增“探底修正罐高”，用于探底后校正探头位置。
 2.⁠测得的罐高偏差过大时，不进行位置校正。
 3.⁠调整瓦锡兰测量结束后回固定点及探底的先后过程。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F118" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="119" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A119" s="34" t="n">
+      <x:c r="F119" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="120" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A120" s="33" t="n">
         <x:v>46157</x:v>
       </x:c>
-      <x:c r="B119" s="17" t="inlineStr">
+      <x:c r="B120" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.6.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C119" s="17" t="inlineStr">
+      <x:c r="C120" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.4.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D119" s="18" t="inlineStr">
+      <x:c r="D120" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">新增长按返回停止测量和查看故障</x:t>
         </x:is>
       </x:c>
-      <x:c r="E119" s="18" t="inlineStr">
+      <x:c r="E120" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠状态页长按返回键，再确认，可以停止测量并回到待机。
 2.⁠停止测量时，同时取消自动恢复。
 3.⁠故障时长按返回键，可以查看原因。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F119" s="19" t="inlineStr">
+      <x:c r="F120" s="20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">两块板需配套升级；旧主控程序不支持新增停止命令。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="120" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A120" s="33" t="n">
+    <x:row r="121" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A121" s="34" t="n">
         <x:v>46157</x:v>
       </x:c>
-      <x:c r="B120" s="13" t="inlineStr">
+      <x:c r="B121" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.5.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C120" s="13" t="inlineStr">
+      <x:c r="C121" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.3.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D120" s="14" t="inlineStr">
+      <x:c r="D121" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">拦截错误传感器数据，修复回零误报</x:t>
         </x:is>
       </x:c>
-      <x:c r="E120" s="14" t="inlineStr">
+      <x:c r="E121" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠收到不完整或错误的传感器数据时，不再当成正常读数。
 2.⁠新增传感器通信测试（SC），方便检查传感器连接。
 3.⁠修复 LTD 传感器（V2 协议）回零时，因不支持某些附加功能而误报故障的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F120" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="121" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A121" s="34" t="n">
+      <x:c r="F121" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="122" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A122" s="33" t="n">
         <x:v>46157</x:v>
       </x:c>
-      <x:c r="B121" s="17" t="inlineStr">
+      <x:c r="B122" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.5.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C121" s="17" t="inlineStr">
+      <x:c r="C122" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.3.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D121" s="18" t="inlineStr">
+      <x:c r="D122" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">屏幕新增中文故障原因显示</x:t>
         </x:is>
       </x:c>
-      <x:c r="E121" s="18" t="inlineStr">
+      <x:c r="E122" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠屏幕除了故障编号，还能显示中文原因。
 2.⁠较长的原因会分行显示，并补齐缺失文字。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F121" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="122" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A122" s="33" t="n">
+      <x:c r="F122" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="123" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A123" s="34" t="n">
         <x:v>46156</x:v>
       </x:c>
-      <x:c r="B122" s="13" t="inlineStr">
+      <x:c r="B123" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.5.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C122" s="13" t="inlineStr">
+      <x:c r="C123" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.2.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D122" s="14" t="inlineStr">
+      <x:c r="D123" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">分布测量由 100 点增加到 200 点</x:t>
         </x:is>
       </x:c>
-      <x:c r="E122" s="14" t="inlineStr">
+      <x:c r="E123" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠分布测量最多可测 200 点，原来最多 100 点。
 2.⁠屏幕可设置 200 点，瓦锡兰系统也可读取新增测点。
 3.⁠状态页增加两块板通信不匹配的提示。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F122" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="123" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A123" s="34" t="n">
+      <x:c r="F123" s="19" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="124" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A124" s="33" t="n">
         <x:v>46156</x:v>
       </x:c>
-      <x:c r="B123" s="17" t="inlineStr">
+      <x:c r="B124" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.4.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C123" s="17" t="inlineStr">
+      <x:c r="C124" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.1.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D123" s="18" t="inlineStr">
+      <x:c r="D124" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">切换操作及时响应，修复误报与漏报</x:t>
         </x:is>
       </x:c>
-      <x:c r="E123" s="18" t="inlineStr">
+      <x:c r="E124" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠等待读数稳定时，也能响应新的操作命令。
 2.⁠正常切换操作不再被误记为故障。
@@ -5127,100 +5149,69 @@
 4.⁠修复固定点密度读取失败却没有报错的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F123" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="124" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A124" s="33" t="n">
+      <x:c r="F124" s="20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="125" s="28" customFormat="1" ht="16.5" customHeight="1">
+      <x:c r="A125" s="34" t="n">
         <x:v>46155</x:v>
       </x:c>
-      <x:c r="B124" s="13" t="inlineStr">
+      <x:c r="B125" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.4.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C124" s="13" t="inlineStr">
+      <x:c r="C125" s="17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.1.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D124" s="14" t="inlineStr">
+      <x:c r="D125" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">日志区分重试过程与最终故障</x:t>
         </x:is>
       </x:c>
-      <x:c r="E124" s="14" t="inlineStr">
+      <x:c r="E125" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠日志会分开显示正在重试、重试成功和最终故障。
 2.⁠修复实际故障原因被笼统的“失败”提示盖住的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F124" s="20" t="inlineStr">
+      <x:c r="F125" s="19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">日志中的“重试”不代表设备最终报故障。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="125" s="28" customFormat="1" ht="16.5" customHeight="1">
-      <x:c r="A125" s="34" t="n">
+    <x:row r="126" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A126" s="33" t="n">
         <x:v>46154</x:v>
       </x:c>
-      <x:c r="B125" s="17" t="inlineStr">
+      <x:c r="B126" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.3.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C125" s="17" t="inlineStr">
+      <x:c r="C126" s="13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.1.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D125" s="18" t="inlineStr">
+      <x:c r="D126" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">测量失败后自动检查并尝试恢复</x:t>
         </x:is>
       </x:c>
-      <x:c r="E125" s="18" t="inlineStr">
+      <x:c r="E126" s="14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠测量失败后自动检查各部件，恢复正常后再重新测量。
 2.⁠传感器通信失败后会重新尝试。
 3.⁠完善电机驱动复位后重新启动的处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F125" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="126" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A126" s="33" t="n">
-        <x:v>46153</x:v>
-      </x:c>
-      <x:c r="B126" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.2.1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C126" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.1.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D126" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">液位信号变化后重新找液面并跟随</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E126" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠液位信号变化后，设备会重新找液面，找到后继续跟随。
-2.⁠连续读到异常频率时，会尝试切换测量模式恢复读数。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F126" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -5233,7 +5224,7 @@
       </x:c>
       <x:c r="B127" s="23" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">V1.2.0.0</x:t>
+          <x:t xml:space="preserve">V1.2.1.0</x:t>
         </x:is>
       </x:c>
       <x:c r="C127" s="23" t="inlineStr">
@@ -5243,13 +5234,13 @@
       </x:c>
       <x:c r="D127" s="23" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">新增电机往返运行测试</x:t>
+          <x:t xml:space="preserve">液位信号变化后重新找液面并跟随</x:t>
         </x:is>
       </x:c>
       <x:c r="E127" s="23" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.⁠新增电机往返测试（BE），可让电机在两个固定位置之间往返，方便检查运行距离。
-2.⁠修复新调试命令带入上一条命令内容的问题。</x:t>
+          <x:t xml:space="preserve">1.⁠液位信号变化后，设备会重新找液面，找到后继续跟随。
+2.⁠连续读到异常频率时，会尝试切换测量模式恢复读数。</x:t>
         </x:is>
       </x:c>
       <x:c r="F127" s="23" t="inlineStr">
@@ -5264,59 +5255,60 @@
       </x:c>
       <x:c r="B128" s="25" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.2.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C128" s="25" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V1.1.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C128" s="25" t="inlineStr">
+      <x:c r="D128" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">新增电机往返运行测试</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E128" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠新增电机往返测试（BE），可让电机在两个固定位置之间往返，方便检查运行距离。
+2.⁠修复新调试命令带入上一条命令内容的问题。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F128" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="129" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A129" s="35" t="n">
+        <x:v>46153</x:v>
+      </x:c>
+      <x:c r="B129" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V1.1.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D128" s="25" t="inlineStr">
+      <x:c r="C129" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.1.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D129" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">屏幕显示两板版本并提示不匹配</x:t>
         </x:is>
       </x:c>
-      <x:c r="E128" s="25" t="inlineStr">
+      <x:c r="E129" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠屏幕可以查看主控板和显示板的程序版本。
 2.⁠两块板程序不匹配时，屏幕会提示。
 3.⁠修复升级后仍显示旧程序版本的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F128" s="25" t="inlineStr">
+      <x:c r="F129" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">升级时使用配套程序包。</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="129" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A129" s="35" t="n">
-        <x:v>46153</x:v>
-      </x:c>
-      <x:c r="B129" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.0.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C129" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.0.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D129" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">主控板和显示板增加程序版本号</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E129" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠主控板、显示板都有程序版本号，方便确认设备用的程序。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F129" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">无版本号设备升级前先记录现场参数。</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -5326,377 +5318,376 @@
       </x:c>
       <x:c r="B130" s="25" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V1.0.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C130" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V1.0.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D130" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">主控板和显示板增加程序版本号</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E130" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠主控板、显示板都有程序版本号，方便确认设备用的程序。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F130" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">无版本号设备升级前先记录现场参数。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="131" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A131" s="35" t="n">
+        <x:v>46153</x:v>
+      </x:c>
+      <x:c r="B131" s="23" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V0.31.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C130" s="25" t="inlineStr">
+      <x:c r="C131" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.28.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D130" s="25" t="inlineStr">
+      <x:c r="D131" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">统一水位电容参数和跟随状态</x:t>
         </x:is>
       </x:c>
-      <x:c r="E130" s="25" t="inlineStr">
+      <x:c r="E131" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠统一主控板、显示板的水位寻找阈值和滞后阈值名称。
 2.⁠进入持续监测后才确认水位跟随状态。
 3.⁠调整等待超时和调试提示。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F130" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="131" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A131" s="35" t="n">
+      <x:c r="F131" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="132" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A132" s="36" t="n">
         <x:v>46151</x:v>
       </x:c>
-      <x:c r="B131" s="23" t="inlineStr">
+      <x:c r="B132" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.31.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C131" s="23" t="inlineStr">
+      <x:c r="C132" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.28.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D131" s="23" t="inlineStr">
+      <x:c r="D132" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加水位变化监测和定期探底</x:t>
         </x:is>
       </x:c>
-      <x:c r="E131" s="23" t="inlineStr">
+      <x:c r="E132" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠水位跟随稳定后继续监测水位变化。
 2.⁠水位寻找阈值和跟随滞后阈值分开设置。
 3.⁠瓦锡兰密度测量可设置每隔若干次重新探底。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F131" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="132" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A132" s="36" t="n">
+      <x:c r="F132" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="133" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A133" s="35" t="n">
         <x:v>46151</x:v>
       </x:c>
-      <x:c r="B132" s="25" t="inlineStr">
+      <x:c r="B133" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.30.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C132" s="25" t="inlineStr">
+      <x:c r="C133" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.27.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D132" s="25" t="inlineStr">
+      <x:c r="D133" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加电机驱动通信测试和状态上报</x:t>
         </x:is>
       </x:c>
-      <x:c r="E132" s="25" t="inlineStr">
+      <x:c r="E133" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加电机驱动芯片（TMC5130）静态通信测试。
 2.⁠电机状态改为由主循环统一刷新。
 3.⁠补充屏幕菜单说明。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F132" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="133" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A133" s="35" t="n">
+      <x:c r="F133" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="134" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A134" s="36" t="n">
         <x:v>46150</x:v>
       </x:c>
-      <x:c r="B133" s="23" t="inlineStr">
+      <x:c r="B134" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.29.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C133" s="23" t="inlineStr">
+      <x:c r="C134" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.26.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D133" s="23" t="inlineStr">
+      <x:c r="D134" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">完善电机测试和驱动故障诊断</x:t>
         </x:is>
       </x:c>
-      <x:c r="E133" s="23" t="inlineStr">
+      <x:c r="E134" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠电机往返测试可设置更多运行参数。
 2.⁠完善电机驱动芯片（TMC5130）的到位确认和故障状态读取。
 3.⁠检测到驱动异常时停机。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F133" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="134" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A134" s="36" t="n">
+      <x:c r="F134" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="135" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A135" s="35" t="n">
         <x:v>46148</x:v>
       </x:c>
-      <x:c r="B134" s="25" t="inlineStr">
+      <x:c r="B135" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.28.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C134" s="25" t="inlineStr">
+      <x:c r="C135" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.26.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D134" s="25" t="inlineStr">
+      <x:c r="D135" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加位置来源切换和屏幕字库</x:t>
         </x:is>
       </x:c>
-      <x:c r="E134" s="25" t="inlineStr">
+      <x:c r="E135" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加电机位置来源自动切换。
 2.⁠增加找罐底后的编码器位置修正和失步检测设置。
 3.⁠显示板补齐新增菜单所需中文字。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F134" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="135" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A135" s="35" t="n">
+      <x:c r="F135" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="136" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A136" s="36" t="n">
         <x:v>46142</x:v>
       </x:c>
-      <x:c r="B135" s="23" t="inlineStr">
+      <x:c r="B136" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.27.3.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C135" s="23" t="inlineStr">
+      <x:c r="C136" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.25.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D135" s="23" t="inlineStr">
+      <x:c r="D136" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复回零和记步状态</x:t>
         </x:is>
       </x:c>
-      <x:c r="E135" s="23" t="inlineStr">
+      <x:c r="E136" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修正粗找零点、精找零点和停稳判断。
 2.⁠修正回零过程中的速度更新。
 3.⁠回零后清除旧的记步基准并更新参数校验。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F135" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="136" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A136" s="36" t="n">
+      <x:c r="F136" s="26" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="137" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A137" s="35" t="n">
         <x:v>46141</x:v>
       </x:c>
-      <x:c r="B136" s="25" t="inlineStr">
+      <x:c r="B137" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.27.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C136" s="25" t="inlineStr">
+      <x:c r="C137" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.25.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D136" s="25" t="inlineStr">
+      <x:c r="D137" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">加强电机位置读数保护</x:t>
         </x:is>
       </x:c>
-      <x:c r="E136" s="25" t="inlineStr">
+      <x:c r="E137" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠拆分电机驱动设置、运动控制和位置换算。
 2.⁠电机驱动芯片（TMC5130）位置读数增加稳定检查。
 3.⁠位置写入失败时不采用错误结果，并调整回零减速。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F136" s="26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="137" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A137" s="35" t="n">
+      <x:c r="F137" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="138" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A138" s="36" t="n">
         <x:v>46140</x:v>
       </x:c>
-      <x:c r="B137" s="23" t="inlineStr">
+      <x:c r="B138" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.27.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C137" s="23" t="inlineStr">
+      <x:c r="C138" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.25.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D137" s="23" t="inlineStr">
+      <x:c r="D138" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复电机状态显示并让电流立即生效</x:t>
         </x:is>
       </x:c>
-      <x:c r="E137" s="23" t="inlineStr">
+      <x:c r="E138" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠根据电机驱动状态和目标位置判断是否正在运行。
 2.⁠修改电机运行电流后立即下发。
 3.⁠屏幕显示、保存值和电机实际设置保持一致。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F137" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="138" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A138" s="36" t="n">
+      <x:c r="F138" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="139" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A139" s="35" t="n">
         <x:v>46140</x:v>
       </x:c>
-      <x:c r="B138" s="25" t="inlineStr">
+      <x:c r="B139" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.27.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C138" s="25" t="inlineStr">
+      <x:c r="C139" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.25.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D138" s="25" t="inlineStr">
+      <x:c r="D139" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">统一电机位置和测量参数</x:t>
         </x:is>
       </x:c>
-      <x:c r="E138" s="25" t="inlineStr">
+      <x:c r="E139" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠统一电机驱动、位置读取和编码器换算。
 2.⁠调整测量流程使用的电机参数。
 3.⁠主控板、显示板同步更新状态、菜单和参数。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F138" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="139" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A139" s="35" t="n">
+      <x:c r="F139" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="140" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A140" s="36" t="n">
         <x:v>46137</x:v>
       </x:c>
-      <x:c r="B139" s="23" t="inlineStr">
+      <x:c r="B140" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.27.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C139" s="23" t="inlineStr">
+      <x:c r="C140" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.25.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D139" s="23" t="inlineStr">
+      <x:c r="D140" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加固定点演示模式</x:t>
         </x:is>
       </x:c>
-      <x:c r="E139" s="23" t="inlineStr">
+      <x:c r="E140" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加固定点模拟测量和周期数据刷新。
 2.⁠可用串口调试命令启动演示。
 3.⁠演示过程可被新命令中止。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F139" s="23" t="inlineStr">
+      <x:c r="F140" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">演示模式使用模拟数据，不能作为现场实测值。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="140" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A140" s="36" t="n">
+    <x:row r="141" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A141" s="35" t="n">
         <x:v>46137</x:v>
       </x:c>
-      <x:c r="B140" s="25" t="inlineStr">
+      <x:c r="B141" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.26.3.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C140" s="25" t="inlineStr">
+      <x:c r="C141" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.25.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D140" s="25" t="inlineStr">
+      <x:c r="D141" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">调整故障处理顺序并增强探底容错</x:t>
         </x:is>
       </x:c>
-      <x:c r="E140" s="25" t="inlineStr">
+      <x:c r="E141" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠调整新命令和故障状态的处理先后。
 2.⁠找罐底增加陀螺仪基准取值和二次精找。
 3.⁠探底异常时增加退出处理，并调整水位跟随判断。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F140" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="141" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A141" s="35" t="n">
-        <x:v>46125</x:v>
-      </x:c>
-      <x:c r="B141" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.26.2.1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C141" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.25.1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D141" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">减少显示板参数重复保存</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E141" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠短时间内连续修改的显示板参数合并保存。
-2.⁠减少存储器重复写入和通信等待。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F141" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -5709,51 +5700,82 @@
       </x:c>
       <x:c r="B142" s="25" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V0.26.2.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C142" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V0.25.1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D142" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">减少显示板参数重复保存</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E142" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠短时间内连续修改的显示板参数合并保存。
+2.⁠减少存储器重复写入和通信等待。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F142" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="143" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A143" s="35" t="n">
+        <x:v>46125</x:v>
+      </x:c>
+      <x:c r="B143" s="23" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V0.26.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C142" s="25" t="inlineStr">
+      <x:c r="C143" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.25.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D142" s="25" t="inlineStr">
+      <x:c r="D143" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">调试操作可被新命令中止</x:t>
         </x:is>
       </x:c>
-      <x:c r="E142" s="25" t="inlineStr">
+      <x:c r="E143" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠串口调试操作也会检查是否收到新命令。
 2.⁠持续运行测试和电机等待过程中收到新命令会退出并停机。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F142" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="143" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A143" s="35" t="n">
+      <x:c r="F143" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="144" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A144" s="36" t="n">
         <x:v>46122</x:v>
       </x:c>
-      <x:c r="B143" s="23" t="inlineStr">
+      <x:c r="B144" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.26.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C143" s="23" t="inlineStr">
+      <x:c r="C144" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.25.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D143" s="23" t="inlineStr">
+      <x:c r="D144" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">完善液位重试和电机状态显示</x:t>
         </x:is>
       </x:c>
-      <x:c r="E143" s="23" t="inlineStr">
+      <x:c r="E144" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠传感器通信失败时按统一方式重试。
 2.⁠完善液位模式恢复和盲区等待退出。
@@ -5761,355 +5783,324 @@
 4.⁠屏幕电机图标与主控板实际状态保持一致。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F143" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="144" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A144" s="36" t="n">
+      <x:c r="F144" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="145" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A145" s="35" t="n">
         <x:v>46121</x:v>
       </x:c>
-      <x:c r="B144" s="25" t="inlineStr">
+      <x:c r="B145" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.26.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C144" s="25" t="inlineStr">
+      <x:c r="C145" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.25.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D144" s="25" t="inlineStr">
+      <x:c r="D145" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加罐高标定和屏幕联动</x:t>
         </x:is>
       </x:c>
-      <x:c r="E144" s="25" t="inlineStr">
+      <x:c r="E145" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加罐高标定操作、状态和参数。
 2.⁠屏幕增加罐高标定入口。
 3.⁠修正找罐底、水位和液位角度等数据显示。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F144" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="145" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A145" s="35" t="n">
+      <x:c r="F145" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="146" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A146" s="36" t="n">
         <x:v>46111</x:v>
       </x:c>
-      <x:c r="B145" s="23" t="inlineStr">
+      <x:c r="B146" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.25.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C145" s="23" t="inlineStr">
+      <x:c r="C146" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.24.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D145" s="23" t="inlineStr">
+      <x:c r="D146" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">水位长时间未稳定仍进入监测</x:t>
         </x:is>
       </x:c>
-      <x:c r="E145" s="23" t="inlineStr">
+      <x:c r="E146" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加等待水位稳定的最长时间。
 2.⁠超过等待时间后仍进入水位跟随监测，避免流程一直停在等待状态。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F145" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="146" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A146" s="36" t="n">
+      <x:c r="F146" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="147" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A147" s="35" t="n">
         <x:v>46109</x:v>
       </x:c>
-      <x:c r="B146" s="25" t="inlineStr">
+      <x:c r="B147" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.25.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C146" s="25" t="inlineStr">
+      <x:c r="C147" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.24.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D146" s="25" t="inlineStr">
+      <x:c r="D147" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">水位标定后恢复跟随</x:t>
         </x:is>
       </x:c>
-      <x:c r="E146" s="25" t="inlineStr">
+      <x:c r="E147" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠水位标定完成后恢复原来的跟随状态。
 2.⁠统一检查水位标定结果是否有效。
 3.⁠密度分布结束后的单点监测可被新操作中止。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F146" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="147" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A147" s="35" t="n">
+      <x:c r="F147" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="148" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A148" s="36" t="n">
         <x:v>46109</x:v>
       </x:c>
-      <x:c r="B147" s="23" t="inlineStr">
+      <x:c r="B148" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.25.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C147" s="23" t="inlineStr">
+      <x:c r="C148" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.24.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D147" s="23" t="inlineStr">
+      <x:c r="D148" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加编码器断线和称重超时检测</x:t>
         </x:is>
       </x:c>
-      <x:c r="E147" s="23" t="inlineStr">
+      <x:c r="E148" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠电机位置编码器读数异常或断线时可识别并重试。
 2.⁠称重通信长时间无回复时会报错。
 3.⁠显示板同步增加对应故障提示。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F147" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="148" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A148" s="36" t="n">
+      <x:c r="F148" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="149" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A149" s="35" t="n">
         <x:v>46109</x:v>
       </x:c>
-      <x:c r="B148" s="25" t="inlineStr">
+      <x:c r="B149" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.24.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C148" s="25" t="inlineStr">
+      <x:c r="C149" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.23.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D148" s="25" t="inlineStr">
+      <x:c r="D149" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">改善板间通信恢复和液位流程</x:t>
         </x:is>
       </x:c>
-      <x:c r="E148" s="25" t="inlineStr">
+      <x:c r="E149" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠显示板串口收发切换和异常恢复更稳定。
 2.⁠调整主控板水位跟随和找液位过程。
 3.⁠完善两块板状态同步和传感器异常处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F148" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="149" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A149" s="35" t="n">
+      <x:c r="F149" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="150" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A150" s="36" t="n">
         <x:v>46108</x:v>
       </x:c>
-      <x:c r="B149" s="23" t="inlineStr">
+      <x:c r="B150" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.24.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C149" s="23" t="inlineStr">
+      <x:c r="C150" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.23.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D149" s="23" t="inlineStr">
+      <x:c r="D150" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">完善水位跟随和切换操作</x:t>
         </x:is>
       </x:c>
-      <x:c r="E149" s="23" t="inlineStr">
+      <x:c r="E150" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠统一测量过程中切换新操作的判断。
 2.⁠水位稳定判断时间可设置。
 3.⁠调整水位跟随步长和传感器异常处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F149" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="150" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A150" s="36" t="n">
+      <x:c r="F150" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="151" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A151" s="35" t="n">
         <x:v>46108</x:v>
       </x:c>
-      <x:c r="B150" s="25" t="inlineStr">
+      <x:c r="B151" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.23.4.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C150" s="25" t="inlineStr">
+      <x:c r="C151" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.23.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D150" s="25" t="inlineStr">
+      <x:c r="D151" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复密度分布测点范围和液位单位</x:t>
         </x:is>
       </x:c>
-      <x:c r="E150" s="25" t="inlineStr">
+      <x:c r="E151" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修正指定区间密度测量使用的上下限。
 2.⁠液位高度统一按 0.1 mm 保存。
 3.⁠当前操作不再被误判为切换操作。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F150" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="151" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A151" s="35" t="n">
+      <x:c r="F151" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="152" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A152" s="36" t="n">
         <x:v>46106</x:v>
       </x:c>
-      <x:c r="B151" s="23" t="inlineStr">
+      <x:c r="B152" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.23.3.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C151" s="23" t="inlineStr">
+      <x:c r="C152" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.23.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D151" s="23" t="inlineStr">
+      <x:c r="D152" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">清理程序编译告警</x:t>
         </x:is>
       </x:c>
-      <x:c r="E151" s="23" t="inlineStr">
+      <x:c r="E152" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠清理主控板程序中的声明、数据读取和未使用调试功能告警。
 2.⁠清理显示板数据校验、显示和瓦锡兰参数转发告警。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F151" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="152" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A152" s="36" t="n">
+      <x:c r="F152" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="153" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A153" s="35" t="n">
         <x:v>46098</x:v>
       </x:c>
-      <x:c r="B152" s="25" t="inlineStr">
+      <x:c r="B153" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.23.3.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C152" s="25" t="inlineStr">
+      <x:c r="C153" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.23.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D152" s="25" t="inlineStr">
+      <x:c r="D153" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">改善两块板通信恢复和参数同步</x:t>
         </x:is>
       </x:c>
-      <x:c r="E152" s="25" t="inlineStr">
+      <x:c r="E153" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠显示板通信异常后可恢复收发。
 2.⁠完善显示板参数保存和批量同步。
 3.⁠修正主控板数据轮询和命令处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F152" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="153" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A153" s="35" t="n">
+      <x:c r="F153" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="154" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A154" s="36" t="n">
         <x:v>46097</x:v>
       </x:c>
-      <x:c r="B153" s="23" t="inlineStr">
+      <x:c r="B154" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.23.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C153" s="23" t="inlineStr">
+      <x:c r="C154" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.23.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D153" s="23" t="inlineStr">
+      <x:c r="D154" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">细分无线和传感器通信故障</x:t>
         </x:is>
       </x:c>
-      <x:c r="E153" s="23" t="inlineStr">
+      <x:c r="E154" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠无线滑环主机、无线从机和传感器通信故障可分别提示。
 2.⁠修正 DSM 传感器、LTD 传感器及无线通信回复的长度和完整性检查。
 3.⁠修正通信错误与故障提示的对应关系。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F153" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="154" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A154" s="36" t="n">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="B154" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.23.1.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C154" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.23.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D154" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">恢复回零水位和探底分段变速</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E154" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠统一电机带速度运行的调用方式。
-2.⁠恢复回零、找水位和找罐底过程中的分段变速。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F154" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -6122,120 +6113,120 @@
       </x:c>
       <x:c r="B155" s="23" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V0.23.1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C155" s="23" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V0.23.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C155" s="23" t="inlineStr">
+      <x:c r="D155" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">恢复回零水位和探底分段变速</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E155" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠统一电机带速度运行的调用方式。
+2.⁠恢复回零、找水位和找罐底过程中的分段变速。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F155" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="156" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A156" s="36" t="n">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="B156" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.23.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D155" s="23" t="inlineStr">
+      <x:c r="C156" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V0.23.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D156" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加按条件运行和临时速度控制</x:t>
         </x:is>
       </x:c>
-      <x:c r="E155" s="23" t="inlineStr">
+      <x:c r="E156" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠电机可运行到指定条件满足后停止。
 2.⁠单次运动可指定临时速度。
 3.⁠临时运动结束后恢复原设置速度。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F155" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="156" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A156" s="36" t="n">
+      <x:c r="F156" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="157" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A157" s="35" t="n">
         <x:v>46093</x:v>
       </x:c>
-      <x:c r="B156" s="25" t="inlineStr">
+      <x:c r="B157" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.22.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C156" s="25" t="inlineStr">
+      <x:c r="C157" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.23.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D156" s="25" t="inlineStr">
+      <x:c r="D157" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复无线滑环主机编译缺少声明</x:t>
         </x:is>
       </x:c>
-      <x:c r="E156" s="25" t="inlineStr">
+      <x:c r="E157" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠补齐无线滑环主机通信程序的函数声明。
 2.⁠修复相关程序编译时找不到通信接口的问题。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F156" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="157" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A157" s="35" t="n">
+      <x:c r="F157" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="158" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A158" s="36" t="n">
         <x:v>46087</x:v>
       </x:c>
-      <x:c r="B157" s="23" t="inlineStr">
+      <x:c r="B158" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.22.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C157" s="23" t="inlineStr">
+      <x:c r="C158" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.23.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D157" s="23" t="inlineStr">
+      <x:c r="D158" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加恒线速度和失步检测</x:t>
         </x:is>
       </x:c>
-      <x:c r="E157" s="23" t="inlineStr">
+      <x:c r="E158" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠根据尺带卷径变化自动调整电机速度，使探头升降速度更稳定。
 2.⁠增加电机实际位置与记录不一致的失步检测。
 3.⁠增加速度限制和运行中速度修正。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F157" s="27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="158" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A158" s="36" t="n">
-        <x:v>46087</x:v>
-      </x:c>
-      <x:c r="B158" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.21.0.1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C158" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.22.0.1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D158" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">增加开发资料入口</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E158" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠在项目说明中增加开发资料入口。
-2.⁠更新仓库程序资料清单。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F158" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -6248,121 +6239,121 @@
       </x:c>
       <x:c r="B159" s="23" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V0.21.0.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C159" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V0.22.0.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D159" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">增加开发资料入口</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E159" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠在项目说明中增加开发资料入口。
+2.⁠更新仓库程序资料清单。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F159" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="160" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A160" s="36" t="n">
+        <x:v>46087</x:v>
+      </x:c>
+      <x:c r="B160" s="25" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V0.21.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C159" s="23" t="inlineStr">
+      <x:c r="C160" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.22.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D159" s="23" t="inlineStr">
+      <x:c r="D160" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">设备参数和位置记录增加双份保存</x:t>
         </x:is>
       </x:c>
-      <x:c r="E159" s="23" t="inlineStr">
+      <x:c r="E160" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠设备参数和电机位置记录各保存两份。
 2.⁠一份记录损坏时可改用另一份。
 3.⁠增加双份记录损坏时的恢复检查。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F159" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="160" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A160" s="36" t="n">
+      <x:c r="F160" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="161" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A161" s="35" t="n">
         <x:v>46086</x:v>
       </x:c>
-      <x:c r="B160" s="25" t="inlineStr">
+      <x:c r="B161" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.20.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C160" s="25" t="inlineStr">
+      <x:c r="C161" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.22.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D160" s="25" t="inlineStr">
+      <x:c r="D161" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加液位水位和尺带补偿参数</x:t>
         </x:is>
       </x:c>
-      <x:c r="E160" s="25" t="inlineStr">
+      <x:c r="E161" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加液位变化滞后时间和水位修正设置。
 2.⁠增加气相温度和尺带温度补偿设置。
 3.⁠主控板、显示板同步增加参数和菜单。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F160" s="25" t="inlineStr">
+      <x:c r="F161" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">升级后会恢复默认参数；升级前记录现场参数，升级后重新设置并复核。</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="161" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A161" s="35" t="n">
+    <x:row r="162" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A162" s="36" t="n">
         <x:v>46086</x:v>
       </x:c>
-      <x:c r="B161" s="23" t="inlineStr">
+      <x:c r="B162" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.19.4.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C161" s="23" t="inlineStr">
+      <x:c r="C162" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.21.1.2</x:t>
         </x:is>
       </x:c>
-      <x:c r="D161" s="23" t="inlineStr">
+      <x:c r="D162" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">恢复运动碰撞检测并整理运行流程</x:t>
         </x:is>
       </x:c>
-      <x:c r="E161" s="23" t="inlineStr">
+      <x:c r="E162" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠恢复探头运动时的称重碰撞检测。
 2.⁠整理主控板运行和测试入口。
 3.⁠调整电机驱动设置。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F161" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="162" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A162" s="36" t="n">
-        <x:v>46085</x:v>
-      </x:c>
-      <x:c r="B162" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.19.3.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C162" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.21.1.1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D162" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">增加显示板自动编译检查</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E162" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠增加显示板程序的自动编译配置。
-2.⁠自动构建检查同时覆盖主控板和显示板。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F162" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -6380,84 +6371,84 @@
       </x:c>
       <x:c r="C163" s="23" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V0.21.1.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D163" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">增加显示板自动编译检查</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E163" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠增加显示板程序的自动编译配置。
+2.⁠自动构建检查同时覆盖主控板和显示板。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F163" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="164" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A164" s="36" t="n">
+        <x:v>46085</x:v>
+      </x:c>
+      <x:c r="B164" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V0.19.3.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C164" s="25" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V0.21.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D163" s="23" t="inlineStr">
+      <x:c r="D164" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复不同开发环境下的编译问题</x:t>
         </x:is>
       </x:c>
-      <x:c r="E163" s="23" t="inlineStr">
+      <x:c r="E164" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠统一主控板、显示板程序文件名称的大小写。
 2.⁠避免在区分大小写的开发环境中找不到文件。
 3.⁠同步调整水位电容换算和位置更新引用。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F163" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="164" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A164" s="36" t="n">
+      <x:c r="F164" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="165" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A165" s="35" t="n">
         <x:v>46085</x:v>
       </x:c>
-      <x:c r="B164" s="25" t="inlineStr">
+      <x:c r="B165" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.19.2.6</x:t>
         </x:is>
       </x:c>
-      <x:c r="C164" s="25" t="inlineStr">
+      <x:c r="C165" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.21.0.2</x:t>
         </x:is>
       </x:c>
-      <x:c r="D164" s="25" t="inlineStr">
+      <x:c r="D165" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">补充开发资料和称重接口说明</x:t>
         </x:is>
       </x:c>
-      <x:c r="E164" s="25" t="inlineStr">
+      <x:c r="E165" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠整理仓库导览资料。
 2.⁠增加主控板程序拆分方案。
 3.⁠补充称重接口说明。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F164" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="165" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A165" s="35" t="n">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="B165" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.19.2.5</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C165" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.21.0.2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D165" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">清理旧验证工程和历史副本</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E165" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠删除不再使用的文本、电机、水位等验证工程。
-2.⁠保留当前主控板、显示板和无线滑环主机工程作为维护入口。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F165" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -6470,23 +6461,23 @@
       </x:c>
       <x:c r="B166" s="25" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">V0.19.2.4</x:t>
+          <x:t xml:space="preserve">V0.19.2.5</x:t>
         </x:is>
       </x:c>
       <x:c r="C166" s="25" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">V0.21.0.1</x:t>
+          <x:t xml:space="preserve">V0.21.0.2</x:t>
         </x:is>
       </x:c>
       <x:c r="D166" s="25" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">停止维护旧工程目录</x:t>
+          <x:t xml:space="preserve">清理旧验证工程和历史副本</x:t>
         </x:is>
       </x:c>
       <x:c r="E166" s="25" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.⁠旧工程目录不再作为当前程序维护内容。
-2.⁠同步整理忽略规则、编辑器设置和构建配置。</x:t>
+          <x:t xml:space="preserve">1.⁠删除不再使用的文本、电机、水位等验证工程。
+2.⁠保留当前主控板、显示板和无线滑环主机工程作为维护入口。</x:t>
         </x:is>
       </x:c>
       <x:c r="F166" s="25" t="inlineStr">
@@ -6501,23 +6492,23 @@
       </x:c>
       <x:c r="B167" s="23" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">V0.19.2.3</x:t>
+          <x:t xml:space="preserve">V0.19.2.4</x:t>
         </x:is>
       </x:c>
       <x:c r="C167" s="23" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">V0.21.0.0</x:t>
+          <x:t xml:space="preserve">V0.21.0.1</x:t>
         </x:is>
       </x:c>
       <x:c r="D167" s="23" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">主控板接入自动构建</x:t>
+          <x:t xml:space="preserve">停止维护旧工程目录</x:t>
         </x:is>
       </x:c>
       <x:c r="E167" s="23" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.⁠合并主控板的两套自动编译配置。
-2.⁠增加持续自动构建检查。</x:t>
+          <x:t xml:space="preserve">1.⁠旧工程目录不再作为当前程序维护内容。
+2.⁠同步整理忽略规则、编辑器设置和构建配置。</x:t>
         </x:is>
       </x:c>
       <x:c r="F167" s="23" t="inlineStr">
@@ -6532,7 +6523,7 @@
       </x:c>
       <x:c r="B168" s="25" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">V0.19.2.2</x:t>
+          <x:t xml:space="preserve">V0.19.2.3</x:t>
         </x:is>
       </x:c>
       <x:c r="C168" s="25" t="inlineStr">
@@ -6542,13 +6533,13 @@
       </x:c>
       <x:c r="D168" s="25" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">完善主控板自动编译基础</x:t>
+          <x:t xml:space="preserve">主控板接入自动构建</x:t>
         </x:is>
       </x:c>
       <x:c r="E168" s="25" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.⁠补齐主控板自动编译所需的工程配置。
-2.⁠增加编译预设、程序链接设置和基础说明。</x:t>
+          <x:t xml:space="preserve">1.⁠合并主控板的两套自动编译配置。
+2.⁠增加持续自动构建检查。</x:t>
         </x:is>
       </x:c>
       <x:c r="F168" s="25" t="inlineStr">
@@ -6563,7 +6554,7 @@
       </x:c>
       <x:c r="B169" s="23" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">V0.19.2.1</x:t>
+          <x:t xml:space="preserve">V0.19.2.2</x:t>
         </x:is>
       </x:c>
       <x:c r="C169" s="23" t="inlineStr">
@@ -6573,13 +6564,13 @@
       </x:c>
       <x:c r="D169" s="23" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">增加主控板自动编译检查</x:t>
+          <x:t xml:space="preserve">完善主控板自动编译基础</x:t>
         </x:is>
       </x:c>
       <x:c r="E169" s="23" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.⁠增加主控板程序的自动编译配置。
-2.⁠补充本机构建说明。</x:t>
+          <x:t xml:space="preserve">1.⁠补齐主控板自动编译所需的工程配置。
+2.⁠增加编译预设、程序链接设置和基础说明。</x:t>
         </x:is>
       </x:c>
       <x:c r="F169" s="23" t="inlineStr">
@@ -6594,438 +6585,438 @@
       </x:c>
       <x:c r="B170" s="25" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V0.19.2.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C170" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V0.21.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D170" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">增加主控板自动编译检查</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E170" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠增加主控板程序的自动编译配置。
+2.⁠补充本机构建说明。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F170" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="171" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A171" s="35" t="n">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="B171" s="23" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V0.19.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C170" s="25" t="inlineStr">
+      <x:c r="C171" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.21.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D170" s="25" t="inlineStr">
+      <x:c r="D171" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加罐高显示并修复水位跟随状态</x:t>
         </x:is>
       </x:c>
-      <x:c r="E170" s="25" t="inlineStr">
+      <x:c r="E171" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠屏幕增加罐高结果显示。
 2.⁠修正部分参数写入后的数值。
 3.⁠每次快速寻找水位前清除上一次判断记录。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F170" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="171" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A171" s="35" t="n">
+      <x:c r="F171" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="172" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A172" s="36" t="n">
         <x:v>46080</x:v>
       </x:c>
-      <x:c r="B171" s="23" t="inlineStr">
+      <x:c r="B172" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.19.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C171" s="23" t="inlineStr">
+      <x:c r="C172" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.20.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D171" s="23" t="inlineStr">
+      <x:c r="D172" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复显示板参数写入数值错误</x:t>
         </x:is>
       </x:c>
-      <x:c r="E171" s="23" t="inlineStr">
+      <x:c r="E172" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修复显示板写入部分参数后数值不正确的问题。
 2.⁠统一串口接收长度和参数转发处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F171" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="172" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A172" s="36" t="n">
+      <x:c r="F172" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="173" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A173" s="35" t="n">
         <x:v>46079</x:v>
       </x:c>
-      <x:c r="B172" s="25" t="inlineStr">
+      <x:c r="B173" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.19.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C172" s="25" t="inlineStr">
+      <x:c r="C173" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.20.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D172" s="25" t="inlineStr">
+      <x:c r="D173" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加水位快速寻找和跟随</x:t>
         </x:is>
       </x:c>
-      <x:c r="E172" s="25" t="inlineStr">
+      <x:c r="E173" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加水位快速寻找。
 2.⁠根据水位信号变化判断是否找到水面。
 3.⁠找到水面后进入持续跟随。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F172" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="173" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A173" s="35" t="n">
+      <x:c r="F173" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="174" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A174" s="36" t="n">
         <x:v>46056</x:v>
       </x:c>
-      <x:c r="B173" s="23" t="inlineStr">
+      <x:c r="B174" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.18.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C173" s="23" t="inlineStr">
+      <x:c r="C174" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.19.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D173" s="23" t="inlineStr">
+      <x:c r="D174" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复福建LNG现场通信和状态显示</x:t>
         </x:is>
       </x:c>
-      <x:c r="E173" s="23" t="inlineStr">
+      <x:c r="E174" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修正瓦锡兰系统读取数据和下发参数时的回复。
 2.⁠修正设备工作状态对应关系。
 3.⁠调整密度测量、单点监测和传感器有效值处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F173" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="174" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A174" s="36" t="n">
+      <x:c r="F174" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="175" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A175" s="35" t="n">
         <x:v>46055</x:v>
       </x:c>
-      <x:c r="B174" s="25" t="inlineStr">
+      <x:c r="B175" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.18.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C174" s="25" t="inlineStr">
+      <x:c r="C175" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.19.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D174" s="25" t="inlineStr">
+      <x:c r="D175" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加多种液位测量方式</x:t>
         </x:is>
       </x:c>
-      <x:c r="E174" s="25" t="inlineStr">
+      <x:c r="E175" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加相对频率、固定频率、密度和超声液位测量方式。
 2.⁠增加液位跟随所需的频率和密度设置。
 3.⁠完善密度读数稳定判断。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F174" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="175" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A175" s="35" t="n">
+      <x:c r="F175" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="176" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A176" s="36" t="n">
         <x:v>46046</x:v>
       </x:c>
-      <x:c r="B175" s="23" t="inlineStr">
+      <x:c r="B176" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.17.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C175" s="23" t="inlineStr">
+      <x:c r="C176" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.18.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D175" s="23" t="inlineStr">
+      <x:c r="D176" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复版本显示和液位参数单位</x:t>
         </x:is>
       </x:c>
-      <x:c r="E175" s="23" t="inlineStr">
+      <x:c r="E176" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修正显示板程序版本显示。
 2.⁠修正液位方式及相关修正参数的单位。
 3.⁠调整探头角度的显示条件。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F175" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="176" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A176" s="36" t="n">
+      <x:c r="F176" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="177" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A177" s="35" t="n">
         <x:v>46045</x:v>
       </x:c>
-      <x:c r="B176" s="25" t="inlineStr">
+      <x:c r="B177" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.17.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C176" s="25" t="inlineStr">
+      <x:c r="C177" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.18.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D176" s="25" t="inlineStr">
+      <x:c r="D177" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复电机定位和无效密度采用</x:t>
         </x:is>
       </x:c>
-      <x:c r="E176" s="25" t="inlineStr">
+      <x:c r="E177" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠按尺带卷绕变化修正电机位置换算。
 2.⁠修复电机到位停止判断。
 3.⁠密度读数无效时不再作为测量结果。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F176" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="177" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A177" s="35" t="n">
+      <x:c r="F177" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="178" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A178" s="36" t="n">
         <x:v>46041</x:v>
       </x:c>
-      <x:c r="B177" s="23" t="inlineStr">
+      <x:c r="B178" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.17.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C177" s="23" t="inlineStr">
+      <x:c r="C178" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.18.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D177" s="23" t="inlineStr">
+      <x:c r="D178" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加上电默认操作和水位零点参数</x:t>
         </x:is>
       </x:c>
-      <x:c r="E177" s="23" t="inlineStr">
+      <x:c r="E178" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠可设置设备上电后的默认操作。
 2.⁠增加水位零点电容和瓦锡兰密度参数。
 3.⁠完善水位标定、瓦锡兰状态和电机控制。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F177" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="178" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A178" s="36" t="n">
+      <x:c r="F178" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="179" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A179" s="35" t="n">
         <x:v>46037</x:v>
       </x:c>
-      <x:c r="B178" s="25" t="inlineStr">
+      <x:c r="B179" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.16.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C178" s="25" t="inlineStr">
+      <x:c r="C179" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.17.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D178" s="25" t="inlineStr">
+      <x:c r="D179" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加水位调试操作和探底角度显示</x:t>
         </x:is>
       </x:c>
-      <x:c r="E178" s="25" t="inlineStr">
+      <x:c r="E179" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加水位跟随、运行到位、强制运动和水位标定调试操作。
 2.⁠屏幕增加探底方式选择。
 3.⁠屏幕可查看陀螺仪角度。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F178" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="179" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A179" s="35" t="n">
+      <x:c r="F179" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="180" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A180" s="36" t="n">
         <x:v>46034</x:v>
       </x:c>
-      <x:c r="B179" s="23" t="inlineStr">
+      <x:c r="B180" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.15.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C179" s="23" t="inlineStr">
+      <x:c r="C180" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.16.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D179" s="23" t="inlineStr">
+      <x:c r="D180" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">整理屏幕菜单和测量流程</x:t>
         </x:is>
       </x:c>
-      <x:c r="E179" s="23" t="inlineStr">
+      <x:c r="E180" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠重新整理显示板参数分组、命令状态显示和中文字库检查。
 2.⁠完善主控板测量调度、电机位置、称重和水位处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F179" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="180" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A180" s="36" t="n">
+      <x:c r="F180" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="181" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A181" s="35" t="n">
         <x:v>46031</x:v>
       </x:c>
-      <x:c r="B180" s="25" t="inlineStr">
+      <x:c r="B181" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.15.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C180" s="25" t="inlineStr">
+      <x:c r="C181" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.16.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D180" s="25" t="inlineStr">
+      <x:c r="D181" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">补齐设备参数和屏幕设置</x:t>
         </x:is>
       </x:c>
-      <x:c r="E180" s="25" t="inlineStr">
+      <x:c r="E181" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠补齐设备、机械、称重、液位、水位和罐底设置。
 2.⁠显示板同步增加菜单和参数读写。
 3.⁠两块板的参数保存内容保持对应。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F180" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="181" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A181" s="35" t="n">
+      <x:c r="F181" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="182" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A182" s="36" t="n">
         <x:v>46031</x:v>
       </x:c>
-      <x:c r="B181" s="23" t="inlineStr">
+      <x:c r="B182" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.14.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C181" s="23" t="inlineStr">
+      <x:c r="C182" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.15.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D181" s="23" t="inlineStr">
+      <x:c r="D182" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复显示板本机参数被错写</x:t>
         </x:is>
       </x:c>
-      <x:c r="E181" s="23" t="inlineStr">
+      <x:c r="E182" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠显示板批量读取主控板参数时，不再覆盖显示板自己的通信设置。
 2.⁠补充找罐底状态检查。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F181" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="182" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A182" s="36" t="n">
+      <x:c r="F182" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="183" s="28" customFormat="1" ht="66" customHeight="1">
+      <x:c r="A183" s="35" t="n">
         <x:v>46028</x:v>
       </x:c>
-      <x:c r="B182" s="25" t="inlineStr">
+      <x:c r="B183" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.14.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C182" s="25" t="inlineStr">
+      <x:c r="C183" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.15.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D182" s="25" t="inlineStr">
+      <x:c r="D183" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">调整水位跟随稳定判断</x:t>
         </x:is>
       </x:c>
-      <x:c r="E182" s="25" t="inlineStr">
+      <x:c r="E183" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠调整水位跟随的移动步长和变化滞后。
 2.⁠调整水位信号丢失判断。
 3.⁠同步电机相关设置并增加内部中文编码检查资料。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F182" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="183" s="28" customFormat="1" ht="66" customHeight="1">
-      <x:c r="A183" s="35" t="n">
-        <x:v>46022</x:v>
-      </x:c>
-      <x:c r="B183" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.14.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C183" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.15.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D183" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">增加电机测试并调整运行保护</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E183" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠增加电机往返和测量流程测试。
-2.⁠调整找罐底、找液位、回零时的电机保护。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F183" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -7038,116 +7029,147 @@
       </x:c>
       <x:c r="B184" s="25" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V0.14.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C184" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V0.15.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D184" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">增加电机测试并调整运行保护</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E184" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠增加电机往返和测量流程测试。
+2.⁠调整找罐底、找液位、回零时的电机保护。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F184" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="185" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A185" s="35" t="n">
+        <x:v>46022</x:v>
+      </x:c>
+      <x:c r="B185" s="23" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V0.13.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C184" s="25" t="inlineStr">
+      <x:c r="C185" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.15.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D184" s="25" t="inlineStr">
+      <x:c r="D185" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加陀螺仪探底方式</x:t>
         </x:is>
       </x:c>
-      <x:c r="E184" s="25" t="inlineStr">
+      <x:c r="E185" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加根据探头倾斜角度判断罐底的方式。
 2.⁠保留原有称重探底方式。
 3.⁠增加角度读取、基准保存和探底设置。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F184" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="185" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A185" s="35" t="n">
+      <x:c r="F185" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="186" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A186" s="36" t="n">
         <x:v>46021</x:v>
       </x:c>
-      <x:c r="B185" s="23" t="inlineStr">
+      <x:c r="B186" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.12.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C185" s="23" t="inlineStr">
+      <x:c r="C186" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.15.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D185" s="23" t="inlineStr">
+      <x:c r="D186" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加多种密度分布测量方式</x:t>
         </x:is>
       </x:c>
-      <x:c r="E185" s="23" t="inlineStr">
+      <x:c r="E186" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠增加普通分布、国标、每米和指定区间密度测量。
 2.⁠统一测点生成、单点取值和结果汇总。
 3.⁠显示板可读取各种分布测量结果。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F185" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="186" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A186" s="36" t="n">
+      <x:c r="F186" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="187" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A187" s="35" t="n">
         <x:v>46017</x:v>
       </x:c>
-      <x:c r="B186" s="25" t="inlineStr">
+      <x:c r="B187" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.11.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C186" s="25" t="inlineStr">
+      <x:c r="C187" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.14.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D186" s="25" t="inlineStr">
+      <x:c r="D187" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复水位重新寻找和通信解析</x:t>
         </x:is>
       </x:c>
-      <x:c r="E186" s="25" t="inlineStr">
+      <x:c r="E187" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠水位状态异常时，探头分步上行重新寻找水面。
 2.⁠修正显示板接收 DSM 数据和主控板数据时的解析问题。
 3.⁠删除重复的菜单处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F186" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="187" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A187" s="35" t="n">
+      <x:c r="F187" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="188" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A188" s="36" t="n">
         <x:v>46016</x:v>
       </x:c>
-      <x:c r="B187" s="23" t="inlineStr">
+      <x:c r="B188" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.11.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C187" s="23" t="inlineStr">
+      <x:c r="C188" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.14.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D187" s="23" t="inlineStr">
+      <x:c r="D188" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">改善多路通信并减少数据冲突</x:t>
         </x:is>
       </x:c>
-      <x:c r="E187" s="23" t="inlineStr">
+      <x:c r="E188" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠不同外部通信按端口设置分别处理。
 2.⁠多条待发送数据改为排队发送，减少互相占用。
@@ -7155,642 +7177,611 @@
 4.⁠完善主控板水位测量流程。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F187" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="188" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A188" s="36" t="n">
+      <x:c r="F188" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="189" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A189" s="35" t="n">
         <x:v>46011</x:v>
       </x:c>
-      <x:c r="B188" s="25" t="inlineStr">
+      <x:c r="B189" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.11.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C188" s="25" t="inlineStr">
+      <x:c r="C189" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.13.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D188" s="25" t="inlineStr">
+      <x:c r="D189" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加水位测量和通信设置菜单</x:t>
         </x:is>
       </x:c>
-      <x:c r="E188" s="25" t="inlineStr">
+      <x:c r="E189" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠主控板增加找水位、水位标定和水位跟随。
 2.⁠显示板增加波特率、校验方式、停止位和通信类型设置。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F188" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="189" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A189" s="35" t="n">
+      <x:c r="F189" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="190" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A190" s="36" t="n">
         <x:v>46007</x:v>
       </x:c>
-      <x:c r="B189" s="23" t="inlineStr">
+      <x:c r="B190" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.10.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C189" s="23" t="inlineStr">
+      <x:c r="C190" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.12.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D189" s="23" t="inlineStr">
+      <x:c r="D190" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">统一主控板和显示板工程名称</x:t>
         </x:is>
       </x:c>
-      <x:c r="E189" s="23" t="inlineStr">
+      <x:c r="E190" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠现用主控板工程统一命名为 CPU2。
 2.⁠现用显示板工程统一命名为 CPU3。
 3.⁠旧工程移入历史目录。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F189" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="190" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A190" s="36" t="n">
+      <x:c r="F190" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="191" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A191" s="35" t="n">
         <x:v>46006</x:v>
       </x:c>
-      <x:c r="B190" s="25" t="inlineStr">
+      <x:c r="B191" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.10.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C190" s="25" t="inlineStr">
+      <x:c r="C191" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.12.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D190" s="25" t="inlineStr">
+      <x:c r="D191" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复显示板通信中断后的恢复</x:t>
         </x:is>
       </x:c>
-      <x:c r="E190" s="25" t="inlineStr">
+      <x:c r="E191" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠显示板串口接收异常后可重新启动接收。
 2.⁠调整三路 RS485 发送后的收发切换时间。
 3.⁠修正部分参数转发。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F190" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="191" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A191" s="35" t="n">
+      <x:c r="F191" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="192" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A192" s="36" t="n">
         <x:v>46003</x:v>
       </x:c>
-      <x:c r="B191" s="23" t="inlineStr">
+      <x:c r="B192" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.10.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C191" s="23" t="inlineStr">
+      <x:c r="C192" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.12.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D191" s="23" t="inlineStr">
+      <x:c r="D192" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">整理显示板参数同步和菜单</x:t>
         </x:is>
       </x:c>
-      <x:c r="E191" s="23" t="inlineStr">
+      <x:c r="E192" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠将显示板本机设置与主控板参数分开同步。
 2.⁠整理罐上操作菜单。
 3.⁠调整外部通信和两板内部通信处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F191" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="192" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A192" s="36" t="n">
+      <x:c r="F192" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="193" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A193" s="35" t="n">
         <x:v>46002</x:v>
       </x:c>
-      <x:c r="B192" s="25" t="inlineStr">
+      <x:c r="B193" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.10.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C192" s="25" t="inlineStr">
+      <x:c r="C193" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.12.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D192" s="25" t="inlineStr">
+      <x:c r="D193" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">通信设置可保存并增加运行看护</x:t>
         </x:is>
       </x:c>
-      <x:c r="E192" s="25" t="inlineStr">
+      <x:c r="E193" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠显示板的三路通信方式、波特率等设置可保存，重启后继续使用。
 2.⁠通信设置修改后可自动重新配置。
 3.⁠主控板和显示板增加运行看护，程序异常卡住时可自动复位。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F192" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="193" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A193" s="35" t="n">
+      <x:c r="F193" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="194" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A194" s="36" t="n">
         <x:v>46000</x:v>
       </x:c>
-      <x:c r="B193" s="23" t="inlineStr">
+      <x:c r="B194" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.9.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C193" s="23" t="inlineStr">
+      <x:c r="C194" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.11.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D193" s="23" t="inlineStr">
+      <x:c r="D194" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加无线传感器通信重试</x:t>
         </x:is>
       </x:c>
-      <x:c r="E193" s="23" t="inlineStr">
+      <x:c r="E194" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠主控板增加无线传感器通信。
 2.⁠通信超时或数据不完整时会重新尝试。
 3.⁠显示板同步读取无线连接状态和相关参数。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F193" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="194" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A194" s="36" t="n">
+      <x:c r="F194" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="195" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A195" s="35" t="n">
         <x:v>45999</x:v>
       </x:c>
-      <x:c r="B194" s="25" t="inlineStr">
+      <x:c r="B195" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.8.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C194" s="25" t="inlineStr">
+      <x:c r="C195" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.10.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D194" s="25" t="inlineStr">
+      <x:c r="D195" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">完善瓦锡兰密度分布测量</x:t>
         </x:is>
       </x:c>
-      <x:c r="E194" s="25" t="inlineStr">
+      <x:c r="E195" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠完善密度分布测量的测点安排和稳定取值。
 2.⁠显示板可按实际测点数分段读取全部结果。
 3.⁠同步无线滑环主机的相关程序。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F194" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="195" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A195" s="35" t="n">
+      <x:c r="F195" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="196" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A196" s="36" t="n">
         <x:v>45995</x:v>
       </x:c>
-      <x:c r="B195" s="23" t="inlineStr">
+      <x:c r="B196" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.7.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C195" s="23" t="inlineStr">
+      <x:c r="C196" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.9.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D195" s="23" t="inlineStr">
+      <x:c r="D196" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">统一设备参数和运行状态</x:t>
         </x:is>
       </x:c>
-      <x:c r="E195" s="23" t="inlineStr">
+      <x:c r="E196" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠统一主控板、显示板的设备参数、操作命令和运行状态。
 2.⁠调整屏幕菜单分组和称重显示。
 3.⁠完善瓦锡兰参数及数据同步。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F195" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="196" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A196" s="36" t="n">
+      <x:c r="F196" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="197" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A197" s="35" t="n">
         <x:v>45992</x:v>
       </x:c>
-      <x:c r="B196" s="25" t="inlineStr">
+      <x:c r="B197" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.6.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C196" s="25" t="inlineStr">
+      <x:c r="C197" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.8.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D196" s="25" t="inlineStr">
+      <x:c r="D197" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">调整测量命令并增加密度参数</x:t>
         </x:is>
       </x:c>
-      <x:c r="E196" s="25" t="inlineStr">
+      <x:c r="E197" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠重新编排主控板、显示板的测量和调试命令。
 2.⁠增加密度计算和显示所需参数。
 3.⁠增加瓦锡兰测量所需参数。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F196" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="197" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A197" s="35" t="n">
+      <x:c r="F197" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="198" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A198" s="36" t="n">
         <x:v>45987</x:v>
       </x:c>
-      <x:c r="B197" s="23" t="inlineStr">
+      <x:c r="B198" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.5.1.2</x:t>
         </x:is>
       </x:c>
-      <x:c r="C197" s="23" t="inlineStr">
+      <x:c r="C198" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.7.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D197" s="23" t="inlineStr">
+      <x:c r="D198" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">调整中文程序编码</x:t>
         </x:is>
       </x:c>
-      <x:c r="E197" s="23" t="inlineStr">
+      <x:c r="E198" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠调整主控板、显示板中文程序文件的编码。
 2.⁠保证中文菜单和调试文字可在原开发工具中正常显示。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F197" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="198" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A198" s="36" t="n">
+      <x:c r="F198" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="199" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A199" s="35" t="n">
         <x:v>45981</x:v>
       </x:c>
-      <x:c r="B198" s="25" t="inlineStr">
+      <x:c r="B199" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.5.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C198" s="25" t="inlineStr">
+      <x:c r="C199" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.7.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D198" s="25" t="inlineStr">
+      <x:c r="D199" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">显示板增加瓦锡兰通信</x:t>
         </x:is>
       </x:c>
-      <x:c r="E198" s="25" t="inlineStr">
+      <x:c r="E199" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠显示板增加与瓦锡兰系统的通信。
 2.⁠支持瓦锡兰系统读取结果、设备状态和相关参数。
 3.⁠将外部通信和两板内部通信分开处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F198" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="199" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A199" s="35" t="n">
+      <x:c r="F199" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="200" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A200" s="36" t="n">
         <x:v>45980</x:v>
       </x:c>
-      <x:c r="B199" s="23" t="inlineStr">
+      <x:c r="B200" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.5.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C199" s="23" t="inlineStr">
+      <x:c r="C200" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.6.1.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D199" s="23" t="inlineStr">
+      <x:c r="D200" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">整理显示板运行入口和主控板传感器程序</x:t>
         </x:is>
       </x:c>
-      <x:c r="E199" s="23" t="inlineStr">
+      <x:c r="E200" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠显示板增加统一的开机初始化和运行入口。
 2.⁠整理主控板串口、传感器和电机程序。
 3.⁠移除未使用的采集驱动文件。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F199" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="200" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A200" s="36" t="n">
+      <x:c r="F200" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="201" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A201" s="35" t="n">
         <x:v>45979</x:v>
       </x:c>
-      <x:c r="B200" s="25" t="inlineStr">
+      <x:c r="B201" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.5.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C200" s="25" t="inlineStr">
+      <x:c r="C201" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.6.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D200" s="25" t="inlineStr">
+      <x:c r="D201" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">修复液位更新和回零卡住</x:t>
         </x:is>
       </x:c>
-      <x:c r="E200" s="25" t="inlineStr">
+      <x:c r="E201" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠修正液位更新、下行距离和盲区处理。
 2.⁠修正部分参数显示的小数位。
 3.⁠零点标定卡住时会报错并让探头上行退出。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F200" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="201" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A201" s="35" t="n">
+      <x:c r="F201" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="202" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A202" s="36" t="n">
         <x:v>45971</x:v>
       </x:c>
-      <x:c r="B201" s="23" t="inlineStr">
+      <x:c r="B202" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.5.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C201" s="23" t="inlineStr">
+      <x:c r="C202" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.6.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D201" s="23" t="inlineStr">
+      <x:c r="D202" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">传感器通信按类型分开处理</x:t>
         </x:is>
       </x:c>
-      <x:c r="E201" s="23" t="inlineStr">
+      <x:c r="E202" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠DSM 传感器和 LTD 传感器改为分别处理。
 2.⁠增加密度测量入口。
 3.⁠统一主控板、显示板的命令、状态和参数对应关系。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F201" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="202" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A202" s="36" t="n">
+      <x:c r="F202" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="203" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A203" s="35" t="n">
         <x:v>45965</x:v>
       </x:c>
-      <x:c r="B202" s="25" t="inlineStr">
+      <x:c r="B203" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.4.2.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C202" s="25" t="inlineStr">
+      <x:c r="C203" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.5.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D202" s="25" t="inlineStr">
+      <x:c r="D203" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">完善测量流程和两板通信</x:t>
         </x:is>
       </x:c>
-      <x:c r="E202" s="25" t="inlineStr">
+      <x:c r="E203" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠继续完善回零、找罐底、液位、电机和传感器处理。
 2.⁠调整主控板与显示板的 RS485 收发控制。
 3.⁠完善 HART 通信处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F202" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="203" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A203" s="35" t="n">
+      <x:c r="F203" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="204" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A204" s="36" t="n">
         <x:v>45953</x:v>
       </x:c>
-      <x:c r="B203" s="23" t="inlineStr">
+      <x:c r="B204" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.4.1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C203" s="23" t="inlineStr">
+      <x:c r="C204" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.5.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D203" s="23" t="inlineStr">
+      <x:c r="D204" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">完善电机称重和回零故障处理</x:t>
         </x:is>
       </x:c>
-      <x:c r="E203" s="23" t="inlineStr">
+      <x:c r="E204" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠完善电机运动和称重采样处理。
 2.⁠调整回零、找罐底和液位测量过程。
 3.⁠补充相应故障提示。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F203" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="204" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A204" s="36" t="n">
+      <x:c r="F204" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="205" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A205" s="35" t="n">
         <x:v>45948</x:v>
       </x:c>
-      <x:c r="B204" s="25" t="inlineStr">
+      <x:c r="B205" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.4.0.2</x:t>
         </x:is>
       </x:c>
-      <x:c r="C204" s="25" t="inlineStr">
+      <x:c r="C205" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.5.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D204" s="25" t="inlineStr">
+      <x:c r="D205" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">整理主控板程序结构</x:t>
         </x:is>
       </x:c>
-      <x:c r="E204" s="25" t="inlineStr">
+      <x:c r="E205" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠整理主控板的驱动、服务和应用程序目录。
 2.⁠调整故障、测量、传感器和电机程序之间的调用关系。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F204" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="205" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A205" s="35" t="n">
+      <x:c r="F205" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="206" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A206" s="36" t="n">
         <x:v>45947</x:v>
       </x:c>
-      <x:c r="B205" s="23" t="inlineStr">
+      <x:c r="B206" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.4.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C205" s="23" t="inlineStr">
+      <x:c r="C206" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.5.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D205" s="23" t="inlineStr">
+      <x:c r="D206" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">调整找液位和液位跟随流程</x:t>
         </x:is>
       </x:c>
-      <x:c r="E205" s="23" t="inlineStr">
+      <x:c r="E206" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠调整找液位、液位跟随、称重和传感器配合过程。
 2.⁠整理主控板程序目录。
 3.⁠同步显示板与主控板的数据对应关系。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F205" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="206" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A206" s="36" t="n">
+      <x:c r="F206" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="207" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A207" s="35" t="n">
         <x:v>45910</x:v>
       </x:c>
-      <x:c r="B206" s="25" t="inlineStr">
+      <x:c r="B207" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.4.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C206" s="25" t="inlineStr">
+      <x:c r="C207" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.5.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D206" s="25" t="inlineStr">
+      <x:c r="D207" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">主控板增加HART通信和电流输出支持</x:t>
         </x:is>
       </x:c>
-      <x:c r="E206" s="25" t="inlineStr">
+      <x:c r="E207" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠主控板接入 HART 通信。
 2.⁠完善 4-20mA 电流输出及相关接口控制。
 3.⁠同步无线滑环主机的通信处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F206" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="207" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A207" s="35" t="n">
-        <x:v>45905</x:v>
-      </x:c>
-      <x:c r="B207" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.3.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C207" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V0.5.0.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D207" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">显示板增加一体机通信</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E207" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1.⁠显示板可与一体机上位系统通信。
-2.⁠支持设备参数读取、设置和数据回复。</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F207" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
@@ -7808,210 +7799,241 @@
       </x:c>
       <x:c r="C208" s="25" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">V0.5.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D208" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">显示板增加一体机通信</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E208" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.⁠显示板可与一体机上位系统通信。
+2.⁠支持设备参数读取、设置和数据回复。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F208" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="209" s="28" customFormat="1" ht="49.5" customHeight="1">
+      <x:c r="A209" s="35" t="n">
+        <x:v>45905</x:v>
+      </x:c>
+      <x:c r="B209" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">V0.3.0.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C209" s="23" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">V0.4.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D208" s="25" t="inlineStr">
+      <x:c r="D209" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">增加4-20mA电流输出</x:t>
         </x:is>
       </x:c>
-      <x:c r="E208" s="25" t="inlineStr">
+      <x:c r="E209" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠主控板增加 4-20mA 电流输出。
 2.⁠补充电流输出和 HART 通信所需的硬件接口设置。
 3.⁠显示板增加对应的通信接口设置。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F208" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="209" s="28" customFormat="1" ht="49.5" customHeight="1">
-      <x:c r="A209" s="35" t="n">
+      <x:c r="F209" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="210" s="28" customFormat="1" ht="33" customHeight="1">
+      <x:c r="A210" s="36" t="n">
         <x:v>45903</x:v>
       </x:c>
-      <x:c r="B209" s="23" t="inlineStr">
+      <x:c r="B210" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.2.0.2</x:t>
         </x:is>
       </x:c>
-      <x:c r="C209" s="23" t="inlineStr">
+      <x:c r="C210" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.3.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D209" s="23" t="inlineStr">
+      <x:c r="D210" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">降低无线滑环主机运行频率</x:t>
         </x:is>
       </x:c>
-      <x:c r="E209" s="23" t="inlineStr">
+      <x:c r="E210" s="25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠降低无线滑环主机运行频率，减少运行功耗。
 2.⁠同步调整主控板测量和显示板通信设置。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F209" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="210" s="28" customFormat="1" ht="33" customHeight="1">
-      <x:c r="A210" s="36" t="n">
+      <x:c r="F210" s="25" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="211">
+      <x:c r="A211" s="35" t="n">
         <x:v>45901</x:v>
       </x:c>
-      <x:c r="B210" s="25" t="inlineStr">
+      <x:c r="B211" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.2.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C210" s="25" t="inlineStr">
+      <x:c r="C211" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.3.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D210" s="25" t="inlineStr">
+      <x:c r="D211" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">显示板启用第三路通信接口</x:t>
         </x:is>
       </x:c>
-      <x:c r="E210" s="25" t="inlineStr">
+      <x:c r="E211" s="23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠显示板增加第三路 RS485 通信接口。
 2.⁠接入数据接收和主板通信处理。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F210" s="25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="211">
-      <x:c r="A211" s="35" t="n">
+      <x:c r="F211" s="23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" t="n">
         <x:v>45898</x:v>
       </x:c>
-      <x:c r="B211" s="23" t="inlineStr">
+      <x:c r="B212" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.2.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C211" s="23" t="inlineStr">
+      <x:c r="C212" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.2.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D211" s="23" t="inlineStr">
+      <x:c r="D212" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">显示板增加对外通信和罐上操作</x:t>
         </x:is>
       </x:c>
-      <x:c r="E211" s="23" t="inlineStr">
+      <x:c r="E212" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠显示板增加与上位系统的通信。
 2.⁠完善罐上操作菜单、按键和状态显示。
 3.⁠同步主控板与显示板之间的操作传递。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F211" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="212">
-      <x:c r="A212" t="n">
+      <x:c r="F212" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" t="n">
         <x:v>45876</x:v>
       </x:c>
-      <x:c r="B212" t="inlineStr">
+      <x:c r="B213" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.2.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C212" t="inlineStr">
+      <x:c r="C213" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.1.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D212" t="inlineStr">
+      <x:c r="D213" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">显示板增加菜单和主控通信</x:t>
         </x:is>
       </x:c>
-      <x:c r="E212" t="inlineStr">
+      <x:c r="E213" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠显示板增加菜单、按键和参数设置。
 2.⁠建立显示板与主控板的数据读取和操作控制。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F212" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="213">
-      <x:c r="A213" t="n">
+      <x:c r="F213" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" t="n">
         <x:v>45873</x:v>
       </x:c>
-      <x:c r="B213" t="inlineStr">
+      <x:c r="B214" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.1.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C213" t="inlineStr">
+      <x:c r="C214" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.0.0.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="D213" t="inlineStr">
+      <x:c r="D214" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">主控板建立基础测量与故障处理</x:t>
         </x:is>
       </x:c>
-      <x:c r="E213" t="inlineStr">
+      <x:c r="E214" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠主控板增加基础测量调度和故障处理。
 2.⁠接入传感器、电机、称重和设备参数保存。
 3.⁠同步整理显示板和无线滑环相关程序。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F213" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="214">
-      <x:c r="A214" t="n">
+      <x:c r="F214" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215" t="n">
         <x:v>45841</x:v>
       </x:c>
-      <x:c r="B214" t="inlineStr">
+      <x:c r="B215" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.0.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C214" t="inlineStr">
+      <x:c r="C215" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V0.0.0.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="D214" t="inlineStr">
+      <x:c r="D215" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">建立首个程序基础版本</x:t>
         </x:is>
       </x:c>
-      <x:c r="E214" t="inlineStr">
+      <x:c r="E215" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.⁠建立主控板、显示板和无线滑环主机的初始程序。
 2.⁠加入早期外围部件检查工程，作为后续开发基础。</x:t>
         </x:is>
       </x:c>
-      <x:c r="F214" t="inlineStr">
+      <x:c r="F215" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">21</x:t>
         </x:is>
@@ -8024,7 +8046,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc9634e87f8f4d96"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcbc90a38410040e4"/>
   </x:tableParts>
 </x:worksheet>
 </file>